--- a/TTABLEAU DES PRIX AVEC REF.xlsx
+++ b/TTABLEAU DES PRIX AVEC REF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melou\blazing-dynasty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC32455-E2E2-4706-AC24-3656A79C89EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3365A63-375A-479C-8CCA-F3DBD20F654F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13935" yWindow="75" windowWidth="13665" windowHeight="14925" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$375</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$376</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="1126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="1127">
   <si>
     <t>Art</t>
   </si>
@@ -3406,6 +3406,9 @@
   </si>
   <si>
     <t>https://www.mihi.care/storage/mini/26/07/tM0TGy6Er6F7Q4ionXoL02WiWeH7CcLEp8q3VJfB.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitamins. Complexe de détoxification et de purification du côlon </t>
   </si>
 </sst>
 </file>
@@ -3815,7 +3818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M378"/>
+  <dimension ref="A1:M379"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -5909,280 +5912,278 @@
       <c r="J86" s="2"/>
     </row>
     <row r="87" spans="1:13">
-      <c r="A87" s="2" t="s">
-        <v>246</v>
+      <c r="A87" s="2">
+        <v>100238</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>247</v>
+        <v>1126</v>
       </c>
       <c r="D87" s="2">
-        <v>9.9</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="E87" s="2">
-        <v>6.93</v>
+        <v>12.53</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
-      <c r="I87" s="3" t="s">
+      <c r="I87" s="3"/>
+      <c r="J87" s="2"/>
+    </row>
+    <row r="88" spans="1:13">
+      <c r="A88" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D88" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="E88" s="2">
+        <v>6.93</v>
+      </c>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="J87" s="2"/>
-    </row>
-    <row r="88" spans="1:13">
-      <c r="A88" s="4" t="s">
+      <c r="J88" s="2"/>
+    </row>
+    <row r="89" spans="1:13">
+      <c r="A89" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B89" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C88" s="6" t="s">
+      <c r="C89" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="D88" s="6">
+      <c r="D89" s="6">
         <v>38.5</v>
       </c>
-      <c r="E88" s="6">
+      <c r="E89" s="6">
         <v>26.95</v>
       </c>
-      <c r="F88" s="6"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="7" t="s">
+      <c r="F89" s="6"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="J88" s="8"/>
-      <c r="K88" s="9"/>
-      <c r="L88" s="9"/>
-    </row>
-    <row r="89" spans="1:13">
-      <c r="A89" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D89" s="2">
-        <v>17.899999999999999</v>
-      </c>
-      <c r="E89" s="2">
-        <v>12.53</v>
-      </c>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J89" s="2"/>
+      <c r="J89" s="8"/>
+      <c r="K89" s="9"/>
+      <c r="L89" s="9"/>
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>9</v>
+        <v>253</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D90" s="2">
-        <v>47</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="E90" s="2">
-        <v>32.9</v>
+        <v>12.53</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
       <c r="I90" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="J90" s="2"/>
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>253</v>
+        <v>9</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D91" s="2">
-        <v>10.5</v>
+        <v>47</v>
       </c>
       <c r="E91" s="2">
-        <v>7.35</v>
+        <v>32.9</v>
       </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
       <c r="I91" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="J91" s="2"/>
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D92" s="2">
-        <v>8.9</v>
+        <v>10.5</v>
       </c>
       <c r="E92" s="2">
-        <v>6.23</v>
+        <v>7.35</v>
       </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
       <c r="I92" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="J92" s="2"/>
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D93" s="2">
-        <v>12.9</v>
+        <v>8.9</v>
       </c>
       <c r="E93" s="2">
-        <v>9.0299999999999994</v>
+        <v>6.23</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
       <c r="I93" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="J93" s="2"/>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D94" s="2">
-        <v>15.9</v>
+        <v>12.9</v>
       </c>
       <c r="E94" s="2">
-        <v>11.13</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="J94" s="2"/>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D95" s="2">
-        <v>9.9</v>
+        <v>15.9</v>
       </c>
       <c r="E95" s="2">
-        <v>6.93</v>
+        <v>11.13</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="J95" s="2"/>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D96" s="2">
-        <v>10.9</v>
+        <v>9.9</v>
       </c>
       <c r="E96" s="2">
-        <v>7.63</v>
+        <v>6.93</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J96" s="2"/>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D97" s="2">
-        <v>16.899999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="E97" s="2">
-        <v>11.83</v>
+        <v>7.63</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="J97" s="2"/>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D98" s="2">
         <v>16.899999999999999</v>
@@ -6194,115 +6195,115 @@
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="3" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="J98" s="2"/>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D99" s="2">
-        <v>11.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E99" s="2">
-        <v>8.33</v>
+        <v>11.83</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
       <c r="I99" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J99" s="2"/>
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D100" s="2">
-        <v>10.5</v>
+        <v>11.9</v>
       </c>
       <c r="E100" s="2">
-        <v>7.35</v>
+        <v>8.33</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="J100" s="2"/>
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>9</v>
+        <v>253</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D101" s="2">
-        <v>65</v>
+        <v>10.5</v>
       </c>
       <c r="E101" s="2">
-        <v>45.5</v>
+        <v>7.35</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J101" s="2"/>
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>253</v>
+        <v>9</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D102" s="2">
-        <v>8.9</v>
+        <v>65</v>
       </c>
       <c r="E102" s="2">
-        <v>6.23</v>
+        <v>45.5</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
       <c r="I102" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="J102" s="2"/>
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D103" s="2">
         <v>8.9</v>
@@ -6314,307 +6315,307 @@
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
       <c r="I103" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="J103" s="2"/>
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D104" s="2">
-        <v>6.9</v>
+        <v>8.9</v>
       </c>
       <c r="E104" s="2">
-        <v>4.83</v>
+        <v>6.23</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
       <c r="I104" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J104" s="2"/>
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D105" s="2">
-        <v>9.8000000000000007</v>
+        <v>6.9</v>
       </c>
       <c r="E105" s="2">
-        <v>6.86</v>
+        <v>4.83</v>
       </c>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="J105" s="2"/>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D106" s="2">
-        <v>8.9</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="E106" s="2">
-        <v>6.23</v>
+        <v>6.86</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
       <c r="I106" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="J106" s="2"/>
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D107" s="2">
-        <v>9.8000000000000007</v>
+        <v>8.9</v>
       </c>
       <c r="E107" s="2">
-        <v>6.86</v>
+        <v>6.23</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
       <c r="I107" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="J107" s="2"/>
     </row>
     <row r="108" spans="1:10">
       <c r="A108" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D108" s="2">
-        <v>11.9</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="E108" s="2">
-        <v>8.33</v>
+        <v>6.86</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
       <c r="I108" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J108" s="2"/>
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D109" s="2">
-        <v>8.6999999999999993</v>
+        <v>11.9</v>
       </c>
       <c r="E109" s="2">
-        <v>6.09</v>
+        <v>8.33</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
       <c r="I109" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="J109" s="2"/>
     </row>
     <row r="110" spans="1:10">
       <c r="A110" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>9</v>
+        <v>253</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D110" s="2">
-        <v>53</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="E110" s="2">
-        <v>37.1</v>
+        <v>6.09</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
       <c r="I110" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J110" s="2"/>
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>253</v>
+        <v>9</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D111" s="2">
-        <v>23.9</v>
+        <v>53</v>
       </c>
       <c r="E111" s="2">
-        <v>16.73</v>
+        <v>37.1</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
       <c r="I111" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="J111" s="2"/>
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D112" s="2">
-        <v>17.899999999999999</v>
+        <v>23.9</v>
       </c>
       <c r="E112" s="2">
-        <v>12.53</v>
+        <v>16.73</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
       <c r="I112" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J112" s="2"/>
     </row>
     <row r="113" spans="1:10">
       <c r="A113" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D113" s="2">
-        <v>21.9</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="E113" s="2">
-        <v>15.33</v>
+        <v>12.53</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
       <c r="I113" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J113" s="2"/>
     </row>
     <row r="114" spans="1:10">
       <c r="A114" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D114" s="2">
-        <v>8.9</v>
+        <v>21.9</v>
       </c>
       <c r="E114" s="2">
-        <v>6.23</v>
+        <v>15.33</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
       <c r="I114" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="J114" s="2"/>
     </row>
     <row r="115" spans="1:10">
       <c r="A115" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D115" s="2">
-        <v>16.899999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="E115" s="2">
-        <v>11.83</v>
+        <v>6.23</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
       <c r="I115" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="J115" s="2"/>
     </row>
     <row r="116" spans="1:10">
       <c r="A116" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D116" s="2">
         <v>16.899999999999999</v>
@@ -6626,67 +6627,67 @@
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
       <c r="I116" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="J116" s="2"/>
     </row>
     <row r="117" spans="1:10">
       <c r="A117" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>1098</v>
+        <v>335</v>
       </c>
       <c r="D117" s="2">
-        <v>37</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E117" s="2">
-        <v>25.9</v>
+        <v>11.83</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
       <c r="I117" s="3" t="s">
-        <v>1099</v>
+        <v>336</v>
       </c>
       <c r="J117" s="2"/>
     </row>
     <row r="118" spans="1:10">
       <c r="A118" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>339</v>
+        <v>1098</v>
       </c>
       <c r="D118" s="2">
-        <v>10.5</v>
+        <v>37</v>
       </c>
       <c r="E118" s="2">
-        <v>7.35</v>
+        <v>25.9</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
       <c r="I118" s="3" t="s">
-        <v>340</v>
+        <v>1099</v>
       </c>
       <c r="J118" s="2"/>
     </row>
     <row r="119" spans="1:10">
       <c r="A119" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D119" s="2">
         <v>10.5</v>
@@ -6698,91 +6699,91 @@
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
       <c r="I119" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="J119" s="2"/>
     </row>
     <row r="120" spans="1:10">
       <c r="A120" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D120" s="2">
-        <v>6.9</v>
+        <v>10.5</v>
       </c>
       <c r="E120" s="2">
-        <v>4.83</v>
+        <v>7.35</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
       <c r="I120" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="J120" s="2"/>
     </row>
     <row r="121" spans="1:10">
       <c r="A121" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>9</v>
+        <v>253</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D121" s="2">
-        <v>25</v>
+        <v>6.9</v>
       </c>
       <c r="E121" s="2">
-        <v>17.5</v>
+        <v>4.83</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
       <c r="I121" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="J121" s="2"/>
     </row>
     <row r="122" spans="1:10">
       <c r="A122" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>253</v>
+        <v>9</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D122" s="2">
-        <v>15.9</v>
+        <v>25</v>
       </c>
       <c r="E122" s="2">
-        <v>11.13</v>
+        <v>17.5</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
       <c r="I122" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="J122" s="2"/>
     </row>
     <row r="123" spans="1:10">
       <c r="A123" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D123" s="2">
         <v>15.9</v>
@@ -6794,19 +6795,19 @@
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
       <c r="I123" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J123" s="2"/>
     </row>
     <row r="124" spans="1:10">
       <c r="A124" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D124" s="2">
         <v>15.9</v>
@@ -6818,43 +6819,43 @@
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
       <c r="I124" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J124" s="2"/>
     </row>
     <row r="125" spans="1:10">
       <c r="A125" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D125" s="2">
-        <v>10.5</v>
+        <v>15.9</v>
       </c>
       <c r="E125" s="2">
-        <v>7.35</v>
+        <v>11.13</v>
       </c>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
       <c r="I125" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="J125" s="2"/>
     </row>
     <row r="126" spans="1:10">
       <c r="A126" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D126" s="2">
         <v>10.5</v>
@@ -6866,67 +6867,67 @@
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
       <c r="I126" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="J126" s="2"/>
     </row>
     <row r="127" spans="1:10">
       <c r="A127" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D127" s="2">
-        <v>11.9</v>
+        <v>10.5</v>
       </c>
       <c r="E127" s="2">
-        <v>8.33</v>
+        <v>7.35</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
       <c r="I127" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="J127" s="2"/>
     </row>
     <row r="128" spans="1:10">
       <c r="A128" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D128" s="2">
-        <v>6.5</v>
+        <v>11.9</v>
       </c>
       <c r="E128" s="2">
-        <v>4.55</v>
+        <v>8.33</v>
       </c>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
       <c r="I128" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="J128" s="2"/>
     </row>
     <row r="129" spans="1:10">
       <c r="A129" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D129" s="2">
         <v>6.5</v>
@@ -6938,67 +6939,67 @@
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
       <c r="I129" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="J129" s="2"/>
     </row>
     <row r="130" spans="1:10">
       <c r="A130" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D130" s="2">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="E130" s="2">
-        <v>3.99</v>
+        <v>4.55</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
       <c r="I130" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="J130" s="2"/>
     </row>
     <row r="131" spans="1:10">
       <c r="A131" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D131" s="2">
-        <v>8.9</v>
+        <v>5.7</v>
       </c>
       <c r="E131" s="2">
-        <v>6.23</v>
+        <v>3.99</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
       <c r="I131" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="J131" s="2"/>
     </row>
     <row r="132" spans="1:10">
       <c r="A132" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D132" s="2">
         <v>8.9</v>
@@ -7010,115 +7011,115 @@
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
       <c r="I132" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="J132" s="2"/>
     </row>
     <row r="133" spans="1:10">
       <c r="A133" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D133" s="2">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="E133" s="2">
-        <v>5.53</v>
+        <v>6.23</v>
       </c>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
       <c r="I133" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J133" s="2"/>
     </row>
     <row r="134" spans="1:10">
       <c r="A134" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D134" s="2">
-        <v>10.5</v>
+        <v>7.9</v>
       </c>
       <c r="E134" s="2">
-        <v>7.35</v>
+        <v>5.53</v>
       </c>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
       <c r="I134" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="J134" s="2"/>
     </row>
     <row r="135" spans="1:10">
       <c r="A135" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D135" s="2">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="E135" s="2">
-        <v>7.07</v>
+        <v>7.35</v>
       </c>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
       <c r="I135" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="J135" s="2"/>
     </row>
     <row r="136" spans="1:10">
       <c r="A136" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D136" s="2">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="E136" s="2">
-        <v>6.93</v>
+        <v>7.07</v>
       </c>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
       <c r="I136" s="3" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J136" s="2"/>
     </row>
     <row r="137" spans="1:10">
       <c r="A137" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D137" s="2">
         <v>9.9</v>
@@ -7130,43 +7131,43 @@
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
       <c r="I137" s="3" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="J137" s="2"/>
     </row>
     <row r="138" spans="1:10">
       <c r="A138" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D138" s="2">
-        <v>7.9</v>
+        <v>9.9</v>
       </c>
       <c r="E138" s="2">
-        <v>5.53</v>
+        <v>6.93</v>
       </c>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
       <c r="I138" s="3" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="J138" s="2"/>
     </row>
     <row r="139" spans="1:10">
       <c r="A139" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D139" s="2">
         <v>7.9</v>
@@ -7178,19 +7179,19 @@
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
       <c r="I139" s="3" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J139" s="2"/>
     </row>
     <row r="140" spans="1:10">
       <c r="A140" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D140" s="2">
         <v>7.9</v>
@@ -7202,307 +7203,307 @@
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
       <c r="I140" s="3" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="J140" s="2"/>
     </row>
     <row r="141" spans="1:10">
       <c r="A141" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D141" s="2">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="E141" s="2">
-        <v>6.23</v>
+        <v>5.53</v>
       </c>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
       <c r="I141" s="3" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="J141" s="2"/>
     </row>
     <row r="142" spans="1:10">
       <c r="A142" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D142" s="2">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="E142" s="2">
-        <v>5.53</v>
+        <v>6.23</v>
       </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
       <c r="I142" s="3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="J142" s="2"/>
     </row>
     <row r="143" spans="1:10">
       <c r="A143" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D143" s="2">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="E143" s="2">
-        <v>5.95</v>
+        <v>5.53</v>
       </c>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
       <c r="I143" s="3" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="J143" s="2"/>
     </row>
     <row r="144" spans="1:10">
       <c r="A144" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D144" s="2">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="E144" s="2">
-        <v>4.55</v>
+        <v>5.95</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
       <c r="I144" s="3" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="J144" s="2"/>
     </row>
     <row r="145" spans="1:10">
       <c r="A145" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D145" s="2">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="E145" s="2">
-        <v>5.46</v>
+        <v>4.55</v>
       </c>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
       <c r="I145" s="3" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="J145" s="2"/>
     </row>
     <row r="146" spans="1:10">
       <c r="A146" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D146" s="2">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="E146" s="2">
-        <v>4.83</v>
+        <v>5.46</v>
       </c>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
       <c r="I146" s="3" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J146" s="2"/>
     </row>
     <row r="147" spans="1:10">
       <c r="A147" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>426</v>
+        <v>253</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D147" s="2">
-        <v>4.9000000000000004</v>
+        <v>6.9</v>
       </c>
       <c r="E147" s="2">
-        <v>3.43</v>
+        <v>4.83</v>
       </c>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
       <c r="I147" s="3" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="J147" s="2"/>
     </row>
     <row r="148" spans="1:10">
       <c r="A148" s="2" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D148" s="2">
-        <v>7.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E148" s="2">
-        <v>5.53</v>
+        <v>3.43</v>
       </c>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
       <c r="I148" s="3" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="J148" s="2"/>
     </row>
     <row r="149" spans="1:10">
       <c r="A149" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>430</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D149" s="2">
-        <v>10.9</v>
+        <v>7.9</v>
       </c>
       <c r="E149" s="2">
-        <v>7.63</v>
+        <v>5.53</v>
       </c>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
       <c r="I149" s="3" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="J149" s="2"/>
     </row>
     <row r="150" spans="1:10">
       <c r="A150" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>430</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D150" s="2">
-        <v>2.9</v>
+        <v>10.9</v>
       </c>
       <c r="E150" s="2">
-        <v>2.0299999999999998</v>
+        <v>7.63</v>
       </c>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
       <c r="I150" s="3" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="J150" s="2"/>
     </row>
     <row r="151" spans="1:10">
       <c r="A151" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>430</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D151" s="2">
-        <v>10.9</v>
+        <v>2.9</v>
       </c>
       <c r="E151" s="2">
-        <v>7.63</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
       <c r="I151" s="3" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="J151" s="2"/>
     </row>
     <row r="152" spans="1:10">
       <c r="A152" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>207</v>
+        <v>430</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D152" s="2">
-        <v>4.5</v>
+        <v>10.9</v>
       </c>
       <c r="E152" s="2">
-        <v>3.15</v>
+        <v>7.63</v>
       </c>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
       <c r="I152" s="3" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="J152" s="2"/>
     </row>
     <row r="153" spans="1:10">
       <c r="A153" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D153" s="2">
         <v>4.5</v>
@@ -7514,115 +7515,115 @@
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
       <c r="I153" s="3" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="J153" s="2"/>
     </row>
     <row r="154" spans="1:10">
       <c r="A154" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D154" s="2">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="E154" s="2">
-        <v>3.36</v>
+        <v>3.15</v>
       </c>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
       <c r="I154" s="3" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="J154" s="2"/>
     </row>
     <row r="155" spans="1:10">
       <c r="A155" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D155" s="2">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="E155" s="2">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
       <c r="I155" s="3" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="J155" s="2"/>
     </row>
     <row r="156" spans="1:10">
       <c r="A156" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D156" s="2">
-        <v>7.9</v>
+        <v>4.5</v>
       </c>
       <c r="E156" s="2">
-        <v>5.53</v>
+        <v>3.15</v>
       </c>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
       <c r="I156" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="J156" s="2"/>
     </row>
     <row r="157" spans="1:10">
       <c r="A157" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D157" s="2">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="E157" s="2">
-        <v>4.55</v>
+        <v>5.53</v>
       </c>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
       <c r="I157" s="3" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="J157" s="2"/>
     </row>
     <row r="158" spans="1:10">
       <c r="A158" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D158" s="2">
         <v>6.5</v>
@@ -7634,235 +7635,235 @@
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
       <c r="I158" s="3" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="J158" s="2"/>
     </row>
     <row r="159" spans="1:10">
       <c r="A159" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D159" s="2">
-        <v>9.9</v>
+        <v>6.5</v>
       </c>
       <c r="E159" s="2">
-        <v>6.93</v>
+        <v>4.55</v>
       </c>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
       <c r="I159" s="3" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="J159" s="2"/>
     </row>
     <row r="160" spans="1:10">
       <c r="A160" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>9</v>
+        <v>207</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>1100</v>
+        <v>464</v>
       </c>
       <c r="D160" s="2">
-        <v>12.5</v>
+        <v>9.9</v>
       </c>
       <c r="E160" s="2">
-        <v>8.75</v>
+        <v>6.93</v>
       </c>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
       <c r="I160" s="3" t="s">
-        <v>1101</v>
+        <v>465</v>
       </c>
       <c r="J160" s="2"/>
     </row>
     <row r="161" spans="1:10">
       <c r="A161" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>207</v>
+        <v>9</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>468</v>
+        <v>1100</v>
       </c>
       <c r="D161" s="2">
-        <v>5.9</v>
+        <v>12.5</v>
       </c>
       <c r="E161" s="2">
-        <v>4.13</v>
+        <v>8.75</v>
       </c>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
       <c r="I161" s="3" t="s">
-        <v>469</v>
+        <v>1101</v>
       </c>
       <c r="J161" s="2"/>
     </row>
     <row r="162" spans="1:10">
       <c r="A162" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D162" s="2">
-        <v>8.9</v>
+        <v>5.9</v>
       </c>
       <c r="E162" s="2">
-        <v>6.23</v>
+        <v>4.13</v>
       </c>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
       <c r="I162" s="3" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="J162" s="2"/>
     </row>
     <row r="163" spans="1:10">
       <c r="A163" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D163" s="2">
-        <v>10.9</v>
+        <v>8.9</v>
       </c>
       <c r="E163" s="2">
-        <v>7.63</v>
+        <v>6.23</v>
       </c>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
       <c r="I163" s="3" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="J163" s="2"/>
     </row>
     <row r="164" spans="1:10">
       <c r="A164" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D164" s="2">
-        <v>6.9</v>
+        <v>10.9</v>
       </c>
       <c r="E164" s="2">
-        <v>4.83</v>
+        <v>7.63</v>
       </c>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
       <c r="I164" s="3" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="J164" s="2"/>
     </row>
     <row r="165" spans="1:10">
       <c r="A165" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D165" s="2">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
       <c r="E165" s="2">
-        <v>6.23</v>
+        <v>4.83</v>
       </c>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
       <c r="I165" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="J165" s="2"/>
     </row>
     <row r="166" spans="1:10">
       <c r="A166" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D166" s="2">
-        <v>11.3</v>
+        <v>8.9</v>
       </c>
       <c r="E166" s="2">
-        <v>7.91</v>
+        <v>6.23</v>
       </c>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
       <c r="I166" s="3" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J166" s="2"/>
     </row>
     <row r="167" spans="1:10">
       <c r="A167" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D167" s="2">
-        <v>7.5</v>
+        <v>11.3</v>
       </c>
       <c r="E167" s="2">
-        <v>5.25</v>
+        <v>7.91</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
       <c r="I167" s="3" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="J167" s="2"/>
     </row>
     <row r="168" spans="1:10">
       <c r="A168" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D168" s="2">
         <v>7.5</v>
@@ -7874,310 +7875,310 @@
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
       <c r="I168" s="3" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="J168" s="2"/>
     </row>
     <row r="169" spans="1:10">
       <c r="A169" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D169" s="2">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="E169" s="2">
-        <v>4.83</v>
+        <v>5.25</v>
       </c>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
       <c r="I169" s="3" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="J169" s="2"/>
     </row>
     <row r="170" spans="1:10">
       <c r="A170" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D170" s="2">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="E170" s="2">
-        <v>4.13</v>
+        <v>4.83</v>
       </c>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
       <c r="I170" s="3" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="J170" s="2"/>
     </row>
     <row r="171" spans="1:10">
       <c r="A171" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D171" s="2">
-        <v>7.5</v>
+        <v>5.9</v>
       </c>
       <c r="E171" s="2">
-        <v>5.25</v>
+        <v>4.13</v>
       </c>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
       <c r="I171" s="3" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="J171" s="2"/>
     </row>
     <row r="172" spans="1:10">
       <c r="A172" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D172" s="2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="E172" s="2">
-        <v>5.53</v>
+        <v>5.25</v>
       </c>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
       <c r="I172" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="J172" s="2"/>
     </row>
     <row r="173" spans="1:10">
       <c r="A173" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D173" s="2">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="E173" s="2">
-        <v>4.13</v>
+        <v>5.53</v>
       </c>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
       <c r="I173" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="J173" s="2"/>
     </row>
     <row r="174" spans="1:10">
       <c r="A174" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D174" s="2">
-        <v>12.9</v>
+        <v>5.9</v>
       </c>
       <c r="E174" s="2">
-        <v>9.0299999999999994</v>
+        <v>4.13</v>
       </c>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
       <c r="I174" s="3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="J174" s="2"/>
     </row>
     <row r="175" spans="1:10">
       <c r="A175" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D175" s="2">
-        <v>8.5</v>
+        <v>12.9</v>
       </c>
       <c r="E175" s="2">
-        <v>5.95</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
       <c r="I175" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J175" s="2"/>
     </row>
     <row r="176" spans="1:10">
       <c r="A176" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D176" s="2">
-        <v>4.9000000000000004</v>
+        <v>8.5</v>
       </c>
       <c r="E176" s="2">
-        <v>3.43</v>
+        <v>5.95</v>
       </c>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
       <c r="I176" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="J176" s="2"/>
     </row>
     <row r="177" spans="1:10">
       <c r="A177" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D177" s="2">
-        <v>5.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E177" s="2">
-        <v>4.13</v>
+        <v>3.43</v>
       </c>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
       <c r="I177" s="3" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="J177" s="2"/>
     </row>
     <row r="178" spans="1:10">
       <c r="A178" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D178" s="2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="E178" s="2">
-        <v>4.2</v>
+        <v>4.13</v>
       </c>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
       <c r="I178" s="3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="J178" s="2"/>
     </row>
     <row r="179" spans="1:10">
       <c r="A179" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D179" s="2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="E179" s="2">
-        <v>4.13</v>
+        <v>4.2</v>
       </c>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
       <c r="I179" s="3" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="J179" s="2"/>
     </row>
     <row r="180" spans="1:10">
       <c r="A180" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D180" s="2">
-        <v>10.9</v>
+        <v>5.9</v>
       </c>
       <c r="E180" s="2">
-        <v>7.63</v>
+        <v>4.13</v>
       </c>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
       <c r="I180" s="3" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="J180" s="2"/>
     </row>
     <row r="181" spans="1:10">
       <c r="A181" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D181" s="2">
-        <v>16.600000000000001</v>
+        <v>10.9</v>
       </c>
       <c r="E181" s="2">
         <v>7.63</v>
@@ -8186,307 +8187,307 @@
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
       <c r="I181" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J181" s="2"/>
     </row>
     <row r="182" spans="1:10">
       <c r="A182" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D182" s="2">
-        <v>12.9</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="E182" s="2">
-        <v>11.62</v>
+        <v>7.63</v>
       </c>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
       <c r="I182" s="3" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="J182" s="2"/>
     </row>
     <row r="183" spans="1:10">
       <c r="A183" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D183" s="2">
-        <v>6.9</v>
+        <v>12.9</v>
       </c>
       <c r="E183" s="2">
-        <v>4.83</v>
+        <v>11.62</v>
       </c>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
       <c r="I183" s="3" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="J183" s="2"/>
     </row>
     <row r="184" spans="1:10">
       <c r="A184" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D184" s="2">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="E184" s="2">
-        <v>5.53</v>
+        <v>4.83</v>
       </c>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
       <c r="I184" s="3" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="J184" s="2"/>
     </row>
     <row r="185" spans="1:10">
       <c r="A185" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D185" s="2">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="E185" s="2">
-        <v>4.83</v>
+        <v>5.53</v>
       </c>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
       <c r="I185" s="3" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J185" s="2"/>
     </row>
     <row r="186" spans="1:10">
       <c r="A186" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D186" s="2">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="E186" s="2">
-        <v>4.2</v>
+        <v>4.83</v>
       </c>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
       <c r="I186" s="3" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="J186" s="2"/>
     </row>
     <row r="187" spans="1:10">
       <c r="A187" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D187" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E187" s="2">
-        <v>4.9000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
       <c r="I187" s="3" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="J187" s="2"/>
     </row>
     <row r="188" spans="1:10">
       <c r="A188" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D188" s="2">
-        <v>8.9</v>
+        <v>7</v>
       </c>
       <c r="E188" s="2">
-        <v>6.23</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
       <c r="I188" s="3" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="J188" s="2"/>
     </row>
     <row r="189" spans="1:10">
       <c r="A189" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D189" s="2">
-        <v>11.9</v>
+        <v>8.9</v>
       </c>
       <c r="E189" s="2">
-        <v>8.33</v>
+        <v>6.23</v>
       </c>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
       <c r="I189" s="3" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="J189" s="2"/>
     </row>
     <row r="190" spans="1:10">
       <c r="A190" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D190" s="2">
-        <v>9.9</v>
+        <v>11.9</v>
       </c>
       <c r="E190" s="2">
-        <v>6.93</v>
+        <v>8.33</v>
       </c>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
       <c r="I190" s="3" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="J190" s="2"/>
     </row>
     <row r="191" spans="1:10">
       <c r="A191" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D191" s="2">
-        <v>8.9</v>
+        <v>9.9</v>
       </c>
       <c r="E191" s="2">
-        <v>6.23</v>
+        <v>6.93</v>
       </c>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
       <c r="I191" s="3" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="J191" s="2"/>
     </row>
     <row r="192" spans="1:10">
       <c r="A192" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D192" s="2">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="E192" s="2">
-        <v>6.93</v>
+        <v>6.23</v>
       </c>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
       <c r="I192" s="3" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J192" s="2"/>
     </row>
     <row r="193" spans="1:11">
       <c r="A193" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D193" s="2">
-        <v>4.5</v>
+        <v>9.9</v>
       </c>
       <c r="E193" s="2">
-        <v>3.15</v>
+        <v>6.93</v>
       </c>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
       <c r="I193" s="3" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="J193" s="2"/>
     </row>
     <row r="194" spans="1:11">
       <c r="A194" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D194" s="2">
         <v>4.5</v>
@@ -8498,43 +8499,43 @@
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="3" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="J194" s="2"/>
     </row>
     <row r="195" spans="1:11">
       <c r="A195" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D195" s="2">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="E195" s="2">
-        <v>4.55</v>
+        <v>3.15</v>
       </c>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
       <c r="I195" s="3" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="J195" s="2"/>
     </row>
     <row r="196" spans="1:11">
       <c r="A196" s="2" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D196" s="2">
         <v>6.5</v>
@@ -8546,19 +8547,19 @@
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
       <c r="I196" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="J196" s="2"/>
     </row>
     <row r="197" spans="1:11">
       <c r="A197" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D197" s="2">
         <v>6.5</v>
@@ -8570,43 +8571,43 @@
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
       <c r="I197" s="3" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="J197" s="2"/>
     </row>
     <row r="198" spans="1:11">
       <c r="A198" s="2" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="D198" s="2">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="E198" s="2">
-        <v>2.73</v>
+        <v>4.55</v>
       </c>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
       <c r="I198" s="3" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="J198" s="2"/>
     </row>
     <row r="199" spans="1:11">
       <c r="A199" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D199" s="2">
         <v>3.9</v>
@@ -8618,237 +8619,237 @@
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
       <c r="I199" s="3" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="J199" s="2"/>
     </row>
     <row r="200" spans="1:11">
       <c r="A200" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D200" s="2">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="E200" s="2">
-        <v>4.55</v>
+        <v>2.73</v>
       </c>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
-      <c r="I200" s="11" t="s">
-        <v>1125</v>
+      <c r="I200" s="3" t="s">
+        <v>583</v>
       </c>
       <c r="J200" s="2"/>
     </row>
     <row r="201" spans="1:11">
       <c r="A201" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D201" s="2">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="E201" s="2">
-        <v>4.13</v>
+        <v>4.55</v>
       </c>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
-      <c r="I201" s="3" t="s">
-        <v>588</v>
+      <c r="I201" s="11" t="s">
+        <v>1125</v>
       </c>
       <c r="J201" s="2"/>
     </row>
     <row r="202" spans="1:11">
       <c r="A202" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="D202" s="2">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="E202" s="2">
-        <v>3.85</v>
+        <v>4.13</v>
       </c>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
-      <c r="I202" s="11" t="s">
-        <v>1124</v>
+      <c r="I202" s="3" t="s">
+        <v>588</v>
       </c>
       <c r="J202" s="2"/>
     </row>
     <row r="203" spans="1:11">
       <c r="A203" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D203" s="2">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="E203" s="2">
-        <v>3.36</v>
+        <v>3.85</v>
       </c>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
-      <c r="I203" s="3" t="s">
-        <v>593</v>
+      <c r="I203" s="11" t="s">
+        <v>1124</v>
       </c>
       <c r="J203" s="2"/>
     </row>
     <row r="204" spans="1:11">
       <c r="A204" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D204" s="2">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="E204" s="2">
-        <v>4.83</v>
+        <v>3.36</v>
       </c>
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
       <c r="I204" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="J204" s="2"/>
+    </row>
+    <row r="205" spans="1:11">
+      <c r="A205" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D205" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="E205" s="2">
+        <v>4.83</v>
+      </c>
+      <c r="F205" s="2"/>
+      <c r="G205" s="2"/>
+      <c r="H205" s="2"/>
+      <c r="I205" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="J204" s="2"/>
-    </row>
-    <row r="205" spans="1:11">
-      <c r="A205" s="6" t="s">
+      <c r="J205" s="2"/>
+    </row>
+    <row r="206" spans="1:11">
+      <c r="A206" s="6" t="s">
         <v>597</v>
-      </c>
-      <c r="B205" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C205" s="6" t="s">
-        <v>598</v>
-      </c>
-      <c r="D205" s="6">
-        <v>6.9</v>
-      </c>
-      <c r="E205" s="6">
-        <v>4.83</v>
-      </c>
-      <c r="F205" s="6"/>
-      <c r="G205" s="6"/>
-      <c r="H205" s="6"/>
-      <c r="I205" s="7" t="s">
-        <v>599</v>
-      </c>
-      <c r="J205" s="8"/>
-      <c r="K205" s="9"/>
-    </row>
-    <row r="206" spans="1:11">
-      <c r="A206" s="5">
-        <v>70109</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>207</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D206" s="6">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="E206" s="6">
-        <v>7.63</v>
+        <v>4.83</v>
       </c>
       <c r="F206" s="6"/>
       <c r="G206" s="6"/>
       <c r="H206" s="6"/>
       <c r="I206" s="7" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="J206" s="8"/>
       <c r="K206" s="9"/>
     </row>
     <row r="207" spans="1:11">
-      <c r="A207" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="D207" s="2">
-        <v>5</v>
-      </c>
-      <c r="E207" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="F207" s="2"/>
-      <c r="G207" s="2"/>
-      <c r="H207" s="2"/>
-      <c r="I207" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="J207" s="2"/>
+      <c r="A207" s="5">
+        <v>70109</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C207" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="D207" s="6">
+        <v>10.9</v>
+      </c>
+      <c r="E207" s="6">
+        <v>7.63</v>
+      </c>
+      <c r="F207" s="6"/>
+      <c r="G207" s="6"/>
+      <c r="H207" s="6"/>
+      <c r="I207" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="J207" s="8"/>
+      <c r="K207" s="9"/>
     </row>
     <row r="208" spans="1:11">
       <c r="A208" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D208" s="2">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="E208" s="2">
-        <v>6.65</v>
+        <v>3.5</v>
       </c>
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
       <c r="I208" s="3" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="J208" s="2"/>
     </row>
     <row r="209" spans="1:10">
       <c r="A209" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>426</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D209" s="2">
         <v>9.5</v>
@@ -8860,43 +8861,43 @@
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
       <c r="I209" s="3" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="J209" s="2"/>
     </row>
     <row r="210" spans="1:10">
       <c r="A210" s="2" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>207</v>
+        <v>426</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D210" s="2">
-        <v>1.2</v>
+        <v>9.5</v>
       </c>
       <c r="E210" s="2">
-        <v>0.84</v>
+        <v>6.65</v>
       </c>
       <c r="F210" s="2"/>
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
       <c r="I210" s="3" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="J210" s="2"/>
     </row>
     <row r="211" spans="1:10">
       <c r="A211" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="D211" s="2">
         <v>1.2</v>
@@ -8908,19 +8909,19 @@
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
       <c r="I211" s="3" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="J211" s="2"/>
     </row>
     <row r="212" spans="1:10">
       <c r="A212" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D212" s="2">
         <v>1.2</v>
@@ -8932,19 +8933,19 @@
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
       <c r="I212" s="3" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="J212" s="2"/>
     </row>
     <row r="213" spans="1:10">
       <c r="A213" s="2" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D213" s="2">
         <v>1.2</v>
@@ -8956,89 +8957,89 @@
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
       <c r="I213" s="3" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="J213" s="2"/>
     </row>
     <row r="214" spans="1:10">
       <c r="A214" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>9</v>
+        <v>207</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D214" s="2">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="E214" s="2">
-        <v>3.15</v>
+        <v>0.84</v>
       </c>
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
       <c r="I214" s="3" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="J214" s="2"/>
     </row>
     <row r="215" spans="1:10">
-      <c r="A215" s="2">
-        <v>21710</v>
-      </c>
-      <c r="B215" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="C215" s="12" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D215" s="2"/>
+      <c r="A215" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D215" s="2">
+        <v>4.5</v>
+      </c>
       <c r="E215" s="2">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="F215" s="11"/>
+        <v>3.15</v>
+      </c>
+      <c r="F215" s="2"/>
       <c r="G215" s="2"/>
       <c r="H215" s="2"/>
-      <c r="I215" s="11" t="s">
-        <v>1122</v>
+      <c r="I215" s="3" t="s">
+        <v>625</v>
       </c>
       <c r="J215" s="2"/>
     </row>
     <row r="216" spans="1:10">
       <c r="A216" s="2">
-        <v>21709</v>
+        <v>21710</v>
       </c>
       <c r="B216" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="C216" s="2" t="s">
-        <v>1118</v>
-      </c>
-      <c r="D216" s="2">
-        <v>3.5</v>
-      </c>
+      <c r="C216" s="12" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D216" s="2"/>
       <c r="E216" s="2">
         <v>2.4500000000000002</v>
       </c>
-      <c r="F216" s="2"/>
+      <c r="F216" s="11"/>
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
-      <c r="I216" s="3" t="s">
-        <v>1121</v>
+      <c r="I216" s="11" t="s">
+        <v>1122</v>
       </c>
       <c r="J216" s="2"/>
     </row>
-    <row r="217" spans="1:10" ht="14.25" customHeight="1">
+    <row r="217" spans="1:10">
       <c r="A217" s="2">
-        <v>21708</v>
+        <v>21709</v>
       </c>
       <c r="B217" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="C217" s="16" t="s">
-        <v>1119</v>
+      <c r="C217" s="2" t="s">
+        <v>1118</v>
       </c>
       <c r="D217" s="2">
         <v>3.5</v>
@@ -9050,67 +9051,67 @@
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
       <c r="I217" s="3" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="J217" s="2"/>
     </row>
-    <row r="218" spans="1:10">
-      <c r="A218" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="B218" s="2" t="s">
+    <row r="218" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A218" s="2">
+        <v>21708</v>
+      </c>
+      <c r="B218" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="C218" s="2" t="s">
-        <v>627</v>
+      <c r="C218" s="16" t="s">
+        <v>1119</v>
       </c>
       <c r="D218" s="2">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="E218" s="2">
-        <v>1.05</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
       <c r="I218" s="3" t="s">
-        <v>628</v>
+        <v>1123</v>
       </c>
       <c r="J218" s="2"/>
     </row>
     <row r="219" spans="1:10">
       <c r="A219" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>630</v>
+        <v>207</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="D219" s="2">
-        <v>7.9</v>
+        <v>1.5</v>
       </c>
       <c r="E219" s="2">
-        <v>5.53</v>
+        <v>1.05</v>
       </c>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
       <c r="I219" s="3" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="J219" s="2"/>
     </row>
     <row r="220" spans="1:10">
       <c r="A220" s="2" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="D220" s="2">
         <v>7.9</v>
@@ -9122,19 +9123,19 @@
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
       <c r="I220" s="3" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="J220" s="2"/>
     </row>
     <row r="221" spans="1:10">
       <c r="A221" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="D221" s="2">
         <v>7.9</v>
@@ -9146,91 +9147,91 @@
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
       <c r="I221" s="3" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="J221" s="2"/>
     </row>
     <row r="222" spans="1:10">
       <c r="A222" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="D222" s="2">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="E222" s="2">
-        <v>4.83</v>
+        <v>5.53</v>
       </c>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
       <c r="I222" s="3" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="J222" s="2"/>
     </row>
     <row r="223" spans="1:10">
       <c r="A223" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D223" s="2">
-        <v>11.9</v>
+        <v>6.9</v>
       </c>
       <c r="E223" s="2">
-        <v>8.33</v>
+        <v>4.83</v>
       </c>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
       <c r="I223" s="3" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="J223" s="2"/>
     </row>
     <row r="224" spans="1:10">
       <c r="A224" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="D224" s="2">
-        <v>0.9</v>
+        <v>11.9</v>
       </c>
       <c r="E224" s="2">
-        <v>0.9</v>
+        <v>8.33</v>
       </c>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
       <c r="I224" s="3" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="J224" s="2"/>
     </row>
     <row r="225" spans="1:13">
       <c r="A225" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D225" s="2">
         <v>0.9</v>
@@ -9242,43 +9243,43 @@
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
       <c r="I225" s="3" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="J225" s="2"/>
     </row>
     <row r="226" spans="1:13">
       <c r="A226" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D226" s="2">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="E226" s="2">
-        <v>4.83</v>
+        <v>0.9</v>
       </c>
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
       <c r="I226" s="3" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="J226" s="2"/>
     </row>
     <row r="227" spans="1:13">
       <c r="A227" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="D227" s="2">
         <v>6.9</v>
@@ -9290,139 +9291,139 @@
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
       <c r="I227" s="3" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="J227" s="2"/>
     </row>
     <row r="228" spans="1:13">
       <c r="A228" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D228" s="2">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="E228" s="2">
-        <v>7.63</v>
+        <v>4.83</v>
       </c>
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
       <c r="I228" s="3" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="J228" s="2"/>
     </row>
     <row r="229" spans="1:13">
       <c r="A229" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="D229" s="2">
-        <v>7.9</v>
+        <v>10.9</v>
       </c>
       <c r="E229" s="2">
-        <v>5.53</v>
+        <v>7.63</v>
       </c>
       <c r="F229" s="2"/>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
       <c r="I229" s="3" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="J229" s="2"/>
     </row>
     <row r="230" spans="1:13">
       <c r="A230" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="D230" s="2">
-        <v>10.9</v>
+        <v>7.9</v>
       </c>
       <c r="E230" s="2">
-        <v>7.63</v>
+        <v>5.53</v>
       </c>
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
       <c r="I230" s="3" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="J230" s="2"/>
     </row>
     <row r="231" spans="1:13">
       <c r="A231" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="D231" s="2">
-        <v>1</v>
+        <v>10.9</v>
       </c>
       <c r="E231" s="2">
-        <v>1</v>
+        <v>7.63</v>
       </c>
       <c r="F231" s="2"/>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
       <c r="I231" s="3" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="J231" s="2"/>
     </row>
     <row r="232" spans="1:13">
       <c r="A232" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D232" s="2">
-        <v>16.899999999999999</v>
+        <v>1</v>
       </c>
       <c r="E232" s="2">
-        <v>11.83</v>
+        <v>1</v>
       </c>
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
       <c r="I232" s="3" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="J232" s="2"/>
     </row>
     <row r="233" spans="1:13">
       <c r="A233" s="2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D233" s="2">
         <v>16.899999999999999</v>
@@ -9434,118 +9435,118 @@
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
       <c r="I233" s="3" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="J233" s="2"/>
     </row>
     <row r="234" spans="1:13">
       <c r="A234" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D234" s="2">
-        <v>1</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E234" s="2">
-        <v>1</v>
+        <v>11.83</v>
       </c>
       <c r="F234" s="2"/>
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
       <c r="I234" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="J234" s="2"/>
+    </row>
+    <row r="235" spans="1:13">
+      <c r="A235" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="D235" s="2">
+        <v>1</v>
+      </c>
+      <c r="E235" s="2">
+        <v>1</v>
+      </c>
+      <c r="F235" s="2"/>
+      <c r="G235" s="2"/>
+      <c r="H235" s="2"/>
+      <c r="I235" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="J234" s="2"/>
-    </row>
-    <row r="235" spans="1:13">
-      <c r="A235" s="5">
+      <c r="J235" s="2"/>
+    </row>
+    <row r="236" spans="1:13">
+      <c r="A236" s="5">
         <v>30802</v>
       </c>
-      <c r="B235" s="6" t="s">
+      <c r="B236" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="C235" s="6" t="s">
+      <c r="C236" s="6" t="s">
         <v>678</v>
       </c>
-      <c r="D235" s="6">
+      <c r="D236" s="6">
         <v>7.9</v>
       </c>
-      <c r="E235" s="6">
+      <c r="E236" s="6">
         <v>5.53</v>
       </c>
-      <c r="F235" s="6"/>
-      <c r="G235" s="6"/>
-      <c r="H235" s="6"/>
-      <c r="I235" s="7" t="s">
+      <c r="F236" s="6"/>
+      <c r="G236" s="6"/>
+      <c r="H236" s="6"/>
+      <c r="I236" s="7" t="s">
         <v>679</v>
       </c>
-      <c r="J235" s="8"/>
-      <c r="K235" s="9"/>
-      <c r="L235" s="9"/>
-      <c r="M235" s="9"/>
-    </row>
-    <row r="236" spans="1:13">
-      <c r="A236" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="D236" s="2">
-        <v>7.9</v>
-      </c>
-      <c r="E236" s="2">
-        <v>5.53</v>
-      </c>
-      <c r="F236" s="2"/>
-      <c r="G236" s="2"/>
-      <c r="H236" s="2"/>
-      <c r="I236" s="3" t="s">
-        <v>682</v>
-      </c>
-      <c r="J236" s="2"/>
+      <c r="J236" s="8"/>
+      <c r="K236" s="9"/>
+      <c r="L236" s="9"/>
+      <c r="M236" s="9"/>
     </row>
     <row r="237" spans="1:13">
       <c r="A237" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="D237" s="2">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
       <c r="E237" s="2">
-        <v>6.65</v>
+        <v>5.53</v>
       </c>
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
       <c r="I237" s="3" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="J237" s="2"/>
     </row>
     <row r="238" spans="1:13">
       <c r="A238" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="D238" s="2">
         <v>9.5</v>
@@ -9557,19 +9558,19 @@
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
       <c r="I238" s="3" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="J238" s="2"/>
     </row>
     <row r="239" spans="1:13">
       <c r="A239" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D239" s="2">
         <v>9.5</v>
@@ -9581,67 +9582,67 @@
       <c r="G239" s="2"/>
       <c r="H239" s="2"/>
       <c r="I239" s="3" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="J239" s="2"/>
     </row>
     <row r="240" spans="1:13">
       <c r="A240" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="D240" s="2">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="E240" s="2">
-        <v>6.23</v>
+        <v>6.65</v>
       </c>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
       <c r="H240" s="2"/>
       <c r="I240" s="3" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="J240" s="2"/>
     </row>
     <row r="241" spans="1:10">
       <c r="A241" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D241" s="2">
-        <v>0.9</v>
+        <v>8.9</v>
       </c>
       <c r="E241" s="2">
-        <v>0.9</v>
+        <v>6.23</v>
       </c>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
       <c r="I241" s="3" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="J241" s="2"/>
     </row>
     <row r="242" spans="1:10">
       <c r="A242" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D242" s="2">
         <v>0.9</v>
@@ -9653,259 +9654,259 @@
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
       <c r="I242" s="3" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="J242" s="2"/>
     </row>
     <row r="243" spans="1:10">
       <c r="A243" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="D243" s="2">
-        <v>5.9</v>
+        <v>0.9</v>
       </c>
       <c r="E243" s="2">
-        <v>4.13</v>
+        <v>0.9</v>
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
       <c r="I243" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="J243" s="2"/>
     </row>
     <row r="244" spans="1:10">
       <c r="A244" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="D244" s="2">
-        <v>7.9</v>
+        <v>5.9</v>
       </c>
       <c r="E244" s="2">
-        <v>5.53</v>
+        <v>4.13</v>
       </c>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
       <c r="H244" s="2"/>
       <c r="I244" s="3" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="J244" s="2"/>
     </row>
     <row r="245" spans="1:10">
       <c r="A245" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D245" s="2">
-        <v>9.9</v>
+        <v>7.9</v>
       </c>
       <c r="E245" s="2">
-        <v>6.93</v>
+        <v>5.53</v>
       </c>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
       <c r="I245" s="3" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="J245" s="2"/>
     </row>
     <row r="246" spans="1:10">
       <c r="A246" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D246" s="2">
-        <v>8.6999999999999993</v>
+        <v>9.9</v>
       </c>
       <c r="E246" s="2">
-        <v>6.09</v>
+        <v>6.93</v>
       </c>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
       <c r="I246" s="3" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="J246" s="2"/>
     </row>
     <row r="247" spans="1:10">
       <c r="A247" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D247" s="2">
-        <v>5.9</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="E247" s="2">
-        <v>4.13</v>
+        <v>6.09</v>
       </c>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
       <c r="I247" s="3" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="J247" s="2"/>
     </row>
     <row r="248" spans="1:10">
       <c r="A248" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D248" s="2">
-        <v>10.5</v>
+        <v>5.9</v>
       </c>
       <c r="E248" s="2">
-        <v>7.35</v>
+        <v>4.13</v>
       </c>
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
       <c r="H248" s="2"/>
       <c r="I248" s="3" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="J248" s="2"/>
     </row>
     <row r="249" spans="1:10">
       <c r="A249" s="2" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D249" s="2">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="E249" s="2">
-        <v>4.13</v>
+        <v>7.35</v>
       </c>
       <c r="F249" s="2"/>
       <c r="G249" s="2"/>
       <c r="H249" s="2"/>
       <c r="I249" s="3" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="J249" s="2"/>
     </row>
     <row r="250" spans="1:10">
       <c r="A250" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D250" s="2">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="E250" s="2">
-        <v>4.55</v>
+        <v>4.13</v>
       </c>
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
       <c r="I250" s="3" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="J250" s="2"/>
     </row>
     <row r="251" spans="1:10">
       <c r="A251" s="2" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D251" s="2">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="E251" s="2">
-        <v>5.53</v>
+        <v>4.55</v>
       </c>
       <c r="F251" s="2"/>
       <c r="G251" s="2"/>
       <c r="H251" s="2"/>
       <c r="I251" s="3" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="J251" s="2"/>
     </row>
     <row r="252" spans="1:10">
       <c r="A252" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="D252" s="2">
-        <v>9.6</v>
+        <v>7.9</v>
       </c>
       <c r="E252" s="2">
-        <v>6.72</v>
+        <v>5.53</v>
       </c>
       <c r="F252" s="2"/>
       <c r="G252" s="2"/>
       <c r="H252" s="2"/>
       <c r="I252" s="3" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="J252" s="2"/>
     </row>
     <row r="253" spans="1:10">
       <c r="A253" s="2" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D253" s="2">
         <v>9.6</v>
@@ -9917,211 +9918,211 @@
       <c r="G253" s="2"/>
       <c r="H253" s="2"/>
       <c r="I253" s="3" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="J253" s="2"/>
     </row>
     <row r="254" spans="1:10">
       <c r="A254" s="2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D254" s="2">
-        <v>10.1</v>
+        <v>9.6</v>
       </c>
       <c r="E254" s="2">
-        <v>7.07</v>
+        <v>6.72</v>
       </c>
       <c r="F254" s="2"/>
       <c r="G254" s="2"/>
       <c r="H254" s="2"/>
       <c r="I254" s="3" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="J254" s="2"/>
     </row>
     <row r="255" spans="1:10">
       <c r="A255" s="2" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D255" s="2">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="E255" s="2">
-        <v>7.63</v>
+        <v>7.07</v>
       </c>
       <c r="F255" s="2"/>
       <c r="G255" s="2"/>
       <c r="H255" s="2"/>
       <c r="I255" s="3" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="J255" s="2"/>
     </row>
     <row r="256" spans="1:10">
       <c r="A256" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="D256" s="2">
-        <v>9.6</v>
+        <v>10.9</v>
       </c>
       <c r="E256" s="2">
-        <v>6.72</v>
+        <v>7.63</v>
       </c>
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
       <c r="I256" s="3" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="J256" s="2"/>
     </row>
     <row r="257" spans="1:11">
       <c r="A257" s="2" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D257" s="2">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="E257" s="2">
-        <v>4.13</v>
+        <v>6.72</v>
       </c>
       <c r="F257" s="2"/>
       <c r="G257" s="2"/>
       <c r="H257" s="2"/>
       <c r="I257" s="3" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="J257" s="2"/>
     </row>
     <row r="258" spans="1:11">
       <c r="A258" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>430</v>
+        <v>630</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D258" s="2">
-        <v>8.9</v>
+        <v>5.9</v>
       </c>
       <c r="E258" s="2">
-        <v>6.23</v>
+        <v>4.13</v>
       </c>
       <c r="F258" s="2"/>
       <c r="G258" s="2"/>
       <c r="H258" s="2"/>
       <c r="I258" s="3" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="J258" s="2"/>
     </row>
     <row r="259" spans="1:11">
       <c r="A259" s="2" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D259" s="2">
-        <v>4.9000000000000004</v>
+        <v>8.9</v>
       </c>
       <c r="E259" s="2">
-        <v>3.43</v>
+        <v>6.23</v>
       </c>
       <c r="F259" s="2"/>
       <c r="G259" s="2"/>
       <c r="H259" s="2"/>
       <c r="I259" s="3" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="J259" s="2"/>
     </row>
     <row r="260" spans="1:11">
       <c r="A260" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="D260" s="2">
-        <v>10.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E260" s="2">
-        <v>7.63</v>
+        <v>3.43</v>
       </c>
       <c r="F260" s="2"/>
       <c r="G260" s="2"/>
       <c r="H260" s="2"/>
       <c r="I260" s="3" t="s">
-        <v>601</v>
+        <v>751</v>
       </c>
       <c r="J260" s="2"/>
     </row>
     <row r="261" spans="1:11">
       <c r="A261" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>754</v>
+        <v>430</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>755</v>
+        <v>600</v>
       </c>
       <c r="D261" s="2">
-        <v>18.5</v>
+        <v>10.9</v>
       </c>
       <c r="E261" s="2">
-        <v>12.95</v>
+        <v>7.63</v>
       </c>
       <c r="F261" s="2"/>
       <c r="G261" s="2"/>
       <c r="H261" s="2"/>
       <c r="I261" s="3" t="s">
-        <v>756</v>
+        <v>601</v>
       </c>
       <c r="J261" s="2"/>
     </row>
     <row r="262" spans="1:11">
       <c r="A262" s="2" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D262" s="2">
         <v>18.5</v>
@@ -10133,19 +10134,19 @@
       <c r="G262" s="2"/>
       <c r="H262" s="2"/>
       <c r="I262" s="3" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="J262" s="2"/>
     </row>
     <row r="263" spans="1:11">
       <c r="A263" s="2" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="D263" s="2">
         <v>18.5</v>
@@ -10157,19 +10158,19 @@
       <c r="G263" s="2"/>
       <c r="H263" s="2"/>
       <c r="I263" s="3" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="J263" s="2"/>
     </row>
     <row r="264" spans="1:11">
       <c r="A264" s="2" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D264" s="2">
         <v>18.5</v>
@@ -10181,19 +10182,19 @@
       <c r="G264" s="2"/>
       <c r="H264" s="2"/>
       <c r="I264" s="3" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="J264" s="2"/>
     </row>
     <row r="265" spans="1:11">
       <c r="A265" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="D265" s="2">
         <v>18.5</v>
@@ -10205,19 +10206,19 @@
       <c r="G265" s="2"/>
       <c r="H265" s="2"/>
       <c r="I265" s="3" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="J265" s="2"/>
     </row>
     <row r="266" spans="1:11">
       <c r="A266" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="D266" s="2">
         <v>18.5</v>
@@ -10229,116 +10230,116 @@
       <c r="G266" s="2"/>
       <c r="H266" s="2"/>
       <c r="I266" s="3" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="J266" s="2"/>
     </row>
     <row r="267" spans="1:11">
       <c r="A267" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="D267" s="2">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="E267" s="2">
-        <v>13.65</v>
+        <v>12.95</v>
       </c>
       <c r="F267" s="2"/>
       <c r="G267" s="2"/>
       <c r="H267" s="2"/>
       <c r="I267" s="3" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="J267" s="2"/>
     </row>
     <row r="268" spans="1:11">
       <c r="A268" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="D268" s="2">
-        <v>22.5</v>
+        <v>19.5</v>
       </c>
       <c r="E268" s="2">
-        <v>15.75</v>
+        <v>13.65</v>
       </c>
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
       <c r="H268" s="2"/>
       <c r="I268" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="J268" s="2"/>
+    </row>
+    <row r="269" spans="1:11">
+      <c r="A269" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="D269" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="E269" s="2">
+        <v>15.75</v>
+      </c>
+      <c r="F269" s="2"/>
+      <c r="G269" s="2"/>
+      <c r="H269" s="2"/>
+      <c r="I269" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="J268" s="2"/>
-    </row>
-    <row r="269" spans="1:11">
-      <c r="A269" s="5">
+      <c r="J269" s="2"/>
+    </row>
+    <row r="270" spans="1:11">
+      <c r="A270" s="5">
         <v>80305</v>
       </c>
-      <c r="B269" s="6" t="s">
+      <c r="B270" s="6" t="s">
         <v>781</v>
       </c>
-      <c r="C269" s="6" t="s">
+      <c r="C270" s="6" t="s">
         <v>778</v>
       </c>
-      <c r="D269" s="6">
+      <c r="D270" s="6">
         <v>6.9</v>
       </c>
-      <c r="E269" s="6">
+      <c r="E270" s="6">
         <v>4.83</v>
       </c>
-      <c r="F269" s="6"/>
-      <c r="G269" s="6"/>
-      <c r="H269" s="6"/>
-      <c r="I269" s="7" t="s">
+      <c r="F270" s="6"/>
+      <c r="G270" s="6"/>
+      <c r="H270" s="6"/>
+      <c r="I270" s="7" t="s">
         <v>779</v>
       </c>
-      <c r="J269" s="8"/>
-      <c r="K269" s="9"/>
-    </row>
-    <row r="270" spans="1:11">
-      <c r="A270" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="D270" s="2">
-        <v>5.9</v>
-      </c>
-      <c r="E270" s="2">
-        <v>4.13</v>
-      </c>
-      <c r="F270" s="2"/>
-      <c r="G270" s="2"/>
-      <c r="H270" s="2"/>
-      <c r="I270" s="11" t="s">
-        <v>1117</v>
-      </c>
-      <c r="J270" s="2"/>
+      <c r="J270" s="8"/>
+      <c r="K270" s="9"/>
     </row>
     <row r="271" spans="1:11">
       <c r="A271" s="2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D271" s="2">
         <v>5.9</v>
@@ -10349,44 +10350,44 @@
       <c r="F271" s="2"/>
       <c r="G271" s="2"/>
       <c r="H271" s="2"/>
-      <c r="I271" s="3" t="s">
-        <v>785</v>
+      <c r="I271" s="11" t="s">
+        <v>1117</v>
       </c>
       <c r="J271" s="2"/>
     </row>
     <row r="272" spans="1:11">
       <c r="A272" s="2" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="D272" s="2">
-        <v>15.9</v>
+        <v>5.9</v>
       </c>
       <c r="E272" s="2">
-        <v>11.13</v>
+        <v>4.13</v>
       </c>
       <c r="F272" s="2"/>
       <c r="G272" s="2"/>
       <c r="H272" s="2"/>
       <c r="I272" s="3" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="J272" s="2"/>
     </row>
     <row r="273" spans="1:10">
       <c r="A273" s="2" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D273" s="2">
         <v>15.9</v>
@@ -10398,115 +10399,115 @@
       <c r="G273" s="2"/>
       <c r="H273" s="2"/>
       <c r="I273" s="3" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="J273" s="2"/>
     </row>
     <row r="274" spans="1:10">
       <c r="A274" s="2" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D274" s="2">
-        <v>4.9000000000000004</v>
+        <v>15.9</v>
       </c>
       <c r="E274" s="2">
-        <v>3.43</v>
+        <v>11.13</v>
       </c>
       <c r="F274" s="2"/>
       <c r="G274" s="2"/>
       <c r="H274" s="2"/>
       <c r="I274" s="3" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="J274" s="2"/>
     </row>
     <row r="275" spans="1:10">
       <c r="A275" s="2" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D275" s="2">
-        <v>6.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E275" s="2">
-        <v>4.55</v>
+        <v>3.43</v>
       </c>
       <c r="F275" s="2"/>
       <c r="G275" s="2"/>
       <c r="H275" s="2"/>
       <c r="I275" s="3" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="J275" s="2"/>
     </row>
     <row r="276" spans="1:10">
       <c r="A276" s="2" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="D276" s="2">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="E276" s="2">
-        <v>4.13</v>
+        <v>4.55</v>
       </c>
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
       <c r="H276" s="2"/>
       <c r="I276" s="3" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="J276" s="2"/>
     </row>
     <row r="277" spans="1:10">
       <c r="A277" s="2" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="D277" s="2">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="E277" s="2">
-        <v>4.55</v>
+        <v>4.13</v>
       </c>
       <c r="F277" s="2"/>
       <c r="G277" s="2"/>
       <c r="H277" s="2"/>
       <c r="I277" s="3" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="J277" s="2"/>
     </row>
     <row r="278" spans="1:10">
       <c r="A278" s="2" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="D278" s="2">
         <v>6.5</v>
@@ -10518,43 +10519,43 @@
       <c r="G278" s="2"/>
       <c r="H278" s="2"/>
       <c r="I278" s="3" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="J278" s="2"/>
     </row>
     <row r="279" spans="1:10">
       <c r="A279" s="2" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D279" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="E279" s="2">
-        <v>4.83</v>
+        <v>4.55</v>
       </c>
       <c r="F279" s="2"/>
       <c r="G279" s="2"/>
       <c r="H279" s="2"/>
       <c r="I279" s="3" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="J279" s="2"/>
     </row>
     <row r="280" spans="1:10">
       <c r="A280" s="2" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="D280" s="2">
         <v>6.9</v>
@@ -10566,451 +10567,451 @@
       <c r="G280" s="2"/>
       <c r="H280" s="2"/>
       <c r="I280" s="3" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="J280" s="2"/>
     </row>
     <row r="281" spans="1:10">
       <c r="A281" s="2" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="D281" s="2">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="E281" s="2">
-        <v>5.53</v>
+        <v>4.83</v>
       </c>
       <c r="F281" s="2"/>
       <c r="G281" s="2"/>
       <c r="H281" s="2"/>
       <c r="I281" s="3" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="J281" s="2"/>
     </row>
     <row r="282" spans="1:10">
       <c r="A282" s="2" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D282" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="E282" s="2">
-        <v>5.25</v>
+        <v>5.53</v>
       </c>
       <c r="F282" s="2"/>
       <c r="G282" s="2"/>
       <c r="H282" s="2"/>
       <c r="I282" s="3" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="J282" s="2"/>
     </row>
     <row r="283" spans="1:10">
       <c r="A283" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="D283" s="2">
-        <v>4.9000000000000004</v>
+        <v>7.5</v>
       </c>
       <c r="E283" s="2">
-        <v>3.43</v>
+        <v>5.25</v>
       </c>
       <c r="F283" s="2"/>
       <c r="G283" s="2"/>
       <c r="H283" s="2"/>
       <c r="I283" s="3" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="J283" s="2"/>
     </row>
     <row r="284" spans="1:10">
       <c r="A284" s="2" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="D284" s="2">
-        <v>6.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E284" s="2">
-        <v>4.83</v>
+        <v>3.43</v>
       </c>
       <c r="F284" s="2"/>
       <c r="G284" s="2"/>
       <c r="H284" s="2"/>
       <c r="I284" s="3" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="J284" s="2"/>
     </row>
     <row r="285" spans="1:10">
       <c r="A285" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="D285" s="2">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="E285" s="2">
-        <v>5.53</v>
+        <v>4.83</v>
       </c>
       <c r="F285" s="2"/>
       <c r="G285" s="2"/>
       <c r="H285" s="2"/>
       <c r="I285" s="3" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="J285" s="2"/>
     </row>
     <row r="286" spans="1:10">
       <c r="A286" s="2" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="D286" s="2">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="E286" s="2">
-        <v>4.83</v>
+        <v>5.53</v>
       </c>
       <c r="F286" s="2"/>
       <c r="G286" s="2"/>
       <c r="H286" s="2"/>
       <c r="I286" s="3" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="J286" s="2"/>
     </row>
     <row r="287" spans="1:10">
       <c r="A287" s="2" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="D287" s="2">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="E287" s="2">
-        <v>5.25</v>
+        <v>4.83</v>
       </c>
       <c r="F287" s="2"/>
       <c r="G287" s="2"/>
       <c r="H287" s="2"/>
       <c r="I287" s="3" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="J287" s="2"/>
     </row>
     <row r="288" spans="1:10">
       <c r="A288" s="2" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="D288" s="2">
-        <v>5.9</v>
+        <v>7.5</v>
       </c>
       <c r="E288" s="2">
-        <v>4.13</v>
+        <v>5.25</v>
       </c>
       <c r="F288" s="2"/>
       <c r="G288" s="2"/>
       <c r="H288" s="2"/>
       <c r="I288" s="3" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="J288" s="2"/>
     </row>
     <row r="289" spans="1:10">
       <c r="A289" s="2" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="D289" s="2">
-        <v>4.9000000000000004</v>
+        <v>5.9</v>
       </c>
       <c r="E289" s="2">
-        <v>3.43</v>
+        <v>4.13</v>
       </c>
       <c r="F289" s="2"/>
       <c r="G289" s="2"/>
       <c r="H289" s="2"/>
       <c r="I289" s="3" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="J289" s="2"/>
     </row>
     <row r="290" spans="1:10">
       <c r="A290" s="2" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="D290" s="2">
-        <v>8.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E290" s="2">
-        <v>5.95</v>
+        <v>3.43</v>
       </c>
       <c r="F290" s="2"/>
       <c r="G290" s="2"/>
       <c r="H290" s="2"/>
       <c r="I290" s="3" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="J290" s="2"/>
     </row>
     <row r="291" spans="1:10">
       <c r="A291" s="2" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="D291" s="2">
-        <v>6.9</v>
+        <v>8.5</v>
       </c>
       <c r="E291" s="2">
-        <v>4.83</v>
+        <v>5.95</v>
       </c>
       <c r="F291" s="2"/>
       <c r="G291" s="2"/>
       <c r="H291" s="2"/>
       <c r="I291" s="3" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="J291" s="2"/>
     </row>
     <row r="292" spans="1:10">
       <c r="A292" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="D292" s="2">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="E292" s="2">
-        <v>4.55</v>
+        <v>4.83</v>
       </c>
       <c r="F292" s="2"/>
       <c r="G292" s="2"/>
       <c r="H292" s="2"/>
       <c r="I292" s="3" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="J292" s="2"/>
     </row>
     <row r="293" spans="1:10">
       <c r="A293" s="2" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D293" s="2">
-        <v>10.9</v>
+        <v>6.5</v>
       </c>
       <c r="E293" s="2">
-        <v>7.63</v>
+        <v>4.55</v>
       </c>
       <c r="F293" s="2"/>
       <c r="G293" s="2"/>
       <c r="H293" s="2"/>
       <c r="I293" s="3" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="J293" s="2"/>
     </row>
     <row r="294" spans="1:10">
       <c r="A294" s="2" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="D294" s="2">
-        <v>6.9</v>
+        <v>10.9</v>
       </c>
       <c r="E294" s="2">
-        <v>4.83</v>
+        <v>7.63</v>
       </c>
       <c r="F294" s="2"/>
       <c r="G294" s="2"/>
       <c r="H294" s="2"/>
       <c r="I294" s="3" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="J294" s="2"/>
     </row>
     <row r="295" spans="1:10">
       <c r="A295" s="2" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="D295" s="2">
-        <v>11.9</v>
+        <v>6.9</v>
       </c>
       <c r="E295" s="2">
-        <v>8.33</v>
+        <v>4.83</v>
       </c>
       <c r="F295" s="2"/>
       <c r="G295" s="2"/>
       <c r="H295" s="2"/>
       <c r="I295" s="3" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="J295" s="2"/>
     </row>
     <row r="296" spans="1:10">
       <c r="A296" s="2" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="D296" s="2">
-        <v>6.9</v>
+        <v>11.9</v>
       </c>
       <c r="E296" s="2">
-        <v>4.83</v>
+        <v>8.33</v>
       </c>
       <c r="F296" s="2"/>
       <c r="G296" s="2"/>
       <c r="H296" s="2"/>
       <c r="I296" s="3" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="J296" s="2"/>
     </row>
     <row r="297" spans="1:10">
       <c r="A297" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="D297" s="2">
-        <v>11.9</v>
+        <v>6.9</v>
       </c>
       <c r="E297" s="2">
-        <v>8.33</v>
+        <v>4.83</v>
       </c>
       <c r="F297" s="2"/>
       <c r="G297" s="2"/>
       <c r="H297" s="2"/>
       <c r="I297" s="3" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="J297" s="2"/>
     </row>
     <row r="298" spans="1:10">
       <c r="A298" s="2" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="D298" s="2">
-        <v>6.9</v>
+        <v>11.9</v>
       </c>
       <c r="E298" s="2">
-        <v>4.83</v>
+        <v>8.33</v>
       </c>
       <c r="F298" s="2"/>
       <c r="G298" s="2"/>
       <c r="H298" s="2"/>
       <c r="I298" s="3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="J298" s="2"/>
     </row>
     <row r="299" spans="1:10">
       <c r="A299" s="2" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="D299" s="2">
         <v>6.9</v>
@@ -11022,43 +11023,43 @@
       <c r="G299" s="2"/>
       <c r="H299" s="2"/>
       <c r="I299" s="3" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="J299" s="2"/>
     </row>
     <row r="300" spans="1:10">
       <c r="A300" s="2" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="D300" s="2">
-        <v>11.9</v>
+        <v>6.9</v>
       </c>
       <c r="E300" s="2">
-        <v>8.33</v>
+        <v>4.83</v>
       </c>
       <c r="F300" s="2"/>
       <c r="G300" s="2"/>
       <c r="H300" s="2"/>
       <c r="I300" s="3" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="J300" s="2"/>
     </row>
     <row r="301" spans="1:10">
       <c r="A301" s="2" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="D301" s="2">
         <v>11.9</v>
@@ -11070,19 +11071,19 @@
       <c r="G301" s="2"/>
       <c r="H301" s="2"/>
       <c r="I301" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="J301" s="2"/>
     </row>
     <row r="302" spans="1:10">
       <c r="A302" s="2" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="D302" s="2">
         <v>11.9</v>
@@ -11094,19 +11095,19 @@
       <c r="G302" s="2"/>
       <c r="H302" s="2"/>
       <c r="I302" s="3" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="J302" s="2"/>
     </row>
     <row r="303" spans="1:10">
       <c r="A303" s="2" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="D303" s="2">
         <v>11.9</v>
@@ -11118,233 +11119,233 @@
       <c r="G303" s="2"/>
       <c r="H303" s="2"/>
       <c r="I303" s="3" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="J303" s="2"/>
     </row>
     <row r="304" spans="1:10">
       <c r="A304" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="D304" s="2">
-        <v>9.9</v>
+        <v>11.9</v>
       </c>
       <c r="E304" s="2">
-        <v>6.93</v>
+        <v>8.33</v>
       </c>
       <c r="F304" s="2"/>
       <c r="G304" s="2"/>
       <c r="H304" s="2"/>
       <c r="I304" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="J304" s="2"/>
     </row>
     <row r="305" spans="1:10">
       <c r="A305" s="2" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="D305" s="2">
-        <v>10.9</v>
+        <v>9.9</v>
       </c>
       <c r="E305" s="2">
-        <v>7.63</v>
+        <v>6.93</v>
       </c>
       <c r="F305" s="2"/>
       <c r="G305" s="2"/>
       <c r="H305" s="2"/>
       <c r="I305" s="3" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="J305" s="2"/>
     </row>
     <row r="306" spans="1:10">
       <c r="A306" s="2" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="D306" s="2">
-        <v>6.9</v>
-      </c>
-      <c r="E306" s="2"/>
+        <v>10.9</v>
+      </c>
+      <c r="E306" s="2">
+        <v>7.63</v>
+      </c>
       <c r="F306" s="2"/>
       <c r="G306" s="2"/>
       <c r="H306" s="2"/>
       <c r="I306" s="3" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="J306" s="2"/>
     </row>
     <row r="307" spans="1:10">
       <c r="A307" s="2" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D307" s="2">
         <v>6.9</v>
       </c>
-      <c r="E307" s="2">
-        <v>4.83</v>
-      </c>
+      <c r="E307" s="2"/>
       <c r="F307" s="2"/>
       <c r="G307" s="2"/>
       <c r="H307" s="2"/>
       <c r="I307" s="3" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="J307" s="2"/>
     </row>
     <row r="308" spans="1:10">
       <c r="A308" s="2" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D308" s="2">
-        <v>5.5</v>
+        <v>6.9</v>
       </c>
       <c r="E308" s="2">
-        <v>3.85</v>
+        <v>4.83</v>
       </c>
       <c r="F308" s="2"/>
       <c r="G308" s="2"/>
       <c r="H308" s="2"/>
       <c r="I308" s="3" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="J308" s="2"/>
     </row>
     <row r="309" spans="1:10">
       <c r="A309" s="2" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="D309" s="2">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="E309" s="2">
-        <v>4.13</v>
+        <v>3.85</v>
       </c>
       <c r="F309" s="2"/>
       <c r="G309" s="2"/>
       <c r="H309" s="2"/>
       <c r="I309" s="3" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="J309" s="2"/>
     </row>
     <row r="310" spans="1:10">
       <c r="A310" s="2" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="D310" s="2">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="E310" s="2">
-        <v>4.55</v>
+        <v>4.13</v>
       </c>
       <c r="F310" s="2"/>
       <c r="G310" s="2"/>
       <c r="H310" s="2"/>
       <c r="I310" s="3" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="J310" s="2"/>
     </row>
     <row r="311" spans="1:10">
       <c r="A311" s="2" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="D311" s="2">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="E311" s="2">
-        <v>5.53</v>
+        <v>4.55</v>
       </c>
       <c r="F311" s="2"/>
       <c r="G311" s="2"/>
       <c r="H311" s="2"/>
       <c r="I311" s="3" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="J311" s="2"/>
     </row>
     <row r="312" spans="1:10">
       <c r="A312" s="2" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="D312" s="2">
-        <v>2.5</v>
+        <v>7.9</v>
       </c>
       <c r="E312" s="2">
-        <v>1.75</v>
+        <v>5.53</v>
       </c>
       <c r="F312" s="2"/>
       <c r="G312" s="2"/>
       <c r="H312" s="2"/>
       <c r="I312" s="3" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="J312" s="2"/>
     </row>
     <row r="313" spans="1:10">
       <c r="A313" s="2" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="D313" s="2">
         <v>2.5</v>
@@ -11356,187 +11357,187 @@
       <c r="G313" s="2"/>
       <c r="H313" s="2"/>
       <c r="I313" s="3" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="J313" s="2"/>
     </row>
     <row r="314" spans="1:10">
       <c r="A314" s="2" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="D314" s="2">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E314" s="2">
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="F314" s="2"/>
       <c r="G314" s="2"/>
       <c r="H314" s="2"/>
       <c r="I314" s="3" t="s">
-        <v>628</v>
+        <v>911</v>
       </c>
       <c r="J314" s="2"/>
     </row>
     <row r="315" spans="1:10">
-      <c r="A315" s="2">
-        <v>80146</v>
-      </c>
-      <c r="B315" s="12" t="s">
+      <c r="A315" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="B315" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="C315" s="12" t="s">
-        <v>1115</v>
+      <c r="C315" s="2" t="s">
+        <v>913</v>
       </c>
       <c r="D315" s="2">
-        <v>7.9</v>
+        <v>1.5</v>
       </c>
       <c r="E315" s="2">
-        <v>5.53</v>
+        <v>1.05</v>
       </c>
       <c r="F315" s="2"/>
       <c r="G315" s="2"/>
       <c r="H315" s="2"/>
       <c r="I315" s="3" t="s">
-        <v>1116</v>
+        <v>628</v>
       </c>
       <c r="J315" s="2"/>
     </row>
     <row r="316" spans="1:10">
-      <c r="A316" s="2" t="s">
-        <v>914</v>
-      </c>
-      <c r="B316" s="2" t="s">
+      <c r="A316" s="2">
+        <v>80146</v>
+      </c>
+      <c r="B316" s="12" t="s">
         <v>781</v>
       </c>
-      <c r="C316" s="2" t="s">
-        <v>915</v>
+      <c r="C316" s="12" t="s">
+        <v>1115</v>
       </c>
       <c r="D316" s="2">
-        <v>1.5</v>
+        <v>7.9</v>
       </c>
       <c r="E316" s="2">
-        <v>1.05</v>
+        <v>5.53</v>
       </c>
       <c r="F316" s="2"/>
       <c r="G316" s="2"/>
       <c r="H316" s="2"/>
       <c r="I316" s="3" t="s">
-        <v>916</v>
+        <v>1116</v>
       </c>
       <c r="J316" s="2"/>
     </row>
     <row r="317" spans="1:10">
-      <c r="A317" s="13">
-        <v>40505</v>
+      <c r="A317" s="2" t="s">
+        <v>914</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>754</v>
+        <v>781</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>1102</v>
+        <v>915</v>
       </c>
       <c r="D317" s="2">
-        <v>20.399999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="E317" s="2">
-        <v>14.28</v>
+        <v>1.05</v>
       </c>
       <c r="F317" s="2"/>
       <c r="G317" s="2"/>
       <c r="H317" s="2"/>
       <c r="I317" s="3" t="s">
-        <v>1103</v>
+        <v>916</v>
       </c>
       <c r="J317" s="2"/>
     </row>
     <row r="318" spans="1:10">
-      <c r="A318" s="2" t="s">
-        <v>917</v>
+      <c r="A318" s="13">
+        <v>40505</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>918</v>
+        <v>1102</v>
       </c>
       <c r="D318" s="2">
-        <v>18.899999999999999</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="E318" s="2">
-        <v>13.23</v>
+        <v>14.28</v>
       </c>
       <c r="F318" s="2"/>
       <c r="G318" s="2"/>
       <c r="H318" s="2"/>
       <c r="I318" s="3" t="s">
-        <v>919</v>
+        <v>1103</v>
       </c>
       <c r="J318" s="2"/>
     </row>
     <row r="319" spans="1:10">
       <c r="A319" s="2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="D319" s="2">
-        <v>20.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="E319" s="2">
-        <v>14.63</v>
+        <v>13.23</v>
       </c>
       <c r="F319" s="2"/>
       <c r="G319" s="2"/>
       <c r="H319" s="2"/>
       <c r="I319" s="3" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="J319" s="2"/>
     </row>
     <row r="320" spans="1:10">
       <c r="A320" s="2" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="D320" s="2">
-        <v>22.5</v>
+        <v>20.9</v>
       </c>
       <c r="E320" s="2">
-        <v>15.75</v>
+        <v>14.63</v>
       </c>
       <c r="F320" s="2"/>
       <c r="G320" s="2"/>
       <c r="H320" s="2"/>
       <c r="I320" s="3" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="J320" s="2"/>
     </row>
-    <row r="321" spans="1:11">
+    <row r="321" spans="1:10">
       <c r="A321" s="2" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="D321" s="2">
         <v>22.5</v>
@@ -11548,19 +11549,19 @@
       <c r="G321" s="2"/>
       <c r="H321" s="2"/>
       <c r="I321" s="3" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="J321" s="2"/>
     </row>
-    <row r="322" spans="1:11">
+    <row r="322" spans="1:10">
       <c r="A322" s="2" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D322" s="2">
         <v>22.5</v>
@@ -11572,19 +11573,19 @@
       <c r="G322" s="2"/>
       <c r="H322" s="2"/>
       <c r="I322" s="3" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="J322" s="2"/>
     </row>
-    <row r="323" spans="1:11">
+    <row r="323" spans="1:10">
       <c r="A323" s="2" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="D323" s="2">
         <v>22.5</v>
@@ -11596,91 +11597,91 @@
       <c r="G323" s="2"/>
       <c r="H323" s="2"/>
       <c r="I323" s="3" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="J323" s="2"/>
     </row>
-    <row r="324" spans="1:11">
+    <row r="324" spans="1:10">
       <c r="A324" s="2" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="D324" s="2">
-        <v>18.5</v>
+        <v>22.5</v>
       </c>
       <c r="E324" s="2">
-        <v>12.95</v>
+        <v>15.75</v>
       </c>
       <c r="F324" s="2"/>
       <c r="G324" s="2"/>
       <c r="H324" s="2"/>
       <c r="I324" s="3" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="J324" s="2"/>
     </row>
-    <row r="325" spans="1:11">
+    <row r="325" spans="1:10">
       <c r="A325" s="2" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D325" s="2">
-        <v>16.3</v>
+        <v>18.5</v>
       </c>
       <c r="E325" s="2">
-        <v>11.41</v>
+        <v>12.95</v>
       </c>
       <c r="F325" s="2"/>
       <c r="G325" s="2"/>
       <c r="H325" s="2"/>
       <c r="I325" s="3" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="J325" s="2"/>
     </row>
-    <row r="326" spans="1:11">
+    <row r="326" spans="1:10">
       <c r="A326" s="2" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="D326" s="2">
-        <v>18.5</v>
+        <v>16.3</v>
       </c>
       <c r="E326" s="2">
-        <v>12.95</v>
+        <v>11.41</v>
       </c>
       <c r="F326" s="2"/>
       <c r="G326" s="2"/>
       <c r="H326" s="2"/>
       <c r="I326" s="3" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="J326" s="2"/>
     </row>
-    <row r="327" spans="1:11">
+    <row r="327" spans="1:10">
       <c r="A327" s="2" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="D327" s="2">
         <v>18.5</v>
@@ -11692,19 +11693,19 @@
       <c r="G327" s="2"/>
       <c r="H327" s="2"/>
       <c r="I327" s="3" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="J327" s="2"/>
     </row>
-    <row r="328" spans="1:11">
+    <row r="328" spans="1:10">
       <c r="A328" s="2" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="D328" s="2">
         <v>18.5</v>
@@ -11716,19 +11717,19 @@
       <c r="G328" s="2"/>
       <c r="H328" s="2"/>
       <c r="I328" s="3" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="J328" s="2"/>
     </row>
-    <row r="329" spans="1:11">
+    <row r="329" spans="1:10">
       <c r="A329" s="2" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="D329" s="2">
         <v>18.5</v>
@@ -11740,19 +11741,19 @@
       <c r="G329" s="2"/>
       <c r="H329" s="2"/>
       <c r="I329" s="3" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="J329" s="2"/>
     </row>
-    <row r="330" spans="1:11">
+    <row r="330" spans="1:10">
       <c r="A330" s="2" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="D330" s="2">
         <v>18.5</v>
@@ -11764,19 +11765,19 @@
       <c r="G330" s="2"/>
       <c r="H330" s="2"/>
       <c r="I330" s="3" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="J330" s="2"/>
     </row>
-    <row r="331" spans="1:11">
+    <row r="331" spans="1:10">
       <c r="A331" s="2" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="D331" s="2">
         <v>18.5</v>
@@ -11788,308 +11789,308 @@
       <c r="G331" s="2"/>
       <c r="H331" s="2"/>
       <c r="I331" s="3" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="J331" s="2"/>
     </row>
-    <row r="332" spans="1:11">
+    <row r="332" spans="1:10">
       <c r="A332" s="2" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="D332" s="2">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="E332" s="2">
-        <v>13.65</v>
+        <v>12.95</v>
       </c>
       <c r="F332" s="2"/>
       <c r="G332" s="2"/>
       <c r="H332" s="2"/>
       <c r="I332" s="3" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="J332" s="2"/>
     </row>
-    <row r="333" spans="1:11">
+    <row r="333" spans="1:10">
       <c r="A333" s="2" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="D333" s="2">
-        <v>22.5</v>
+        <v>19.5</v>
       </c>
       <c r="E333" s="2">
-        <v>15.75</v>
+        <v>13.65</v>
       </c>
       <c r="F333" s="2"/>
       <c r="G333" s="2"/>
       <c r="H333" s="2"/>
       <c r="I333" s="3" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="J333" s="2"/>
     </row>
-    <row r="334" spans="1:11">
+    <row r="334" spans="1:10">
       <c r="A334" s="2" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="D334" s="2">
-        <v>16.899999999999999</v>
+        <v>22.5</v>
       </c>
       <c r="E334" s="2">
-        <v>11.83</v>
+        <v>15.75</v>
       </c>
       <c r="F334" s="2"/>
       <c r="G334" s="2"/>
       <c r="H334" s="2"/>
       <c r="I334" s="3" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="J334" s="2"/>
     </row>
-    <row r="335" spans="1:11">
+    <row r="335" spans="1:10">
       <c r="A335" s="2" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D335" s="2">
-        <v>23.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E335" s="2">
-        <v>16.73</v>
+        <v>11.83</v>
       </c>
       <c r="F335" s="2"/>
       <c r="G335" s="2"/>
       <c r="H335" s="2"/>
       <c r="I335" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="J335" s="2"/>
+    </row>
+    <row r="336" spans="1:10">
+      <c r="A336" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="C336" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="D336" s="2">
+        <v>23.9</v>
+      </c>
+      <c r="E336" s="2">
+        <v>16.73</v>
+      </c>
+      <c r="F336" s="2"/>
+      <c r="G336" s="2"/>
+      <c r="H336" s="2"/>
+      <c r="I336" s="3" t="s">
         <v>970</v>
       </c>
-      <c r="J335" s="2"/>
-    </row>
-    <row r="336" spans="1:11">
-      <c r="A336" s="5">
+      <c r="J336" s="2"/>
+    </row>
+    <row r="337" spans="1:11">
+      <c r="A337" s="5">
         <v>100236</v>
       </c>
-      <c r="B336" s="10" t="s">
+      <c r="B337" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="C336" s="6" t="s">
+      <c r="C337" s="6" t="s">
         <v>971</v>
       </c>
-      <c r="D336" s="6">
+      <c r="D337" s="6">
         <v>14.9</v>
       </c>
-      <c r="E336" s="6">
+      <c r="E337" s="6">
         <v>10.43</v>
       </c>
-      <c r="F336" s="6"/>
-      <c r="G336" s="6"/>
-      <c r="H336" s="6"/>
-      <c r="I336" s="7" t="s">
+      <c r="F337" s="6"/>
+      <c r="G337" s="6"/>
+      <c r="H337" s="6"/>
+      <c r="I337" s="7" t="s">
         <v>972</v>
       </c>
-      <c r="J336" s="8"/>
-      <c r="K336" s="9"/>
-    </row>
-    <row r="337" spans="1:11">
-      <c r="A337" s="2" t="s">
-        <v>973</v>
-      </c>
-      <c r="B337" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C337" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="D337" s="2">
-        <v>11.5</v>
-      </c>
-      <c r="E337" s="2">
-        <v>8.0500000000000007</v>
-      </c>
-      <c r="F337" s="2"/>
-      <c r="G337" s="2"/>
-      <c r="H337" s="2"/>
-      <c r="I337" s="3" t="s">
-        <v>975</v>
-      </c>
-      <c r="J337" s="2"/>
+      <c r="J337" s="8"/>
+      <c r="K337" s="9"/>
     </row>
     <row r="338" spans="1:11">
       <c r="A338" s="2" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="D338" s="2">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="E338" s="2">
-        <v>7.63</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="F338" s="2"/>
       <c r="G338" s="2"/>
       <c r="H338" s="2"/>
       <c r="I338" s="3" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="J338" s="2"/>
     </row>
     <row r="339" spans="1:11">
       <c r="A339" s="2" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="D339" s="2">
-        <v>14.9</v>
+        <v>10.9</v>
       </c>
       <c r="E339" s="2">
-        <v>10.15</v>
+        <v>7.63</v>
       </c>
       <c r="F339" s="2"/>
       <c r="G339" s="2"/>
       <c r="H339" s="2"/>
       <c r="I339" s="3" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="J339" s="2"/>
     </row>
     <row r="340" spans="1:11">
       <c r="A340" s="2" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="D340" s="2">
-        <v>9.9</v>
+        <v>14.9</v>
       </c>
       <c r="E340" s="2">
-        <v>6.93</v>
+        <v>10.15</v>
       </c>
       <c r="F340" s="2"/>
       <c r="G340" s="2"/>
       <c r="H340" s="2"/>
       <c r="I340" s="3" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="J340" s="2"/>
     </row>
     <row r="341" spans="1:11">
       <c r="A341" s="2" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="D341" s="2">
-        <v>16.899999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="E341" s="2">
-        <v>11.83</v>
+        <v>6.93</v>
       </c>
       <c r="F341" s="2"/>
       <c r="G341" s="2"/>
       <c r="H341" s="2"/>
       <c r="I341" s="3" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="J341" s="2"/>
     </row>
     <row r="342" spans="1:11">
       <c r="A342" s="2" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="D342" s="2">
-        <v>14</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E342" s="2">
-        <v>9.8000000000000007</v>
+        <v>11.83</v>
       </c>
       <c r="F342" s="2"/>
       <c r="G342" s="2"/>
       <c r="H342" s="2"/>
       <c r="I342" s="3" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="J342" s="2"/>
     </row>
     <row r="343" spans="1:11">
       <c r="A343" s="2" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>1104</v>
+        <v>989</v>
       </c>
       <c r="D343" s="2">
-        <v>15.9</v>
+        <v>14</v>
       </c>
       <c r="E343" s="2">
-        <v>11.13</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="F343" s="2"/>
       <c r="G343" s="2"/>
       <c r="H343" s="2"/>
       <c r="I343" s="3" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="J343" s="2"/>
     </row>
     <row r="344" spans="1:11">
       <c r="A344" s="2" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>994</v>
+        <v>1104</v>
       </c>
       <c r="D344" s="2">
         <v>15.9</v>
@@ -12101,478 +12102,480 @@
       <c r="G344" s="2"/>
       <c r="H344" s="2"/>
       <c r="I344" s="3" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="J344" s="2"/>
     </row>
     <row r="345" spans="1:11">
       <c r="A345" s="2" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="D345" s="2">
-        <v>11.9</v>
+        <v>15.9</v>
       </c>
       <c r="E345" s="2">
-        <v>8.33</v>
+        <v>11.13</v>
       </c>
       <c r="F345" s="2"/>
       <c r="G345" s="2"/>
       <c r="H345" s="2"/>
       <c r="I345" s="3" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="J345" s="2"/>
     </row>
     <row r="346" spans="1:11">
       <c r="A346" s="2" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="D346" s="2">
-        <v>6.9</v>
+        <v>11.9</v>
       </c>
       <c r="E346" s="2">
-        <v>4.83</v>
+        <v>8.33</v>
       </c>
       <c r="F346" s="2"/>
       <c r="G346" s="2"/>
       <c r="H346" s="2"/>
       <c r="I346" s="3" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J346" s="2"/>
     </row>
     <row r="347" spans="1:11">
       <c r="A347" s="2" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="D347" s="2">
-        <v>11.5</v>
+        <v>6.9</v>
       </c>
       <c r="E347" s="2">
-        <v>8.0500000000000007</v>
+        <v>4.83</v>
       </c>
       <c r="F347" s="2"/>
       <c r="G347" s="2"/>
       <c r="H347" s="2"/>
       <c r="I347" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="J347" s="2"/>
+    </row>
+    <row r="348" spans="1:11">
+      <c r="A348" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C348" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D348" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="E348" s="2">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="F348" s="2"/>
+      <c r="G348" s="2"/>
+      <c r="H348" s="2"/>
+      <c r="I348" s="3" t="s">
         <v>1004</v>
       </c>
-      <c r="J347" s="2"/>
-    </row>
-    <row r="348" spans="1:11">
-      <c r="A348" s="5">
+      <c r="J348" s="2"/>
+    </row>
+    <row r="349" spans="1:11">
+      <c r="A349" s="5">
         <v>100224</v>
       </c>
-      <c r="B348" s="6" t="s">
+      <c r="B349" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C348" s="6" t="s">
+      <c r="C349" s="6" t="s">
         <v>1005</v>
       </c>
-      <c r="D348" s="6">
+      <c r="D349" s="6">
         <v>12.5</v>
       </c>
-      <c r="E348" s="6">
+      <c r="E349" s="6">
         <v>8.75</v>
       </c>
-      <c r="F348" s="6"/>
-      <c r="G348" s="6"/>
-      <c r="H348" s="6"/>
-      <c r="I348" s="7" t="s">
+      <c r="F349" s="6"/>
+      <c r="G349" s="6"/>
+      <c r="H349" s="6"/>
+      <c r="I349" s="7" t="s">
         <v>1006</v>
       </c>
-      <c r="J348" s="8"/>
-      <c r="K348" s="9"/>
-    </row>
-    <row r="349" spans="1:11">
-      <c r="A349" s="2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B349" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C349" s="2" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D349" s="2">
-        <v>11.3</v>
-      </c>
-      <c r="E349" s="2">
-        <v>7.91</v>
-      </c>
-      <c r="F349" s="2"/>
-      <c r="G349" s="2"/>
-      <c r="H349" s="2"/>
-      <c r="I349" s="3" t="s">
-        <v>1009</v>
-      </c>
-      <c r="J349" s="2"/>
+      <c r="J349" s="8"/>
+      <c r="K349" s="9"/>
     </row>
     <row r="350" spans="1:11">
       <c r="A350" s="2" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="D350" s="2">
-        <v>26.9</v>
+        <v>11.3</v>
       </c>
       <c r="E350" s="2">
-        <v>18.829999999999998</v>
+        <v>7.91</v>
       </c>
       <c r="F350" s="2"/>
       <c r="G350" s="2"/>
       <c r="H350" s="2"/>
       <c r="I350" s="3" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="J350" s="2"/>
     </row>
     <row r="351" spans="1:11">
       <c r="A351" s="2" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="D351" s="2">
-        <v>19.899999999999999</v>
+        <v>26.9</v>
       </c>
       <c r="E351" s="2">
-        <v>13.93</v>
+        <v>18.829999999999998</v>
       </c>
       <c r="F351" s="2"/>
       <c r="G351" s="2"/>
       <c r="H351" s="2"/>
       <c r="I351" s="3" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="J351" s="2"/>
     </row>
     <row r="352" spans="1:11">
       <c r="A352" s="2" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>9</v>
+        <v>225</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D352" s="2">
-        <v>36</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="E352" s="2">
-        <v>25.2</v>
+        <v>13.93</v>
       </c>
       <c r="F352" s="2"/>
       <c r="G352" s="2"/>
       <c r="H352" s="2"/>
       <c r="I352" s="3" t="s">
-        <v>223</v>
+        <v>1015</v>
       </c>
       <c r="J352" s="2"/>
     </row>
     <row r="353" spans="1:10">
       <c r="A353" s="2" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>225</v>
+        <v>9</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="D353" s="2">
-        <v>16.899999999999999</v>
+        <v>36</v>
       </c>
       <c r="E353" s="2">
-        <v>11.83</v>
+        <v>25.2</v>
       </c>
       <c r="F353" s="2"/>
       <c r="G353" s="2"/>
       <c r="H353" s="2"/>
       <c r="I353" s="3" t="s">
-        <v>1020</v>
+        <v>223</v>
       </c>
       <c r="J353" s="2"/>
     </row>
     <row r="354" spans="1:10">
       <c r="A354" s="2" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="D354" s="2">
-        <v>18.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E354" s="2">
-        <v>12.95</v>
+        <v>11.83</v>
       </c>
       <c r="F354" s="2"/>
       <c r="G354" s="2"/>
       <c r="H354" s="2"/>
       <c r="I354" s="3" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="J354" s="2"/>
     </row>
     <row r="355" spans="1:10">
       <c r="A355" s="2" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="D355" s="2">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="E355" s="2">
-        <v>10.85</v>
+        <v>12.95</v>
       </c>
       <c r="F355" s="2"/>
       <c r="G355" s="2"/>
       <c r="H355" s="2"/>
       <c r="I355" s="3" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="J355" s="2"/>
     </row>
     <row r="356" spans="1:10">
-      <c r="A356" s="13">
-        <v>100218</v>
-      </c>
-      <c r="B356" s="12" t="s">
-        <v>1105</v>
+      <c r="A356" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>232</v>
+        <v>1025</v>
       </c>
       <c r="D356" s="2">
-        <v>12.9</v>
+        <v>15.5</v>
       </c>
       <c r="E356" s="2">
-        <v>9.0299999999999994</v>
+        <v>10.85</v>
       </c>
       <c r="F356" s="2"/>
       <c r="G356" s="2"/>
       <c r="H356" s="2"/>
-      <c r="I356" s="3"/>
+      <c r="I356" s="3" t="s">
+        <v>1026</v>
+      </c>
       <c r="J356" s="2"/>
     </row>
     <row r="357" spans="1:10">
-      <c r="A357" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B357" s="2" t="s">
-        <v>225</v>
+      <c r="A357" s="13">
+        <v>100218</v>
+      </c>
+      <c r="B357" s="12" t="s">
+        <v>1105</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>1028</v>
+        <v>232</v>
       </c>
       <c r="D357" s="2">
-        <v>19.899999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="E357" s="2">
-        <v>13.93</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="F357" s="2"/>
       <c r="G357" s="2"/>
       <c r="H357" s="2"/>
-      <c r="I357" s="3" t="s">
-        <v>1029</v>
-      </c>
+      <c r="I357" s="3"/>
       <c r="J357" s="2"/>
     </row>
     <row r="358" spans="1:10">
       <c r="A358" s="2" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>9</v>
+        <v>225</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="D358" s="2">
-        <v>50.5</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="E358" s="2">
-        <v>35.35</v>
+        <v>13.93</v>
       </c>
       <c r="F358" s="2"/>
       <c r="G358" s="2"/>
       <c r="H358" s="2"/>
       <c r="I358" s="3" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="J358" s="2"/>
     </row>
     <row r="359" spans="1:10">
       <c r="A359" s="2" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="D359" s="2">
-        <v>32.5</v>
+        <v>50.5</v>
       </c>
       <c r="E359" s="2">
-        <v>22.75</v>
+        <v>35.35</v>
       </c>
       <c r="F359" s="2"/>
       <c r="G359" s="2"/>
       <c r="H359" s="2"/>
       <c r="I359" s="3" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="J359" s="2"/>
     </row>
     <row r="360" spans="1:10">
       <c r="A360" s="2" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="D360" s="2">
-        <v>43.5</v>
+        <v>32.5</v>
       </c>
       <c r="E360" s="2">
-        <v>30.45</v>
+        <v>22.75</v>
       </c>
       <c r="F360" s="2"/>
       <c r="G360" s="2"/>
       <c r="H360" s="2"/>
       <c r="I360" s="3" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="J360" s="2"/>
     </row>
     <row r="361" spans="1:10">
       <c r="A361" s="2" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>225</v>
+        <v>9</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="D361" s="2">
-        <v>8.9</v>
+        <v>43.5</v>
       </c>
       <c r="E361" s="2">
-        <v>6.23</v>
+        <v>30.45</v>
       </c>
       <c r="F361" s="2"/>
       <c r="G361" s="2"/>
       <c r="H361" s="2"/>
       <c r="I361" s="3" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="J361" s="2"/>
     </row>
     <row r="362" spans="1:10">
       <c r="A362" s="2" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="D362" s="2">
-        <v>14.5</v>
+        <v>8.9</v>
       </c>
       <c r="E362" s="2">
-        <v>10.15</v>
+        <v>6.23</v>
       </c>
       <c r="F362" s="2"/>
       <c r="G362" s="2"/>
       <c r="H362" s="2"/>
       <c r="I362" s="3" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="J362" s="2"/>
     </row>
     <row r="363" spans="1:10">
-      <c r="A363" s="13">
-        <v>100206</v>
-      </c>
-      <c r="B363" s="12" t="s">
-        <v>1105</v>
-      </c>
-      <c r="C363" s="12" t="s">
-        <v>244</v>
+      <c r="A363" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>1043</v>
       </c>
       <c r="D363" s="2">
-        <v>18.899999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="E363" s="2">
-        <v>13.23</v>
+        <v>10.15</v>
       </c>
       <c r="F363" s="2"/>
       <c r="G363" s="2"/>
       <c r="H363" s="2"/>
-      <c r="I363" s="3"/>
+      <c r="I363" s="3" t="s">
+        <v>1044</v>
+      </c>
       <c r="J363" s="2"/>
     </row>
     <row r="364" spans="1:10">
       <c r="A364" s="13">
-        <v>100220</v>
+        <v>100206</v>
       </c>
       <c r="B364" s="12" t="s">
         <v>1105</v>
       </c>
       <c r="C364" s="12" t="s">
-        <v>1106</v>
+        <v>244</v>
       </c>
       <c r="D364" s="2">
-        <v>9.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="E364" s="2">
-        <v>6.93</v>
+        <v>13.23</v>
       </c>
       <c r="F364" s="2"/>
       <c r="G364" s="2"/>
@@ -12581,230 +12584,228 @@
       <c r="J364" s="2"/>
     </row>
     <row r="365" spans="1:10">
-      <c r="A365" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B365" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C365" s="2" t="s">
-        <v>1046</v>
+      <c r="A365" s="13">
+        <v>100220</v>
+      </c>
+      <c r="B365" s="12" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C365" s="12" t="s">
+        <v>1106</v>
       </c>
       <c r="D365" s="2">
-        <v>5.2</v>
+        <v>9.9</v>
       </c>
       <c r="E365" s="2">
-        <v>3.64</v>
+        <v>6.93</v>
       </c>
       <c r="F365" s="2"/>
       <c r="G365" s="2"/>
       <c r="H365" s="2"/>
-      <c r="I365" s="3" t="s">
-        <v>1047</v>
-      </c>
+      <c r="I365" s="3"/>
       <c r="J365" s="2"/>
     </row>
     <row r="366" spans="1:10">
       <c r="A366" s="2" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="D366" s="2">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="E366" s="2">
-        <v>4.2</v>
+        <v>3.64</v>
       </c>
       <c r="F366" s="2"/>
       <c r="G366" s="2"/>
       <c r="H366" s="2"/>
       <c r="I366" s="3" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="J366" s="2"/>
     </row>
     <row r="367" spans="1:10">
       <c r="A367" s="2" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="D367" s="2">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="E367" s="2">
-        <v>4.83</v>
+        <v>4.2</v>
       </c>
       <c r="F367" s="2"/>
       <c r="G367" s="2"/>
       <c r="H367" s="2"/>
       <c r="I367" s="3" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="J367" s="2"/>
     </row>
     <row r="368" spans="1:10">
       <c r="A368" s="2" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="D368" s="2">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="E368" s="2">
-        <v>5.53</v>
+        <v>4.83</v>
       </c>
       <c r="F368" s="2"/>
       <c r="G368" s="2"/>
       <c r="H368" s="2"/>
       <c r="I368" s="3" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="J368" s="2"/>
     </row>
     <row r="369" spans="1:10">
       <c r="A369" s="2" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="D369" s="2">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="E369" s="2">
-        <v>6.23</v>
+        <v>5.53</v>
       </c>
       <c r="F369" s="2"/>
       <c r="G369" s="2"/>
       <c r="H369" s="2"/>
       <c r="I369" s="3" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="J369" s="2"/>
     </row>
     <row r="370" spans="1:10">
       <c r="A370" s="2" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="D370" s="2">
-        <v>12.9</v>
+        <v>8.9</v>
       </c>
       <c r="E370" s="2">
-        <v>9.0299999999999994</v>
+        <v>6.23</v>
       </c>
       <c r="F370" s="2"/>
       <c r="G370" s="2"/>
       <c r="H370" s="2"/>
       <c r="I370" s="3" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="J370" s="2"/>
     </row>
     <row r="371" spans="1:10">
       <c r="A371" s="2" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="D371" s="2">
-        <v>7.9</v>
+        <v>12.9</v>
       </c>
       <c r="E371" s="2">
-        <v>5.53</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="F371" s="2"/>
       <c r="G371" s="2"/>
       <c r="H371" s="2"/>
       <c r="I371" s="3" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="J371" s="2"/>
     </row>
     <row r="372" spans="1:10">
       <c r="A372" s="2" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>9</v>
+        <v>225</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="D372" s="2">
-        <v>2.5</v>
+        <v>7.9</v>
       </c>
       <c r="E372" s="2">
-        <v>2.5</v>
+        <v>5.53</v>
       </c>
       <c r="F372" s="2"/>
       <c r="G372" s="2"/>
       <c r="H372" s="2"/>
       <c r="I372" s="3" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="J372" s="2"/>
     </row>
     <row r="373" spans="1:10">
       <c r="A373" s="2" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>781</v>
+        <v>9</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="D373" s="2">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="E373" s="2">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="F373" s="2"/>
       <c r="G373" s="2"/>
       <c r="H373" s="2"/>
       <c r="I373" s="3" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="J373" s="2"/>
     </row>
     <row r="374" spans="1:10">
       <c r="A374" s="2" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="D374" s="2">
         <v>0.3</v>
@@ -12816,19 +12817,19 @@
       <c r="G374" s="2"/>
       <c r="H374" s="2"/>
       <c r="I374" s="3" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="J374" s="2"/>
     </row>
     <row r="375" spans="1:10">
       <c r="A375" s="2" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="D375" s="2">
         <v>0.3</v>
@@ -12840,59 +12841,63 @@
       <c r="G375" s="2"/>
       <c r="H375" s="2"/>
       <c r="I375" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="J375" s="2"/>
+    </row>
+    <row r="376" spans="1:10">
+      <c r="A376" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D376" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E376" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F376" s="2"/>
+      <c r="G376" s="2"/>
+      <c r="H376" s="2"/>
+      <c r="I376" s="3" t="s">
         <v>1077</v>
       </c>
-      <c r="J375" s="2"/>
-    </row>
-    <row r="376" spans="1:10">
-      <c r="A376" s="14">
-        <v>120101</v>
-      </c>
-      <c r="B376" s="12" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C376" t="s">
-        <v>1109</v>
-      </c>
-      <c r="D376" s="12">
-        <v>4.5</v>
-      </c>
-      <c r="E376">
-        <v>3.15</v>
-      </c>
-      <c r="I376" s="11" t="s">
-        <v>1110</v>
-      </c>
+      <c r="J376" s="2"/>
     </row>
     <row r="377" spans="1:10">
       <c r="A377" s="14">
-        <v>120102</v>
+        <v>120101</v>
       </c>
       <c r="B377" s="12" t="s">
         <v>1108</v>
       </c>
-      <c r="C377" s="15" t="s">
-        <v>1111</v>
+      <c r="C377" t="s">
+        <v>1109</v>
       </c>
       <c r="D377" s="12">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E377">
-        <v>2.4500000000000002</v>
+        <v>3.15</v>
       </c>
       <c r="I377" s="11" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="378" spans="1:10">
       <c r="A378" s="14">
-        <v>120103</v>
+        <v>120102</v>
       </c>
       <c r="B378" s="12" t="s">
         <v>1108</v>
       </c>
-      <c r="C378" t="s">
-        <v>1113</v>
+      <c r="C378" s="15" t="s">
+        <v>1111</v>
       </c>
       <c r="D378" s="12">
         <v>3.5</v>
@@ -12900,12 +12905,32 @@
       <c r="E378">
         <v>2.4500000000000002</v>
       </c>
-      <c r="I378" t="s">
+      <c r="I378" s="11" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10">
+      <c r="A379" s="14">
+        <v>120103</v>
+      </c>
+      <c r="B379" s="12" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C379" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D379" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="E379">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="I379" t="s">
         <v>1114</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J375" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J376" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -12991,288 +13016,288 @@
     <hyperlink ref="I84" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
     <hyperlink ref="I85" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
     <hyperlink ref="I86" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="I87" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="I88" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="I89" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="I90" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="I91" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="I92" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="I93" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="I94" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="I95" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="I96" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="I97" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="I98" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="I99" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="I100" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="I101" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="I102" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="I103" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="I104" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="I105" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="I106" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="I107" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="I108" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="I109" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="I110" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="I111" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="I112" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="I113" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="I114" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="I115" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="I116" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="I118" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="I119" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="I120" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="I121" r:id="rId118" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="I122" r:id="rId119" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="I123" r:id="rId120" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="I124" r:id="rId121" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="I125" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="I126" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="I127" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="I128" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="I129" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="I130" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="I131" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="I132" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="I133" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="I134" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="I135" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="I136" r:id="rId133" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="I137" r:id="rId134" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="I138" r:id="rId135" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="I139" r:id="rId136" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="I140" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="I141" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="I142" r:id="rId139" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="I143" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="I144" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="I145" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="I146" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="I147" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="I148" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="I149" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="I150" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="I151" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="I152" r:id="rId149" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="I153" r:id="rId150" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="I154" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="I155" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="I156" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="I157" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="I158" r:id="rId155" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="I159" r:id="rId156" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="I161" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="I162" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="I163" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="I164" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="I165" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="I166" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="I167" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="I168" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="I169" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="I170" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="I171" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="I172" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="I173" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="I174" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="I175" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="I176" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="I177" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="I178" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="I179" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="I180" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="I181" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="I182" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="I183" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="I184" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="I185" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="I186" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="I187" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="I188" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="I189" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="I190" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="I191" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="I192" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="I193" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="I194" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="I195" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="I196" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="I197" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="I198" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="I199" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="I200" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="I201" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="I202" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="I203" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="I204" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="I205" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="I206" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="I207" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="I208" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="I209" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="I210" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="I211" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="I212" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="I213" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="I214" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="I218" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="I219" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="I220" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="I221" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="I222" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="I223" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="I224" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="I225" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="I226" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="I227" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="I228" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="I229" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="I230" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="I231" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="I232" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="I233" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="I234" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="I235" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="I236" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="I237" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="I238" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="I239" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="I240" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="I241" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="I242" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="I243" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="I244" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="I245" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="I246" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="I247" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="I248" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="I249" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="I250" r:id="rId243" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="I251" r:id="rId244" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="I252" r:id="rId245" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="I253" r:id="rId246" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="I254" r:id="rId247" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="I255" r:id="rId248" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="I256" r:id="rId249" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="I257" r:id="rId250" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="I258" r:id="rId251" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="I259" r:id="rId252" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="I260" r:id="rId253" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="I261" r:id="rId254" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="I262" r:id="rId255" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="I263" r:id="rId256" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="I264" r:id="rId257" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="I265" r:id="rId258" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="I266" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="I267" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="I268" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="I269" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="I270" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="I271" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="I272" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="I273" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="I274" r:id="rId267" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="I275" r:id="rId268" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="I276" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="I277" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="I278" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="I279" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="I280" r:id="rId273" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="I281" r:id="rId274" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="I282" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="I283" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="I284" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="I285" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="I286" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="I287" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="I288" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="I289" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="I290" r:id="rId283" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="I291" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="I292" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="I293" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="I294" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="I295" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="I296" r:id="rId289" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="I297" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="I298" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="I299" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="I300" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="I301" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="I302" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="I303" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="I304" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="I305" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="I306" r:id="rId299" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="I307" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="I308" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="I309" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="I310" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="I311" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="I312" r:id="rId305" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="I313" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="I314" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="I316" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="I318" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="I319" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="I320" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="I321" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="I322" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="I323" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="I324" r:id="rId315" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="I325" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="I326" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="I327" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="I328" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="I329" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="I330" r:id="rId321" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="I331" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="I332" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="I333" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="I334" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="I335" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="I336" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="I337" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="I338" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="I339" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="I340" r:id="rId331" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="I341" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="I342" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="I343" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="I344" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="I345" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="I346" r:id="rId337" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="I347" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="I348" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="I349" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="I350" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="I351" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="I352" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="I353" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="I354" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="I355" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="I357" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="I358" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="I359" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="I360" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="I361" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="I362" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="I365" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="I366" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="I367" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="I368" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="I369" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="I370" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="I371" r:id="rId359" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="I372" r:id="rId360" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="I373" r:id="rId361" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="I374" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="I375" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="I376" r:id="rId364" xr:uid="{F9160EA0-F07B-4BB5-B702-F5073AA95056}"/>
-    <hyperlink ref="I377" r:id="rId365" xr:uid="{1AC55159-5C0D-4F25-94CA-0E2E9DEE3542}"/>
-    <hyperlink ref="I215" r:id="rId366" xr:uid="{39463792-79B1-460E-B346-5F21542FF683}"/>
+    <hyperlink ref="I88" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="I89" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="I90" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="I91" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="I92" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="I93" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="I94" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="I95" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="I96" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="I97" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="I98" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="I99" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="I100" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="I101" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="I102" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="I103" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="I104" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="I105" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="I106" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="I107" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="I108" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="I109" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="I110" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="I111" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="I112" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="I113" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="I114" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="I115" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="I116" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="I117" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="I119" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="I120" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="I121" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="I122" r:id="rId118" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="I123" r:id="rId119" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="I124" r:id="rId120" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="I125" r:id="rId121" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="I126" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="I127" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="I128" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="I129" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="I130" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="I131" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="I132" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="I133" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="I134" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="I135" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="I136" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="I137" r:id="rId133" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="I138" r:id="rId134" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="I139" r:id="rId135" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="I140" r:id="rId136" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="I141" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="I142" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="I143" r:id="rId139" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="I144" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="I145" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="I146" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="I147" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="I148" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="I149" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="I150" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="I151" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="I152" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="I153" r:id="rId149" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="I154" r:id="rId150" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="I155" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="I156" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="I157" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="I158" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="I159" r:id="rId155" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="I160" r:id="rId156" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="I162" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="I163" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="I164" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="I165" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="I166" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="I167" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="I168" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="I169" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="I170" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="I171" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="I172" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="I173" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="I174" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="I175" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="I176" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="I177" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="I178" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="I179" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="I180" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="I181" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="I182" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="I183" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="I184" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="I185" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="I186" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="I187" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="I188" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="I189" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="I190" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="I191" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="I192" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="I193" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="I194" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="I195" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="I196" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="I197" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="I198" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="I199" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="I200" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="I201" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="I202" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="I203" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="I204" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="I205" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="I206" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="I207" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="I208" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="I209" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="I210" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="I211" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="I212" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="I213" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="I214" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="I215" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="I219" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="I220" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="I221" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="I222" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="I223" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="I224" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="I225" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="I226" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="I227" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="I228" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="I229" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="I230" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="I231" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="I232" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="I233" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="I234" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="I235" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="I236" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="I237" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="I238" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="I239" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="I240" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="I241" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="I242" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="I243" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="I244" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="I245" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="I246" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="I247" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="I248" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="I249" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="I250" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="I251" r:id="rId243" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="I252" r:id="rId244" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="I253" r:id="rId245" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="I254" r:id="rId246" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="I255" r:id="rId247" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="I256" r:id="rId248" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="I257" r:id="rId249" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="I258" r:id="rId250" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="I259" r:id="rId251" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="I260" r:id="rId252" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="I261" r:id="rId253" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="I262" r:id="rId254" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="I263" r:id="rId255" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="I264" r:id="rId256" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="I265" r:id="rId257" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="I266" r:id="rId258" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="I267" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="I268" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="I269" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="I270" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="I271" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="I272" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="I273" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="I274" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="I275" r:id="rId267" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="I276" r:id="rId268" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="I277" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="I278" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="I279" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="I280" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="I281" r:id="rId273" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="I282" r:id="rId274" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="I283" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="I284" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="I285" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="I286" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="I287" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="I288" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="I289" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="I290" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="I291" r:id="rId283" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="I292" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="I293" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="I294" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="I295" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="I296" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="I297" r:id="rId289" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="I298" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="I299" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="I300" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="I301" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="I302" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="I303" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="I304" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="I305" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="I306" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="I307" r:id="rId299" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="I308" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="I309" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="I310" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="I311" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="I312" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="I313" r:id="rId305" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="I314" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="I315" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="I317" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="I319" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="I320" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="I321" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="I322" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="I323" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="I324" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="I325" r:id="rId315" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="I326" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="I327" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="I328" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="I329" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="I330" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="I331" r:id="rId321" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="I332" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="I333" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="I334" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="I335" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="I336" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="I337" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="I338" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="I339" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="I340" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="I341" r:id="rId331" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="I342" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="I343" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="I344" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="I345" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="I346" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="I347" r:id="rId337" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="I348" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="I349" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="I350" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="I351" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="I352" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="I353" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="I354" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="I355" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="I356" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="I358" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="I359" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="I360" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="I361" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="I362" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="I363" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="I366" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="I367" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="I368" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="I369" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="I370" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="I371" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="I372" r:id="rId359" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="I373" r:id="rId360" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="I374" r:id="rId361" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="I375" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="I376" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="I377" r:id="rId364" xr:uid="{F9160EA0-F07B-4BB5-B702-F5073AA95056}"/>
+    <hyperlink ref="I378" r:id="rId365" xr:uid="{1AC55159-5C0D-4F25-94CA-0E2E9DEE3542}"/>
+    <hyperlink ref="I216" r:id="rId366" xr:uid="{39463792-79B1-460E-B346-5F21542FF683}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/TTABLEAU DES PRIX AVEC REF.xlsx
+++ b/TTABLEAU DES PRIX AVEC REF.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melou\blazing-dynasty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3365A63-375A-479C-8CCA-F3DBD20F654F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586DC711-4419-4CD9-9586-0B7F0A440A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13935" yWindow="75" windowWidth="13665" windowHeight="14925" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$376</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$379</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="1133">
   <si>
     <t>Art</t>
   </si>
@@ -3409,13 +3409,31 @@
   </si>
   <si>
     <t xml:space="preserve">Vitamins. Complexe de détoxification et de purification du côlon </t>
+  </si>
+  <si>
+    <t>Smart Meal. Supergreens &amp; Fibres quotidiens. Saveur mangue</t>
+  </si>
+  <si>
+    <t>https://www.mihi.care/storage/26/09/fbBhnLvqmgktJxnLGhT5I2OkK0fvu3IFOElY1ihQ.png</t>
+  </si>
+  <si>
+    <t>Vitamins. Racine d'échinacée Vital</t>
+  </si>
+  <si>
+    <t>https://www.mihi.care/storage/26/09/t7AoPGZFRQZAhTpdq3PXvpd1bWm5jzXveDO8kytN.png</t>
+  </si>
+  <si>
+    <t>Healthy Body. Baume corporel à l'eucalyptus</t>
+  </si>
+  <si>
+    <t>https://www.mihi.care/storage/26/09/RFp3lE5PSVk90Q5TQtpLX3COOUm0YX8dOcnbMopJ.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3471,6 +3489,11 @@
       <color rgb="FF212529"/>
       <name val="Jost"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF767676"/>
+      <name val="Jost"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -3520,7 +3543,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3553,6 +3576,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -3818,7 +3842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M379"/>
+  <dimension ref="A1:M382"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -5984,422 +6008,428 @@
       <c r="L89" s="9"/>
     </row>
     <row r="90" spans="1:13">
-      <c r="A90" s="2" t="s">
-        <v>252</v>
+      <c r="A90" s="4">
+        <v>100314</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D90" s="2">
-        <v>17.899999999999999</v>
-      </c>
-      <c r="E90" s="2">
-        <v>12.53</v>
-      </c>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J90" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D90" s="6">
+        <v>9.9</v>
+      </c>
+      <c r="E90" s="6">
+        <v>6.93</v>
+      </c>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="J90" s="8"/>
+      <c r="K90" s="9"/>
+      <c r="L90" s="9"/>
     </row>
     <row r="91" spans="1:13">
-      <c r="A91" s="2" t="s">
-        <v>256</v>
+      <c r="A91" s="4">
+        <v>100239</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D91" s="2">
-        <v>47</v>
-      </c>
-      <c r="E91" s="2">
-        <v>32.9</v>
-      </c>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J91" s="2"/>
-    </row>
-    <row r="92" spans="1:13">
-      <c r="A92" s="2" t="s">
-        <v>259</v>
+        <v>225</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D91" s="6">
+        <v>12.9</v>
+      </c>
+      <c r="E91" s="6">
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="F91" s="6"/>
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="J91" s="8"/>
+      <c r="K91" s="9"/>
+      <c r="L91" s="9"/>
+    </row>
+    <row r="92" spans="1:13" ht="18">
+      <c r="A92" s="17">
+        <v>120104</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D92" s="2">
-        <v>10.5</v>
-      </c>
-      <c r="E92" s="2">
-        <v>7.35</v>
-      </c>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="J92" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D92" s="6">
+        <v>20.5</v>
+      </c>
+      <c r="E92" s="6">
+        <v>14.35</v>
+      </c>
+      <c r="F92" s="6"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="J92" s="8"/>
+      <c r="K92" s="9"/>
+      <c r="L92" s="9"/>
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="2" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="D93" s="2">
-        <v>8.9</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="E93" s="2">
-        <v>6.23</v>
+        <v>12.53</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
       <c r="I93" s="3" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="J93" s="2"/>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="2" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>253</v>
+        <v>9</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="D94" s="2">
-        <v>12.9</v>
+        <v>47</v>
       </c>
       <c r="E94" s="2">
-        <v>9.0299999999999994</v>
+        <v>32.9</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="3" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="J94" s="2"/>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="2" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="D95" s="2">
-        <v>15.9</v>
+        <v>10.5</v>
       </c>
       <c r="E95" s="2">
-        <v>11.13</v>
+        <v>7.35</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="3" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="J95" s="2"/>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="2" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="D96" s="2">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="E96" s="2">
-        <v>6.93</v>
+        <v>6.23</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="3" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="J96" s="2"/>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="2" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D97" s="2">
-        <v>10.9</v>
+        <v>12.9</v>
       </c>
       <c r="E97" s="2">
-        <v>7.63</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="3" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="J97" s="2"/>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="2" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="D98" s="2">
-        <v>16.899999999999999</v>
+        <v>15.9</v>
       </c>
       <c r="E98" s="2">
-        <v>11.83</v>
+        <v>11.13</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="3" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="J98" s="2"/>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="2" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="D99" s="2">
-        <v>16.899999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="E99" s="2">
-        <v>11.83</v>
+        <v>6.93</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
       <c r="I99" s="3" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="J99" s="2"/>
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="2" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D100" s="2">
-        <v>11.9</v>
+        <v>10.9</v>
       </c>
       <c r="E100" s="2">
-        <v>8.33</v>
+        <v>7.63</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="3" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="J100" s="2"/>
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="2" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="D101" s="2">
-        <v>10.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E101" s="2">
-        <v>7.35</v>
+        <v>11.83</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="3" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="J101" s="2"/>
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="2" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>9</v>
+        <v>253</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D102" s="2">
-        <v>65</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E102" s="2">
-        <v>45.5</v>
+        <v>11.83</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
       <c r="I102" s="3" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="J102" s="2"/>
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="2" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="D103" s="2">
-        <v>8.9</v>
+        <v>11.9</v>
       </c>
       <c r="E103" s="2">
-        <v>6.23</v>
+        <v>8.33</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
       <c r="I103" s="3" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="J103" s="2"/>
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="2" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="D104" s="2">
-        <v>8.9</v>
+        <v>10.5</v>
       </c>
       <c r="E104" s="2">
-        <v>6.23</v>
+        <v>7.35</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
       <c r="I104" s="3" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="J104" s="2"/>
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="2" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>253</v>
+        <v>9</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D105" s="2">
-        <v>6.9</v>
+        <v>65</v>
       </c>
       <c r="E105" s="2">
-        <v>4.83</v>
+        <v>45.5</v>
       </c>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="3" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="J105" s="2"/>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="2" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D106" s="2">
-        <v>9.8000000000000007</v>
+        <v>8.9</v>
       </c>
       <c r="E106" s="2">
-        <v>6.86</v>
+        <v>6.23</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
       <c r="I106" s="3" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="J106" s="2"/>
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="2" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="D107" s="2">
         <v>8.9</v>
@@ -6411,859 +6441,859 @@
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
       <c r="I107" s="3" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="J107" s="2"/>
     </row>
     <row r="108" spans="1:10">
       <c r="A108" s="2" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="D108" s="2">
-        <v>9.8000000000000007</v>
+        <v>6.9</v>
       </c>
       <c r="E108" s="2">
-        <v>6.86</v>
+        <v>4.83</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
       <c r="I108" s="3" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="J108" s="2"/>
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="2" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D109" s="2">
-        <v>11.9</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="E109" s="2">
-        <v>8.33</v>
+        <v>6.86</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
       <c r="I109" s="3" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="J109" s="2"/>
     </row>
     <row r="110" spans="1:10">
       <c r="A110" s="2" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="D110" s="2">
-        <v>8.6999999999999993</v>
+        <v>8.9</v>
       </c>
       <c r="E110" s="2">
-        <v>6.09</v>
+        <v>6.23</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
       <c r="I110" s="3" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="J110" s="2"/>
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="2" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>9</v>
+        <v>253</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="D111" s="2">
-        <v>53</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="E111" s="2">
-        <v>37.1</v>
+        <v>6.86</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
       <c r="I111" s="3" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="J111" s="2"/>
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="2" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="D112" s="2">
-        <v>23.9</v>
+        <v>11.9</v>
       </c>
       <c r="E112" s="2">
-        <v>16.73</v>
+        <v>8.33</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
       <c r="I112" s="3" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="J112" s="2"/>
     </row>
     <row r="113" spans="1:10">
       <c r="A113" s="2" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="D113" s="2">
-        <v>17.899999999999999</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="E113" s="2">
-        <v>12.53</v>
+        <v>6.09</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
       <c r="I113" s="3" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="J113" s="2"/>
     </row>
     <row r="114" spans="1:10">
       <c r="A114" s="2" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>253</v>
+        <v>9</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D114" s="2">
-        <v>21.9</v>
+        <v>53</v>
       </c>
       <c r="E114" s="2">
-        <v>15.33</v>
+        <v>37.1</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
       <c r="I114" s="3" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="J114" s="2"/>
     </row>
     <row r="115" spans="1:10">
       <c r="A115" s="2" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="D115" s="2">
-        <v>8.9</v>
+        <v>23.9</v>
       </c>
       <c r="E115" s="2">
-        <v>6.23</v>
+        <v>16.73</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
       <c r="I115" s="3" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="J115" s="2"/>
     </row>
     <row r="116" spans="1:10">
       <c r="A116" s="2" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D116" s="2">
-        <v>16.899999999999999</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="E116" s="2">
-        <v>11.83</v>
+        <v>12.53</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
       <c r="I116" s="3" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="J116" s="2"/>
     </row>
     <row r="117" spans="1:10">
       <c r="A117" s="2" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="D117" s="2">
-        <v>16.899999999999999</v>
+        <v>21.9</v>
       </c>
       <c r="E117" s="2">
-        <v>11.83</v>
+        <v>15.33</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
       <c r="I117" s="3" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="J117" s="2"/>
     </row>
     <row r="118" spans="1:10">
       <c r="A118" s="2" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>1098</v>
+        <v>329</v>
       </c>
       <c r="D118" s="2">
-        <v>37</v>
+        <v>8.9</v>
       </c>
       <c r="E118" s="2">
-        <v>25.9</v>
+        <v>6.23</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
       <c r="I118" s="3" t="s">
-        <v>1099</v>
+        <v>330</v>
       </c>
       <c r="J118" s="2"/>
     </row>
     <row r="119" spans="1:10">
       <c r="A119" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="D119" s="2">
-        <v>10.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E119" s="2">
-        <v>7.35</v>
+        <v>11.83</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
       <c r="I119" s="3" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="J119" s="2"/>
     </row>
     <row r="120" spans="1:10">
       <c r="A120" s="2" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="D120" s="2">
-        <v>10.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E120" s="2">
-        <v>7.35</v>
+        <v>11.83</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
       <c r="I120" s="3" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="J120" s="2"/>
     </row>
     <row r="121" spans="1:10">
       <c r="A121" s="2" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>345</v>
+        <v>1098</v>
       </c>
       <c r="D121" s="2">
-        <v>6.9</v>
+        <v>37</v>
       </c>
       <c r="E121" s="2">
-        <v>4.83</v>
+        <v>25.9</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
       <c r="I121" s="3" t="s">
-        <v>346</v>
+        <v>1099</v>
       </c>
       <c r="J121" s="2"/>
     </row>
     <row r="122" spans="1:10">
       <c r="A122" s="2" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>9</v>
+        <v>253</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="D122" s="2">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="E122" s="2">
-        <v>17.5</v>
+        <v>7.35</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
       <c r="I122" s="3" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="J122" s="2"/>
     </row>
     <row r="123" spans="1:10">
       <c r="A123" s="2" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="D123" s="2">
-        <v>15.9</v>
+        <v>10.5</v>
       </c>
       <c r="E123" s="2">
-        <v>11.13</v>
+        <v>7.35</v>
       </c>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
       <c r="I123" s="3" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="J123" s="2"/>
     </row>
     <row r="124" spans="1:10">
       <c r="A124" s="2" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D124" s="2">
-        <v>15.9</v>
+        <v>6.9</v>
       </c>
       <c r="E124" s="2">
-        <v>11.13</v>
+        <v>4.83</v>
       </c>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
       <c r="I124" s="3" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="J124" s="2"/>
     </row>
     <row r="125" spans="1:10">
       <c r="A125" s="2" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>253</v>
+        <v>9</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D125" s="2">
-        <v>15.9</v>
+        <v>25</v>
       </c>
       <c r="E125" s="2">
-        <v>11.13</v>
+        <v>17.5</v>
       </c>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
       <c r="I125" s="3" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="J125" s="2"/>
     </row>
     <row r="126" spans="1:10">
       <c r="A126" s="2" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="D126" s="2">
-        <v>10.5</v>
+        <v>15.9</v>
       </c>
       <c r="E126" s="2">
-        <v>7.35</v>
+        <v>11.13</v>
       </c>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
       <c r="I126" s="3" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="J126" s="2"/>
     </row>
     <row r="127" spans="1:10">
       <c r="A127" s="2" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="D127" s="2">
-        <v>10.5</v>
+        <v>15.9</v>
       </c>
       <c r="E127" s="2">
-        <v>7.35</v>
+        <v>11.13</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
       <c r="I127" s="3" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="J127" s="2"/>
     </row>
     <row r="128" spans="1:10">
       <c r="A128" s="2" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="D128" s="2">
-        <v>11.9</v>
+        <v>15.9</v>
       </c>
       <c r="E128" s="2">
-        <v>8.33</v>
+        <v>11.13</v>
       </c>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
       <c r="I128" s="3" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="J128" s="2"/>
     </row>
     <row r="129" spans="1:10">
       <c r="A129" s="2" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="D129" s="2">
-        <v>6.5</v>
+        <v>10.5</v>
       </c>
       <c r="E129" s="2">
-        <v>4.55</v>
+        <v>7.35</v>
       </c>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
       <c r="I129" s="3" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J129" s="2"/>
     </row>
     <row r="130" spans="1:10">
       <c r="A130" s="2" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="D130" s="2">
-        <v>6.5</v>
+        <v>10.5</v>
       </c>
       <c r="E130" s="2">
-        <v>4.55</v>
+        <v>7.35</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
       <c r="I130" s="3" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="J130" s="2"/>
     </row>
     <row r="131" spans="1:10">
       <c r="A131" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="D131" s="2">
-        <v>5.7</v>
+        <v>11.9</v>
       </c>
       <c r="E131" s="2">
-        <v>3.99</v>
+        <v>8.33</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
       <c r="I131" s="3" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="J131" s="2"/>
     </row>
     <row r="132" spans="1:10">
       <c r="A132" s="2" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="D132" s="2">
-        <v>8.9</v>
+        <v>6.5</v>
       </c>
       <c r="E132" s="2">
-        <v>6.23</v>
+        <v>4.55</v>
       </c>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
       <c r="I132" s="3" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="J132" s="2"/>
     </row>
     <row r="133" spans="1:10">
       <c r="A133" s="2" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D133" s="2">
-        <v>8.9</v>
+        <v>6.5</v>
       </c>
       <c r="E133" s="2">
-        <v>6.23</v>
+        <v>4.55</v>
       </c>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
       <c r="I133" s="3" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="J133" s="2"/>
     </row>
     <row r="134" spans="1:10">
       <c r="A134" s="2" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="D134" s="2">
-        <v>7.9</v>
+        <v>5.7</v>
       </c>
       <c r="E134" s="2">
-        <v>5.53</v>
+        <v>3.99</v>
       </c>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
       <c r="I134" s="3" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="J134" s="2"/>
     </row>
     <row r="135" spans="1:10">
       <c r="A135" s="2" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="D135" s="2">
-        <v>10.5</v>
+        <v>8.9</v>
       </c>
       <c r="E135" s="2">
-        <v>7.35</v>
+        <v>6.23</v>
       </c>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
       <c r="I135" s="3" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="J135" s="2"/>
     </row>
     <row r="136" spans="1:10">
       <c r="A136" s="2" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="D136" s="2">
-        <v>10.1</v>
+        <v>8.9</v>
       </c>
       <c r="E136" s="2">
-        <v>7.07</v>
+        <v>6.23</v>
       </c>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
       <c r="I136" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="J136" s="2"/>
     </row>
     <row r="137" spans="1:10">
       <c r="A137" s="2" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="D137" s="2">
-        <v>9.9</v>
+        <v>7.9</v>
       </c>
       <c r="E137" s="2">
-        <v>6.93</v>
+        <v>5.53</v>
       </c>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
       <c r="I137" s="3" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="J137" s="2"/>
     </row>
     <row r="138" spans="1:10">
       <c r="A138" s="2" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D138" s="2">
-        <v>9.9</v>
+        <v>10.5</v>
       </c>
       <c r="E138" s="2">
-        <v>6.93</v>
+        <v>7.35</v>
       </c>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
       <c r="I138" s="3" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="J138" s="2"/>
     </row>
     <row r="139" spans="1:10">
       <c r="A139" s="2" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="D139" s="2">
-        <v>7.9</v>
+        <v>10.1</v>
       </c>
       <c r="E139" s="2">
-        <v>5.53</v>
+        <v>7.07</v>
       </c>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
       <c r="I139" s="3" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="J139" s="2"/>
     </row>
     <row r="140" spans="1:10">
       <c r="A140" s="2" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="D140" s="2">
-        <v>7.9</v>
+        <v>9.9</v>
       </c>
       <c r="E140" s="2">
-        <v>5.53</v>
+        <v>6.93</v>
       </c>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
       <c r="I140" s="3" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="J140" s="2"/>
     </row>
     <row r="141" spans="1:10">
       <c r="A141" s="2" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="D141" s="2">
-        <v>7.9</v>
+        <v>9.9</v>
       </c>
       <c r="E141" s="2">
-        <v>5.53</v>
+        <v>6.93</v>
       </c>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
       <c r="I141" s="3" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="J141" s="2"/>
     </row>
     <row r="142" spans="1:10">
       <c r="A142" s="2" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="D142" s="2">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="E142" s="2">
-        <v>6.23</v>
+        <v>5.53</v>
       </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
       <c r="I142" s="3" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="J142" s="2"/>
     </row>
     <row r="143" spans="1:10">
       <c r="A143" s="2" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="D143" s="2">
         <v>7.9</v>
@@ -7275,307 +7305,307 @@
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
       <c r="I143" s="3" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="J143" s="2"/>
     </row>
     <row r="144" spans="1:10">
       <c r="A144" s="2" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="D144" s="2">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="E144" s="2">
-        <v>5.95</v>
+        <v>5.53</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
       <c r="I144" s="3" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="J144" s="2"/>
     </row>
     <row r="145" spans="1:10">
       <c r="A145" s="2" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="D145" s="2">
-        <v>6.5</v>
+        <v>8.9</v>
       </c>
       <c r="E145" s="2">
-        <v>4.55</v>
+        <v>6.23</v>
       </c>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
       <c r="I145" s="3" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J145" s="2"/>
     </row>
     <row r="146" spans="1:10">
       <c r="A146" s="2" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="D146" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="E146" s="2">
-        <v>5.46</v>
+        <v>5.53</v>
       </c>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
       <c r="I146" s="3" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="J146" s="2"/>
     </row>
     <row r="147" spans="1:10">
       <c r="A147" s="2" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="D147" s="2">
-        <v>6.9</v>
+        <v>8.5</v>
       </c>
       <c r="E147" s="2">
-        <v>4.83</v>
+        <v>5.95</v>
       </c>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
       <c r="I147" s="3" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="J147" s="2"/>
     </row>
     <row r="148" spans="1:10">
       <c r="A148" s="2" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>426</v>
+        <v>253</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="D148" s="2">
-        <v>4.9000000000000004</v>
+        <v>6.5</v>
       </c>
       <c r="E148" s="2">
-        <v>3.43</v>
+        <v>4.55</v>
       </c>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
       <c r="I148" s="3" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="J148" s="2"/>
     </row>
     <row r="149" spans="1:10">
       <c r="A149" s="2" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>430</v>
+        <v>253</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="D149" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="E149" s="2">
-        <v>5.53</v>
+        <v>5.46</v>
       </c>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
       <c r="I149" s="3" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="J149" s="2"/>
     </row>
     <row r="150" spans="1:10">
       <c r="A150" s="2" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>430</v>
+        <v>253</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="D150" s="2">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="E150" s="2">
-        <v>7.63</v>
+        <v>4.83</v>
       </c>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
       <c r="I150" s="3" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="J150" s="2"/>
     </row>
     <row r="151" spans="1:10">
       <c r="A151" s="2" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D151" s="2">
-        <v>2.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E151" s="2">
-        <v>2.0299999999999998</v>
+        <v>3.43</v>
       </c>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
       <c r="I151" s="3" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="J151" s="2"/>
     </row>
     <row r="152" spans="1:10">
       <c r="A152" s="2" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>430</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="D152" s="2">
-        <v>10.9</v>
+        <v>7.9</v>
       </c>
       <c r="E152" s="2">
-        <v>7.63</v>
+        <v>5.53</v>
       </c>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
       <c r="I152" s="3" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="J152" s="2"/>
     </row>
     <row r="153" spans="1:10">
       <c r="A153" s="2" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>207</v>
+        <v>430</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="D153" s="2">
-        <v>4.5</v>
+        <v>10.9</v>
       </c>
       <c r="E153" s="2">
-        <v>3.15</v>
+        <v>7.63</v>
       </c>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
       <c r="I153" s="3" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="J153" s="2"/>
     </row>
     <row r="154" spans="1:10">
       <c r="A154" s="2" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>207</v>
+        <v>430</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="D154" s="2">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="E154" s="2">
-        <v>3.15</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
       <c r="I154" s="3" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="J154" s="2"/>
     </row>
     <row r="155" spans="1:10">
       <c r="A155" s="2" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>207</v>
+        <v>430</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="D155" s="2">
-        <v>4.8</v>
+        <v>10.9</v>
       </c>
       <c r="E155" s="2">
-        <v>3.36</v>
+        <v>7.63</v>
       </c>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
       <c r="I155" s="3" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="J155" s="2"/>
     </row>
     <row r="156" spans="1:10">
       <c r="A156" s="2" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="D156" s="2">
         <v>4.5</v>
@@ -7587,235 +7617,235 @@
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
       <c r="I156" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="J156" s="2"/>
     </row>
     <row r="157" spans="1:10">
       <c r="A157" s="2" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="D157" s="2">
-        <v>7.9</v>
+        <v>4.5</v>
       </c>
       <c r="E157" s="2">
-        <v>5.53</v>
+        <v>3.15</v>
       </c>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
       <c r="I157" s="3" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="J157" s="2"/>
     </row>
     <row r="158" spans="1:10">
       <c r="A158" s="2" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="D158" s="2">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="E158" s="2">
-        <v>4.55</v>
+        <v>3.36</v>
       </c>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
       <c r="I158" s="3" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="J158" s="2"/>
     </row>
     <row r="159" spans="1:10">
       <c r="A159" s="2" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="D159" s="2">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="E159" s="2">
-        <v>4.55</v>
+        <v>3.15</v>
       </c>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
       <c r="I159" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="J159" s="2"/>
     </row>
     <row r="160" spans="1:10">
       <c r="A160" s="2" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="D160" s="2">
-        <v>9.9</v>
+        <v>7.9</v>
       </c>
       <c r="E160" s="2">
-        <v>6.93</v>
+        <v>5.53</v>
       </c>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
       <c r="I160" s="3" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="J160" s="2"/>
     </row>
     <row r="161" spans="1:10">
       <c r="A161" s="2" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>9</v>
+        <v>207</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>1100</v>
+        <v>458</v>
       </c>
       <c r="D161" s="2">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="E161" s="2">
-        <v>8.75</v>
+        <v>4.55</v>
       </c>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
       <c r="I161" s="3" t="s">
-        <v>1101</v>
+        <v>459</v>
       </c>
       <c r="J161" s="2"/>
     </row>
     <row r="162" spans="1:10">
       <c r="A162" s="2" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="D162" s="2">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="E162" s="2">
-        <v>4.13</v>
+        <v>4.55</v>
       </c>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
       <c r="I162" s="3" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="J162" s="2"/>
     </row>
     <row r="163" spans="1:10">
       <c r="A163" s="2" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="D163" s="2">
-        <v>8.9</v>
+        <v>9.9</v>
       </c>
       <c r="E163" s="2">
-        <v>6.23</v>
+        <v>6.93</v>
       </c>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
       <c r="I163" s="3" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="J163" s="2"/>
     </row>
     <row r="164" spans="1:10">
       <c r="A164" s="2" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>207</v>
+        <v>9</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>474</v>
+        <v>1100</v>
       </c>
       <c r="D164" s="2">
-        <v>10.9</v>
+        <v>12.5</v>
       </c>
       <c r="E164" s="2">
-        <v>7.63</v>
+        <v>8.75</v>
       </c>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
       <c r="I164" s="3" t="s">
-        <v>475</v>
+        <v>1101</v>
       </c>
       <c r="J164" s="2"/>
     </row>
     <row r="165" spans="1:10">
       <c r="A165" s="2" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="D165" s="2">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="E165" s="2">
-        <v>4.83</v>
+        <v>4.13</v>
       </c>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
       <c r="I165" s="3" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="J165" s="2"/>
     </row>
     <row r="166" spans="1:10">
       <c r="A166" s="2" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="D166" s="2">
         <v>8.9</v>
@@ -7827,139 +7857,139 @@
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
       <c r="I166" s="3" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="J166" s="2"/>
     </row>
     <row r="167" spans="1:10">
       <c r="A167" s="2" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="D167" s="2">
-        <v>11.3</v>
+        <v>10.9</v>
       </c>
       <c r="E167" s="2">
-        <v>7.91</v>
+        <v>7.63</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
       <c r="I167" s="3" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="J167" s="2"/>
     </row>
     <row r="168" spans="1:10">
       <c r="A168" s="2" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="D168" s="2">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="E168" s="2">
-        <v>5.25</v>
+        <v>4.83</v>
       </c>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
       <c r="I168" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="J168" s="2"/>
     </row>
     <row r="169" spans="1:10">
       <c r="A169" s="2" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="D169" s="2">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="E169" s="2">
-        <v>5.25</v>
+        <v>6.23</v>
       </c>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
       <c r="I169" s="3" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="J169" s="2"/>
     </row>
     <row r="170" spans="1:10">
       <c r="A170" s="2" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="D170" s="2">
-        <v>6.9</v>
+        <v>11.3</v>
       </c>
       <c r="E170" s="2">
-        <v>4.83</v>
+        <v>7.91</v>
       </c>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
       <c r="I170" s="3" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="J170" s="2"/>
     </row>
     <row r="171" spans="1:10">
       <c r="A171" s="2" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="D171" s="2">
-        <v>5.9</v>
+        <v>7.5</v>
       </c>
       <c r="E171" s="2">
-        <v>4.13</v>
+        <v>5.25</v>
       </c>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
       <c r="I171" s="3" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="J171" s="2"/>
     </row>
     <row r="172" spans="1:10">
       <c r="A172" s="2" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="D172" s="2">
         <v>7.5</v>
@@ -7971,43 +8001,43 @@
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
       <c r="I172" s="3" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="J172" s="2"/>
     </row>
     <row r="173" spans="1:10">
       <c r="A173" s="2" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="D173" s="2">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="E173" s="2">
-        <v>5.53</v>
+        <v>4.83</v>
       </c>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
       <c r="I173" s="3" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="J173" s="2"/>
     </row>
     <row r="174" spans="1:10">
       <c r="A174" s="2" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="D174" s="2">
         <v>5.9</v>
@@ -8019,427 +8049,427 @@
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
       <c r="I174" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="J174" s="2"/>
     </row>
     <row r="175" spans="1:10">
       <c r="A175" s="2" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="D175" s="2">
-        <v>12.9</v>
+        <v>7.5</v>
       </c>
       <c r="E175" s="2">
-        <v>9.0299999999999994</v>
+        <v>5.25</v>
       </c>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
       <c r="I175" s="3" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="J175" s="2"/>
     </row>
     <row r="176" spans="1:10">
       <c r="A176" s="2" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="D176" s="2">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="E176" s="2">
-        <v>5.95</v>
+        <v>5.53</v>
       </c>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
       <c r="I176" s="3" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="J176" s="2"/>
     </row>
     <row r="177" spans="1:10">
       <c r="A177" s="2" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="D177" s="2">
-        <v>4.9000000000000004</v>
+        <v>5.9</v>
       </c>
       <c r="E177" s="2">
-        <v>3.43</v>
+        <v>4.13</v>
       </c>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
       <c r="I177" s="3" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="J177" s="2"/>
     </row>
     <row r="178" spans="1:10">
       <c r="A178" s="2" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="D178" s="2">
-        <v>5.9</v>
+        <v>12.9</v>
       </c>
       <c r="E178" s="2">
-        <v>4.13</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
       <c r="I178" s="3" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="J178" s="2"/>
     </row>
     <row r="179" spans="1:10">
       <c r="A179" s="2" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="D179" s="2">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="E179" s="2">
-        <v>4.2</v>
+        <v>5.95</v>
       </c>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
       <c r="I179" s="3" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="J179" s="2"/>
     </row>
     <row r="180" spans="1:10">
       <c r="A180" s="2" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="D180" s="2">
-        <v>5.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E180" s="2">
-        <v>4.13</v>
+        <v>3.43</v>
       </c>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
       <c r="I180" s="3" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="J180" s="2"/>
     </row>
     <row r="181" spans="1:10">
       <c r="A181" s="2" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="D181" s="2">
-        <v>10.9</v>
+        <v>5.9</v>
       </c>
       <c r="E181" s="2">
-        <v>7.63</v>
+        <v>4.13</v>
       </c>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
       <c r="I181" s="3" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="J181" s="2"/>
     </row>
     <row r="182" spans="1:10">
       <c r="A182" s="2" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="D182" s="2">
-        <v>16.600000000000001</v>
+        <v>6</v>
       </c>
       <c r="E182" s="2">
-        <v>7.63</v>
+        <v>4.2</v>
       </c>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
       <c r="I182" s="3" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="J182" s="2"/>
     </row>
     <row r="183" spans="1:10">
       <c r="A183" s="2" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="D183" s="2">
-        <v>12.9</v>
+        <v>5.9</v>
       </c>
       <c r="E183" s="2">
-        <v>11.62</v>
+        <v>4.13</v>
       </c>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
       <c r="I183" s="3" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="J183" s="2"/>
     </row>
     <row r="184" spans="1:10">
       <c r="A184" s="2" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="D184" s="2">
-        <v>6.9</v>
+        <v>10.9</v>
       </c>
       <c r="E184" s="2">
-        <v>4.83</v>
+        <v>7.63</v>
       </c>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
       <c r="I184" s="3" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="J184" s="2"/>
     </row>
     <row r="185" spans="1:10">
       <c r="A185" s="2" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="D185" s="2">
-        <v>7.9</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="E185" s="2">
-        <v>5.53</v>
+        <v>7.63</v>
       </c>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
       <c r="I185" s="3" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="J185" s="2"/>
     </row>
     <row r="186" spans="1:10">
       <c r="A186" s="2" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="D186" s="2">
-        <v>6.9</v>
+        <v>12.9</v>
       </c>
       <c r="E186" s="2">
-        <v>4.83</v>
+        <v>11.62</v>
       </c>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
       <c r="I186" s="3" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="J186" s="2"/>
     </row>
     <row r="187" spans="1:10">
       <c r="A187" s="2" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="D187" s="2">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="E187" s="2">
-        <v>4.2</v>
+        <v>4.83</v>
       </c>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
       <c r="I187" s="3" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="J187" s="2"/>
     </row>
     <row r="188" spans="1:10">
       <c r="A188" s="2" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="D188" s="2">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="E188" s="2">
-        <v>4.9000000000000004</v>
+        <v>5.53</v>
       </c>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
       <c r="I188" s="3" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="J188" s="2"/>
     </row>
     <row r="189" spans="1:10">
       <c r="A189" s="2" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="D189" s="2">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
       <c r="E189" s="2">
-        <v>6.23</v>
+        <v>4.83</v>
       </c>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
       <c r="I189" s="3" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="J189" s="2"/>
     </row>
     <row r="190" spans="1:10">
       <c r="A190" s="2" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="D190" s="2">
-        <v>11.9</v>
+        <v>6</v>
       </c>
       <c r="E190" s="2">
-        <v>8.33</v>
+        <v>4.2</v>
       </c>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
       <c r="I190" s="3" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="J190" s="2"/>
     </row>
     <row r="191" spans="1:10">
       <c r="A191" s="2" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="D191" s="2">
-        <v>9.9</v>
+        <v>7</v>
       </c>
       <c r="E191" s="2">
-        <v>6.93</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
       <c r="I191" s="3" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="J191" s="2"/>
     </row>
     <row r="192" spans="1:10">
       <c r="A192" s="2" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="D192" s="2">
         <v>8.9</v>
@@ -8451,211 +8481,211 @@
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
       <c r="I192" s="3" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="J192" s="2"/>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:10">
       <c r="A193" s="2" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="D193" s="2">
-        <v>9.9</v>
+        <v>11.9</v>
       </c>
       <c r="E193" s="2">
-        <v>6.93</v>
+        <v>8.33</v>
       </c>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
       <c r="I193" s="3" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="J193" s="2"/>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:10">
       <c r="A194" s="2" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="D194" s="2">
-        <v>4.5</v>
+        <v>9.9</v>
       </c>
       <c r="E194" s="2">
-        <v>3.15</v>
+        <v>6.93</v>
       </c>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="3" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="J194" s="2"/>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:10">
       <c r="A195" s="2" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="D195" s="2">
-        <v>4.5</v>
+        <v>8.9</v>
       </c>
       <c r="E195" s="2">
-        <v>3.15</v>
+        <v>6.23</v>
       </c>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
       <c r="I195" s="3" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="J195" s="2"/>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:10">
       <c r="A196" s="2" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="D196" s="2">
-        <v>6.5</v>
+        <v>9.9</v>
       </c>
       <c r="E196" s="2">
-        <v>4.55</v>
+        <v>6.93</v>
       </c>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
       <c r="I196" s="3" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="J196" s="2"/>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:10">
       <c r="A197" s="2" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="D197" s="2">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="E197" s="2">
-        <v>4.55</v>
+        <v>3.15</v>
       </c>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
       <c r="I197" s="3" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="J197" s="2"/>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:10">
       <c r="A198" s="2" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="D198" s="2">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="E198" s="2">
-        <v>4.55</v>
+        <v>3.15</v>
       </c>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
       <c r="I198" s="3" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="J198" s="2"/>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:10">
       <c r="A199" s="2" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="D199" s="2">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="E199" s="2">
-        <v>2.73</v>
+        <v>4.55</v>
       </c>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
       <c r="I199" s="3" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="J199" s="2"/>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:10">
       <c r="A200" s="2" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="D200" s="2">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="E200" s="2">
-        <v>2.73</v>
+        <v>4.55</v>
       </c>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
       <c r="I200" s="3" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="J200" s="2"/>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:10">
       <c r="A201" s="2" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="D201" s="2">
         <v>6.5</v>
@@ -8666,310 +8696,310 @@
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
-      <c r="I201" s="11" t="s">
-        <v>1125</v>
+      <c r="I201" s="3" t="s">
+        <v>577</v>
       </c>
       <c r="J201" s="2"/>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:10">
       <c r="A202" s="2" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="D202" s="2">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="E202" s="2">
-        <v>4.13</v>
+        <v>2.73</v>
       </c>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
       <c r="I202" s="3" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="J202" s="2"/>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:10">
       <c r="A203" s="2" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="D203" s="2">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="E203" s="2">
-        <v>3.85</v>
+        <v>2.73</v>
       </c>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
-      <c r="I203" s="11" t="s">
-        <v>1124</v>
+      <c r="I203" s="3" t="s">
+        <v>583</v>
       </c>
       <c r="J203" s="2"/>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:10">
       <c r="A204" s="2" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="D204" s="2">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="E204" s="2">
-        <v>3.36</v>
+        <v>4.55</v>
       </c>
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
-      <c r="I204" s="3" t="s">
-        <v>593</v>
+      <c r="I204" s="11" t="s">
+        <v>1125</v>
       </c>
       <c r="J204" s="2"/>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:10">
       <c r="A205" s="2" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="D205" s="2">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="E205" s="2">
-        <v>4.83</v>
+        <v>4.13</v>
       </c>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
       <c r="I205" s="3" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="J205" s="2"/>
     </row>
-    <row r="206" spans="1:11">
-      <c r="A206" s="6" t="s">
-        <v>597</v>
-      </c>
-      <c r="B206" s="6" t="s">
+    <row r="206" spans="1:10">
+      <c r="A206" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B206" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C206" s="6" t="s">
-        <v>598</v>
-      </c>
-      <c r="D206" s="6">
+      <c r="C206" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="D206" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="E206" s="2">
+        <v>3.85</v>
+      </c>
+      <c r="F206" s="2"/>
+      <c r="G206" s="2"/>
+      <c r="H206" s="2"/>
+      <c r="I206" s="11" t="s">
+        <v>1124</v>
+      </c>
+      <c r="J206" s="2"/>
+    </row>
+    <row r="207" spans="1:10">
+      <c r="A207" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="D207" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="E207" s="2">
+        <v>3.36</v>
+      </c>
+      <c r="F207" s="2"/>
+      <c r="G207" s="2"/>
+      <c r="H207" s="2"/>
+      <c r="I207" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="J207" s="2"/>
+    </row>
+    <row r="208" spans="1:10">
+      <c r="A208" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D208" s="2">
         <v>6.9</v>
       </c>
-      <c r="E206" s="6">
+      <c r="E208" s="2">
         <v>4.83</v>
-      </c>
-      <c r="F206" s="6"/>
-      <c r="G206" s="6"/>
-      <c r="H206" s="6"/>
-      <c r="I206" s="7" t="s">
-        <v>599</v>
-      </c>
-      <c r="J206" s="8"/>
-      <c r="K206" s="9"/>
-    </row>
-    <row r="207" spans="1:11">
-      <c r="A207" s="5">
-        <v>70109</v>
-      </c>
-      <c r="B207" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C207" s="6" t="s">
-        <v>600</v>
-      </c>
-      <c r="D207" s="6">
-        <v>10.9</v>
-      </c>
-      <c r="E207" s="6">
-        <v>7.63</v>
-      </c>
-      <c r="F207" s="6"/>
-      <c r="G207" s="6"/>
-      <c r="H207" s="6"/>
-      <c r="I207" s="7" t="s">
-        <v>601</v>
-      </c>
-      <c r="J207" s="8"/>
-      <c r="K207" s="9"/>
-    </row>
-    <row r="208" spans="1:11">
-      <c r="A208" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="D208" s="2">
-        <v>5</v>
-      </c>
-      <c r="E208" s="2">
-        <v>3.5</v>
       </c>
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
       <c r="I208" s="3" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="J208" s="2"/>
     </row>
-    <row r="209" spans="1:10">
-      <c r="A209" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="D209" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="E209" s="2">
-        <v>6.65</v>
-      </c>
-      <c r="F209" s="2"/>
-      <c r="G209" s="2"/>
-      <c r="H209" s="2"/>
-      <c r="I209" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="J209" s="2"/>
-    </row>
-    <row r="210" spans="1:10">
-      <c r="A210" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="D210" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="E210" s="2">
-        <v>6.65</v>
-      </c>
-      <c r="F210" s="2"/>
-      <c r="G210" s="2"/>
-      <c r="H210" s="2"/>
-      <c r="I210" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="J210" s="2"/>
-    </row>
-    <row r="211" spans="1:10">
+    <row r="209" spans="1:11">
+      <c r="A209" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C209" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="D209" s="6">
+        <v>6.9</v>
+      </c>
+      <c r="E209" s="6">
+        <v>4.83</v>
+      </c>
+      <c r="F209" s="6"/>
+      <c r="G209" s="6"/>
+      <c r="H209" s="6"/>
+      <c r="I209" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="J209" s="8"/>
+      <c r="K209" s="9"/>
+    </row>
+    <row r="210" spans="1:11">
+      <c r="A210" s="5">
+        <v>70109</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="D210" s="6">
+        <v>10.9</v>
+      </c>
+      <c r="E210" s="6">
+        <v>7.63</v>
+      </c>
+      <c r="F210" s="6"/>
+      <c r="G210" s="6"/>
+      <c r="H210" s="6"/>
+      <c r="I210" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="J210" s="8"/>
+      <c r="K210" s="9"/>
+    </row>
+    <row r="211" spans="1:11">
       <c r="A211" s="2" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>207</v>
+        <v>430</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="D211" s="2">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="E211" s="2">
-        <v>0.84</v>
+        <v>3.5</v>
       </c>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
       <c r="I211" s="3" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="J211" s="2"/>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" spans="1:11">
       <c r="A212" s="2" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>207</v>
+        <v>426</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="D212" s="2">
-        <v>1.2</v>
+        <v>9.5</v>
       </c>
       <c r="E212" s="2">
-        <v>0.84</v>
+        <v>6.65</v>
       </c>
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
       <c r="I212" s="3" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="J212" s="2"/>
     </row>
-    <row r="213" spans="1:10">
+    <row r="213" spans="1:11">
       <c r="A213" s="2" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>207</v>
+        <v>426</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="D213" s="2">
-        <v>1.2</v>
+        <v>9.5</v>
       </c>
       <c r="E213" s="2">
-        <v>0.84</v>
+        <v>6.65</v>
       </c>
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
       <c r="I213" s="3" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="J213" s="2"/>
     </row>
-    <row r="214" spans="1:10">
+    <row r="214" spans="1:11">
       <c r="A214" s="2" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="D214" s="2">
         <v>1.2</v>
@@ -8981,497 +9011,497 @@
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
       <c r="I214" s="3" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="J214" s="2"/>
     </row>
-    <row r="215" spans="1:10">
+    <row r="215" spans="1:11">
       <c r="A215" s="2" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>9</v>
+        <v>207</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="D215" s="2">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="E215" s="2">
-        <v>3.15</v>
+        <v>0.84</v>
       </c>
       <c r="F215" s="2"/>
       <c r="G215" s="2"/>
       <c r="H215" s="2"/>
       <c r="I215" s="3" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="J215" s="2"/>
     </row>
-    <row r="216" spans="1:10">
-      <c r="A216" s="2">
-        <v>21710</v>
-      </c>
-      <c r="B216" s="12" t="s">
+    <row r="216" spans="1:11">
+      <c r="A216" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="B216" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C216" s="12" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D216" s="2"/>
+      <c r="C216" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D216" s="2">
+        <v>1.2</v>
+      </c>
       <c r="E216" s="2">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="F216" s="11"/>
+        <v>0.84</v>
+      </c>
+      <c r="F216" s="2"/>
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
-      <c r="I216" s="11" t="s">
-        <v>1122</v>
+      <c r="I216" s="3" t="s">
+        <v>619</v>
       </c>
       <c r="J216" s="2"/>
     </row>
-    <row r="217" spans="1:10">
-      <c r="A217" s="2">
-        <v>21709</v>
-      </c>
-      <c r="B217" s="12" t="s">
+    <row r="217" spans="1:11">
+      <c r="A217" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B217" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>1118</v>
+        <v>621</v>
       </c>
       <c r="D217" s="2">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="E217" s="2">
-        <v>2.4500000000000002</v>
+        <v>0.84</v>
       </c>
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
       <c r="I217" s="3" t="s">
-        <v>1121</v>
+        <v>622</v>
       </c>
       <c r="J217" s="2"/>
     </row>
-    <row r="218" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A218" s="2">
-        <v>21708</v>
-      </c>
-      <c r="B218" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="C218" s="16" t="s">
-        <v>1119</v>
+    <row r="218" spans="1:11">
+      <c r="A218" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>624</v>
       </c>
       <c r="D218" s="2">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E218" s="2">
-        <v>2.4500000000000002</v>
+        <v>3.15</v>
       </c>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
       <c r="I218" s="3" t="s">
-        <v>1123</v>
+        <v>625</v>
       </c>
       <c r="J218" s="2"/>
     </row>
-    <row r="219" spans="1:10">
-      <c r="A219" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="B219" s="2" t="s">
+    <row r="219" spans="1:11">
+      <c r="A219" s="2">
+        <v>21710</v>
+      </c>
+      <c r="B219" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="C219" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="D219" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="C219" s="12" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D219" s="2"/>
       <c r="E219" s="2">
-        <v>1.05</v>
-      </c>
-      <c r="F219" s="2"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F219" s="11"/>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
-      <c r="I219" s="3" t="s">
-        <v>628</v>
+      <c r="I219" s="11" t="s">
+        <v>1122</v>
       </c>
       <c r="J219" s="2"/>
     </row>
-    <row r="220" spans="1:10">
-      <c r="A220" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>630</v>
+    <row r="220" spans="1:11">
+      <c r="A220" s="2">
+        <v>21709</v>
+      </c>
+      <c r="B220" s="12" t="s">
+        <v>207</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>631</v>
+        <v>1118</v>
       </c>
       <c r="D220" s="2">
-        <v>7.9</v>
+        <v>3.5</v>
       </c>
       <c r="E220" s="2">
-        <v>5.53</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
       <c r="I220" s="3" t="s">
-        <v>632</v>
+        <v>1121</v>
       </c>
       <c r="J220" s="2"/>
     </row>
-    <row r="221" spans="1:10">
-      <c r="A221" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>634</v>
+    <row r="221" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A221" s="2">
+        <v>21708</v>
+      </c>
+      <c r="B221" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C221" s="16" t="s">
+        <v>1119</v>
       </c>
       <c r="D221" s="2">
-        <v>7.9</v>
+        <v>3.5</v>
       </c>
       <c r="E221" s="2">
-        <v>5.53</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
       <c r="I221" s="3" t="s">
-        <v>635</v>
+        <v>1123</v>
       </c>
       <c r="J221" s="2"/>
     </row>
-    <row r="222" spans="1:10">
+    <row r="222" spans="1:11">
       <c r="A222" s="2" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>630</v>
+        <v>207</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="D222" s="2">
-        <v>7.9</v>
+        <v>1.5</v>
       </c>
       <c r="E222" s="2">
-        <v>5.53</v>
+        <v>1.05</v>
       </c>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
       <c r="I222" s="3" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="J222" s="2"/>
     </row>
-    <row r="223" spans="1:10">
+    <row r="223" spans="1:11">
       <c r="A223" s="2" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="D223" s="2">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="E223" s="2">
-        <v>4.83</v>
+        <v>5.53</v>
       </c>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
       <c r="I223" s="3" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="J223" s="2"/>
     </row>
-    <row r="224" spans="1:10">
+    <row r="224" spans="1:11">
       <c r="A224" s="2" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="D224" s="2">
-        <v>11.9</v>
+        <v>7.9</v>
       </c>
       <c r="E224" s="2">
-        <v>8.33</v>
+        <v>5.53</v>
       </c>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
       <c r="I224" s="3" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="J224" s="2"/>
     </row>
     <row r="225" spans="1:13">
       <c r="A225" s="2" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="D225" s="2">
-        <v>0.9</v>
+        <v>7.9</v>
       </c>
       <c r="E225" s="2">
-        <v>0.9</v>
+        <v>5.53</v>
       </c>
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
       <c r="I225" s="3" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="J225" s="2"/>
     </row>
     <row r="226" spans="1:13">
       <c r="A226" s="2" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="D226" s="2">
-        <v>0.9</v>
+        <v>6.9</v>
       </c>
       <c r="E226" s="2">
-        <v>0.9</v>
+        <v>4.83</v>
       </c>
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
       <c r="I226" s="3" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="J226" s="2"/>
     </row>
     <row r="227" spans="1:13">
       <c r="A227" s="2" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="D227" s="2">
-        <v>6.9</v>
+        <v>11.9</v>
       </c>
       <c r="E227" s="2">
-        <v>4.83</v>
+        <v>8.33</v>
       </c>
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
       <c r="I227" s="3" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="J227" s="2"/>
     </row>
     <row r="228" spans="1:13">
       <c r="A228" s="2" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="D228" s="2">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="E228" s="2">
-        <v>4.83</v>
+        <v>0.9</v>
       </c>
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
       <c r="I228" s="3" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="J228" s="2"/>
     </row>
     <row r="229" spans="1:13">
       <c r="A229" s="2" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="D229" s="2">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="E229" s="2">
-        <v>7.63</v>
+        <v>0.9</v>
       </c>
       <c r="F229" s="2"/>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
       <c r="I229" s="3" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="J229" s="2"/>
     </row>
     <row r="230" spans="1:13">
       <c r="A230" s="2" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="D230" s="2">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="E230" s="2">
-        <v>5.53</v>
+        <v>4.83</v>
       </c>
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
       <c r="I230" s="3" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="J230" s="2"/>
     </row>
     <row r="231" spans="1:13">
       <c r="A231" s="2" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="D231" s="2">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="E231" s="2">
-        <v>7.63</v>
+        <v>4.83</v>
       </c>
       <c r="F231" s="2"/>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
       <c r="I231" s="3" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="J231" s="2"/>
     </row>
     <row r="232" spans="1:13">
       <c r="A232" s="2" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="D232" s="2">
-        <v>1</v>
+        <v>10.9</v>
       </c>
       <c r="E232" s="2">
-        <v>1</v>
+        <v>7.63</v>
       </c>
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
       <c r="I232" s="3" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="J232" s="2"/>
     </row>
     <row r="233" spans="1:13">
       <c r="A233" s="2" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>670</v>
+        <v>661</v>
       </c>
       <c r="D233" s="2">
-        <v>16.899999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="E233" s="2">
-        <v>11.83</v>
+        <v>5.53</v>
       </c>
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
       <c r="I233" s="3" t="s">
-        <v>671</v>
+        <v>662</v>
       </c>
       <c r="J233" s="2"/>
     </row>
     <row r="234" spans="1:13">
       <c r="A234" s="2" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="D234" s="2">
-        <v>16.899999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="E234" s="2">
-        <v>11.83</v>
+        <v>7.63</v>
       </c>
       <c r="F234" s="2"/>
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
       <c r="I234" s="3" t="s">
-        <v>674</v>
+        <v>665</v>
       </c>
       <c r="J234" s="2"/>
     </row>
     <row r="235" spans="1:13">
       <c r="A235" s="2" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>676</v>
+        <v>667</v>
       </c>
       <c r="D235" s="2">
         <v>1</v>
@@ -9483,526 +9513,526 @@
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
       <c r="I235" s="3" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="J235" s="2"/>
     </row>
     <row r="236" spans="1:13">
-      <c r="A236" s="5">
-        <v>30802</v>
-      </c>
-      <c r="B236" s="6" t="s">
+      <c r="A236" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="B236" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="C236" s="6" t="s">
-        <v>678</v>
-      </c>
-      <c r="D236" s="6">
-        <v>7.9</v>
-      </c>
-      <c r="E236" s="6">
-        <v>5.53</v>
-      </c>
-      <c r="F236" s="6"/>
-      <c r="G236" s="6"/>
-      <c r="H236" s="6"/>
-      <c r="I236" s="7" t="s">
-        <v>679</v>
-      </c>
-      <c r="J236" s="8"/>
-      <c r="K236" s="9"/>
-      <c r="L236" s="9"/>
-      <c r="M236" s="9"/>
+      <c r="C236" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="D236" s="2">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="E236" s="2">
+        <v>11.83</v>
+      </c>
+      <c r="F236" s="2"/>
+      <c r="G236" s="2"/>
+      <c r="H236" s="2"/>
+      <c r="I236" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="J236" s="2"/>
     </row>
     <row r="237" spans="1:13">
       <c r="A237" s="2" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="D237" s="2">
-        <v>7.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E237" s="2">
-        <v>5.53</v>
+        <v>11.83</v>
       </c>
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
       <c r="I237" s="3" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="J237" s="2"/>
     </row>
     <row r="238" spans="1:13">
       <c r="A238" s="2" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="D238" s="2">
-        <v>9.5</v>
+        <v>1</v>
       </c>
       <c r="E238" s="2">
-        <v>6.65</v>
+        <v>1</v>
       </c>
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
       <c r="I238" s="3" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="J238" s="2"/>
     </row>
     <row r="239" spans="1:13">
-      <c r="A239" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="B239" s="2" t="s">
+      <c r="A239" s="5">
+        <v>30802</v>
+      </c>
+      <c r="B239" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="C239" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="D239" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="E239" s="2">
-        <v>6.65</v>
-      </c>
-      <c r="F239" s="2"/>
-      <c r="G239" s="2"/>
-      <c r="H239" s="2"/>
-      <c r="I239" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="J239" s="2"/>
+      <c r="C239" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="D239" s="6">
+        <v>7.9</v>
+      </c>
+      <c r="E239" s="6">
+        <v>5.53</v>
+      </c>
+      <c r="F239" s="6"/>
+      <c r="G239" s="6"/>
+      <c r="H239" s="6"/>
+      <c r="I239" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="J239" s="8"/>
+      <c r="K239" s="9"/>
+      <c r="L239" s="9"/>
+      <c r="M239" s="9"/>
     </row>
     <row r="240" spans="1:13">
       <c r="A240" s="2" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="D240" s="2">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
       <c r="E240" s="2">
-        <v>6.65</v>
+        <v>5.53</v>
       </c>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
       <c r="H240" s="2"/>
       <c r="I240" s="3" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="J240" s="2"/>
     </row>
     <row r="241" spans="1:10">
       <c r="A241" s="2" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="D241" s="2">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="E241" s="2">
-        <v>6.23</v>
+        <v>6.65</v>
       </c>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
       <c r="I241" s="3" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="J241" s="2"/>
     </row>
     <row r="242" spans="1:10">
       <c r="A242" s="2" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="D242" s="2">
-        <v>0.9</v>
+        <v>9.5</v>
       </c>
       <c r="E242" s="2">
-        <v>0.9</v>
+        <v>6.65</v>
       </c>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
       <c r="I242" s="3" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="J242" s="2"/>
     </row>
     <row r="243" spans="1:10">
       <c r="A243" s="2" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="D243" s="2">
-        <v>0.9</v>
+        <v>9.5</v>
       </c>
       <c r="E243" s="2">
-        <v>0.9</v>
+        <v>6.65</v>
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
       <c r="I243" s="3" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="J243" s="2"/>
     </row>
     <row r="244" spans="1:10">
       <c r="A244" s="2" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="D244" s="2">
-        <v>5.9</v>
+        <v>8.9</v>
       </c>
       <c r="E244" s="2">
-        <v>4.13</v>
+        <v>6.23</v>
       </c>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
       <c r="H244" s="2"/>
       <c r="I244" s="3" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
       <c r="J244" s="2"/>
     </row>
     <row r="245" spans="1:10">
       <c r="A245" s="2" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="D245" s="2">
-        <v>7.9</v>
+        <v>0.9</v>
       </c>
       <c r="E245" s="2">
-        <v>5.53</v>
+        <v>0.9</v>
       </c>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
       <c r="I245" s="3" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="J245" s="2"/>
     </row>
     <row r="246" spans="1:10">
       <c r="A246" s="2" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="D246" s="2">
-        <v>9.9</v>
+        <v>0.9</v>
       </c>
       <c r="E246" s="2">
-        <v>6.93</v>
+        <v>0.9</v>
       </c>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
       <c r="I246" s="3" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="J246" s="2"/>
     </row>
     <row r="247" spans="1:10">
       <c r="A247" s="2" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="D247" s="2">
-        <v>8.6999999999999993</v>
+        <v>5.9</v>
       </c>
       <c r="E247" s="2">
-        <v>6.09</v>
+        <v>4.13</v>
       </c>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
       <c r="I247" s="3" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="J247" s="2"/>
     </row>
     <row r="248" spans="1:10">
       <c r="A248" s="2" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="D248" s="2">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="E248" s="2">
-        <v>4.13</v>
+        <v>5.53</v>
       </c>
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
       <c r="H248" s="2"/>
       <c r="I248" s="3" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="J248" s="2"/>
     </row>
     <row r="249" spans="1:10">
       <c r="A249" s="2" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="D249" s="2">
-        <v>10.5</v>
+        <v>9.9</v>
       </c>
       <c r="E249" s="2">
-        <v>7.35</v>
+        <v>6.93</v>
       </c>
       <c r="F249" s="2"/>
       <c r="G249" s="2"/>
       <c r="H249" s="2"/>
       <c r="I249" s="3" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="J249" s="2"/>
     </row>
     <row r="250" spans="1:10">
       <c r="A250" s="2" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="D250" s="2">
-        <v>5.9</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="E250" s="2">
-        <v>4.13</v>
+        <v>6.09</v>
       </c>
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
       <c r="I250" s="3" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="J250" s="2"/>
     </row>
     <row r="251" spans="1:10">
       <c r="A251" s="2" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="D251" s="2">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="E251" s="2">
-        <v>4.55</v>
+        <v>4.13</v>
       </c>
       <c r="F251" s="2"/>
       <c r="G251" s="2"/>
       <c r="H251" s="2"/>
       <c r="I251" s="3" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="J251" s="2"/>
     </row>
     <row r="252" spans="1:10">
       <c r="A252" s="2" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="D252" s="2">
-        <v>7.9</v>
+        <v>10.5</v>
       </c>
       <c r="E252" s="2">
-        <v>5.53</v>
+        <v>7.35</v>
       </c>
       <c r="F252" s="2"/>
       <c r="G252" s="2"/>
       <c r="H252" s="2"/>
       <c r="I252" s="3" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="J252" s="2"/>
     </row>
     <row r="253" spans="1:10">
       <c r="A253" s="2" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="D253" s="2">
-        <v>9.6</v>
+        <v>5.9</v>
       </c>
       <c r="E253" s="2">
-        <v>6.72</v>
+        <v>4.13</v>
       </c>
       <c r="F253" s="2"/>
       <c r="G253" s="2"/>
       <c r="H253" s="2"/>
       <c r="I253" s="3" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="J253" s="2"/>
     </row>
     <row r="254" spans="1:10">
       <c r="A254" s="2" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
       <c r="D254" s="2">
-        <v>9.6</v>
+        <v>6.5</v>
       </c>
       <c r="E254" s="2">
-        <v>6.72</v>
+        <v>4.55</v>
       </c>
       <c r="F254" s="2"/>
       <c r="G254" s="2"/>
       <c r="H254" s="2"/>
       <c r="I254" s="3" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="J254" s="2"/>
     </row>
     <row r="255" spans="1:10">
       <c r="A255" s="2" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
       <c r="D255" s="2">
-        <v>10.1</v>
+        <v>7.9</v>
       </c>
       <c r="E255" s="2">
-        <v>7.07</v>
+        <v>5.53</v>
       </c>
       <c r="F255" s="2"/>
       <c r="G255" s="2"/>
       <c r="H255" s="2"/>
       <c r="I255" s="3" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="J255" s="2"/>
     </row>
     <row r="256" spans="1:10">
       <c r="A256" s="2" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="D256" s="2">
-        <v>10.9</v>
+        <v>9.6</v>
       </c>
       <c r="E256" s="2">
-        <v>7.63</v>
+        <v>6.72</v>
       </c>
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
       <c r="I256" s="3" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="J256" s="2"/>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257" spans="1:10">
       <c r="A257" s="2" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
       <c r="D257" s="2">
         <v>9.6</v>
@@ -10014,187 +10044,187 @@
       <c r="G257" s="2"/>
       <c r="H257" s="2"/>
       <c r="I257" s="3" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="J257" s="2"/>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258" spans="1:10">
       <c r="A258" s="2" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>630</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="D258" s="2">
-        <v>5.9</v>
+        <v>10.1</v>
       </c>
       <c r="E258" s="2">
-        <v>4.13</v>
+        <v>7.07</v>
       </c>
       <c r="F258" s="2"/>
       <c r="G258" s="2"/>
       <c r="H258" s="2"/>
       <c r="I258" s="3" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
       <c r="J258" s="2"/>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259" spans="1:10">
       <c r="A259" s="2" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>430</v>
+        <v>630</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
       <c r="D259" s="2">
-        <v>8.9</v>
+        <v>10.9</v>
       </c>
       <c r="E259" s="2">
-        <v>6.23</v>
+        <v>7.63</v>
       </c>
       <c r="F259" s="2"/>
       <c r="G259" s="2"/>
       <c r="H259" s="2"/>
       <c r="I259" s="3" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="J259" s="2"/>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260" spans="1:10">
       <c r="A260" s="2" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>426</v>
+        <v>630</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="D260" s="2">
-        <v>4.9000000000000004</v>
+        <v>9.6</v>
       </c>
       <c r="E260" s="2">
-        <v>3.43</v>
+        <v>6.72</v>
       </c>
       <c r="F260" s="2"/>
       <c r="G260" s="2"/>
       <c r="H260" s="2"/>
       <c r="I260" s="3" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="J260" s="2"/>
     </row>
-    <row r="261" spans="1:11">
+    <row r="261" spans="1:10">
       <c r="A261" s="2" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>430</v>
+        <v>630</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>600</v>
+        <v>744</v>
       </c>
       <c r="D261" s="2">
-        <v>10.9</v>
+        <v>5.9</v>
       </c>
       <c r="E261" s="2">
-        <v>7.63</v>
+        <v>4.13</v>
       </c>
       <c r="F261" s="2"/>
       <c r="G261" s="2"/>
       <c r="H261" s="2"/>
       <c r="I261" s="3" t="s">
-        <v>601</v>
+        <v>745</v>
       </c>
       <c r="J261" s="2"/>
     </row>
-    <row r="262" spans="1:11">
+    <row r="262" spans="1:10">
       <c r="A262" s="2" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>754</v>
+        <v>430</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="D262" s="2">
-        <v>18.5</v>
+        <v>8.9</v>
       </c>
       <c r="E262" s="2">
-        <v>12.95</v>
+        <v>6.23</v>
       </c>
       <c r="F262" s="2"/>
       <c r="G262" s="2"/>
       <c r="H262" s="2"/>
       <c r="I262" s="3" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="J262" s="2"/>
     </row>
-    <row r="263" spans="1:11">
+    <row r="263" spans="1:10">
       <c r="A263" s="2" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>754</v>
+        <v>426</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="D263" s="2">
-        <v>18.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E263" s="2">
-        <v>12.95</v>
+        <v>3.43</v>
       </c>
       <c r="F263" s="2"/>
       <c r="G263" s="2"/>
       <c r="H263" s="2"/>
       <c r="I263" s="3" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="J263" s="2"/>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:10">
       <c r="A264" s="2" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>754</v>
+        <v>430</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>761</v>
+        <v>600</v>
       </c>
       <c r="D264" s="2">
-        <v>18.5</v>
+        <v>10.9</v>
       </c>
       <c r="E264" s="2">
-        <v>12.95</v>
+        <v>7.63</v>
       </c>
       <c r="F264" s="2"/>
       <c r="G264" s="2"/>
       <c r="H264" s="2"/>
       <c r="I264" s="3" t="s">
-        <v>762</v>
+        <v>601</v>
       </c>
       <c r="J264" s="2"/>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265" spans="1:10">
       <c r="A265" s="2" t="s">
-        <v>763</v>
+        <v>753</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="D265" s="2">
         <v>18.5</v>
@@ -10206,19 +10236,19 @@
       <c r="G265" s="2"/>
       <c r="H265" s="2"/>
       <c r="I265" s="3" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="J265" s="2"/>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266" spans="1:10">
       <c r="A266" s="2" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="D266" s="2">
         <v>18.5</v>
@@ -10230,19 +10260,19 @@
       <c r="G266" s="2"/>
       <c r="H266" s="2"/>
       <c r="I266" s="3" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
       <c r="J266" s="2"/>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267" spans="1:10">
       <c r="A267" s="2" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="D267" s="2">
         <v>18.5</v>
@@ -10254,284 +10284,284 @@
       <c r="G267" s="2"/>
       <c r="H267" s="2"/>
       <c r="I267" s="3" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="J267" s="2"/>
     </row>
-    <row r="268" spans="1:11">
+    <row r="268" spans="1:10">
       <c r="A268" s="2" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="D268" s="2">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="E268" s="2">
-        <v>13.65</v>
+        <v>12.95</v>
       </c>
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
       <c r="H268" s="2"/>
       <c r="I268" s="3" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="J268" s="2"/>
     </row>
-    <row r="269" spans="1:11">
+    <row r="269" spans="1:10">
       <c r="A269" s="2" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="D269" s="2">
-        <v>22.5</v>
+        <v>18.5</v>
       </c>
       <c r="E269" s="2">
-        <v>15.75</v>
+        <v>12.95</v>
       </c>
       <c r="F269" s="2"/>
       <c r="G269" s="2"/>
       <c r="H269" s="2"/>
       <c r="I269" s="3" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="J269" s="2"/>
     </row>
-    <row r="270" spans="1:11">
-      <c r="A270" s="5">
-        <v>80305</v>
-      </c>
-      <c r="B270" s="6" t="s">
-        <v>781</v>
-      </c>
-      <c r="C270" s="6" t="s">
-        <v>778</v>
-      </c>
-      <c r="D270" s="6">
-        <v>6.9</v>
-      </c>
-      <c r="E270" s="6">
-        <v>4.83</v>
-      </c>
-      <c r="F270" s="6"/>
-      <c r="G270" s="6"/>
-      <c r="H270" s="6"/>
-      <c r="I270" s="7" t="s">
-        <v>779</v>
-      </c>
-      <c r="J270" s="8"/>
-      <c r="K270" s="9"/>
-    </row>
-    <row r="271" spans="1:11">
+    <row r="270" spans="1:10">
+      <c r="A270" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="D270" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="E270" s="2">
+        <v>12.95</v>
+      </c>
+      <c r="F270" s="2"/>
+      <c r="G270" s="2"/>
+      <c r="H270" s="2"/>
+      <c r="I270" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="J270" s="2"/>
+    </row>
+    <row r="271" spans="1:10">
       <c r="A271" s="2" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>781</v>
+        <v>754</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="D271" s="2">
-        <v>5.9</v>
+        <v>19.5</v>
       </c>
       <c r="E271" s="2">
-        <v>4.13</v>
+        <v>13.65</v>
       </c>
       <c r="F271" s="2"/>
       <c r="G271" s="2"/>
       <c r="H271" s="2"/>
-      <c r="I271" s="11" t="s">
-        <v>1117</v>
+      <c r="I271" s="3" t="s">
+        <v>774</v>
       </c>
       <c r="J271" s="2"/>
     </row>
-    <row r="272" spans="1:11">
+    <row r="272" spans="1:10">
       <c r="A272" s="2" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>781</v>
+        <v>754</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="D272" s="2">
-        <v>5.9</v>
+        <v>22.5</v>
       </c>
       <c r="E272" s="2">
-        <v>4.13</v>
+        <v>15.75</v>
       </c>
       <c r="F272" s="2"/>
       <c r="G272" s="2"/>
       <c r="H272" s="2"/>
       <c r="I272" s="3" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="J272" s="2"/>
     </row>
-    <row r="273" spans="1:10">
-      <c r="A273" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="B273" s="2" t="s">
+    <row r="273" spans="1:11">
+      <c r="A273" s="5">
+        <v>80305</v>
+      </c>
+      <c r="B273" s="6" t="s">
         <v>781</v>
       </c>
-      <c r="C273" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="D273" s="2">
-        <v>15.9</v>
-      </c>
-      <c r="E273" s="2">
-        <v>11.13</v>
-      </c>
-      <c r="F273" s="2"/>
-      <c r="G273" s="2"/>
-      <c r="H273" s="2"/>
-      <c r="I273" s="3" t="s">
-        <v>788</v>
-      </c>
-      <c r="J273" s="2"/>
-    </row>
-    <row r="274" spans="1:10">
+      <c r="C273" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="D273" s="6">
+        <v>6.9</v>
+      </c>
+      <c r="E273" s="6">
+        <v>4.83</v>
+      </c>
+      <c r="F273" s="6"/>
+      <c r="G273" s="6"/>
+      <c r="H273" s="6"/>
+      <c r="I273" s="7" t="s">
+        <v>779</v>
+      </c>
+      <c r="J273" s="8"/>
+      <c r="K273" s="9"/>
+    </row>
+    <row r="274" spans="1:11">
       <c r="A274" s="2" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="D274" s="2">
-        <v>15.9</v>
+        <v>5.9</v>
       </c>
       <c r="E274" s="2">
-        <v>11.13</v>
+        <v>4.13</v>
       </c>
       <c r="F274" s="2"/>
       <c r="G274" s="2"/>
       <c r="H274" s="2"/>
-      <c r="I274" s="3" t="s">
-        <v>791</v>
+      <c r="I274" s="11" t="s">
+        <v>1117</v>
       </c>
       <c r="J274" s="2"/>
     </row>
-    <row r="275" spans="1:10">
+    <row r="275" spans="1:11">
       <c r="A275" s="2" t="s">
-        <v>792</v>
+        <v>783</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>793</v>
+        <v>784</v>
       </c>
       <c r="D275" s="2">
-        <v>4.9000000000000004</v>
+        <v>5.9</v>
       </c>
       <c r="E275" s="2">
-        <v>3.43</v>
+        <v>4.13</v>
       </c>
       <c r="F275" s="2"/>
       <c r="G275" s="2"/>
       <c r="H275" s="2"/>
       <c r="I275" s="3" t="s">
-        <v>794</v>
+        <v>785</v>
       </c>
       <c r="J275" s="2"/>
     </row>
-    <row r="276" spans="1:10">
+    <row r="276" spans="1:11">
       <c r="A276" s="2" t="s">
-        <v>795</v>
+        <v>786</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
       <c r="D276" s="2">
-        <v>6.5</v>
+        <v>15.9</v>
       </c>
       <c r="E276" s="2">
-        <v>4.55</v>
+        <v>11.13</v>
       </c>
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
       <c r="H276" s="2"/>
       <c r="I276" s="3" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
       <c r="J276" s="2"/>
     </row>
-    <row r="277" spans="1:10">
+    <row r="277" spans="1:11">
       <c r="A277" s="2" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
       <c r="D277" s="2">
-        <v>5.9</v>
+        <v>15.9</v>
       </c>
       <c r="E277" s="2">
-        <v>4.13</v>
+        <v>11.13</v>
       </c>
       <c r="F277" s="2"/>
       <c r="G277" s="2"/>
       <c r="H277" s="2"/>
       <c r="I277" s="3" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
       <c r="J277" s="2"/>
     </row>
-    <row r="278" spans="1:10">
+    <row r="278" spans="1:11">
       <c r="A278" s="2" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="D278" s="2">
-        <v>6.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E278" s="2">
-        <v>4.55</v>
+        <v>3.43</v>
       </c>
       <c r="F278" s="2"/>
       <c r="G278" s="2"/>
       <c r="H278" s="2"/>
       <c r="I278" s="3" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
       <c r="J278" s="2"/>
     </row>
-    <row r="279" spans="1:10">
+    <row r="279" spans="1:11">
       <c r="A279" s="2" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="D279" s="2">
         <v>6.5</v>
@@ -10543,379 +10573,379 @@
       <c r="G279" s="2"/>
       <c r="H279" s="2"/>
       <c r="I279" s="3" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
       <c r="J279" s="2"/>
     </row>
-    <row r="280" spans="1:10">
+    <row r="280" spans="1:11">
       <c r="A280" s="2" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
       <c r="D280" s="2">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="E280" s="2">
-        <v>4.83</v>
+        <v>4.13</v>
       </c>
       <c r="F280" s="2"/>
       <c r="G280" s="2"/>
       <c r="H280" s="2"/>
       <c r="I280" s="3" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
       <c r="J280" s="2"/>
     </row>
-    <row r="281" spans="1:10">
+    <row r="281" spans="1:11">
       <c r="A281" s="2" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
       <c r="D281" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="E281" s="2">
-        <v>4.83</v>
+        <v>4.55</v>
       </c>
       <c r="F281" s="2"/>
       <c r="G281" s="2"/>
       <c r="H281" s="2"/>
       <c r="I281" s="3" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
       <c r="J281" s="2"/>
     </row>
-    <row r="282" spans="1:10">
+    <row r="282" spans="1:11">
       <c r="A282" s="2" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
       <c r="D282" s="2">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="E282" s="2">
-        <v>5.53</v>
+        <v>4.55</v>
       </c>
       <c r="F282" s="2"/>
       <c r="G282" s="2"/>
       <c r="H282" s="2"/>
       <c r="I282" s="3" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
       <c r="J282" s="2"/>
     </row>
-    <row r="283" spans="1:10">
+    <row r="283" spans="1:11">
       <c r="A283" s="2" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
       <c r="D283" s="2">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="E283" s="2">
-        <v>5.25</v>
+        <v>4.83</v>
       </c>
       <c r="F283" s="2"/>
       <c r="G283" s="2"/>
       <c r="H283" s="2"/>
       <c r="I283" s="3" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
       <c r="J283" s="2"/>
     </row>
-    <row r="284" spans="1:10">
+    <row r="284" spans="1:11">
       <c r="A284" s="2" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D284" s="2">
-        <v>4.9000000000000004</v>
+        <v>6.9</v>
       </c>
       <c r="E284" s="2">
-        <v>3.43</v>
+        <v>4.83</v>
       </c>
       <c r="F284" s="2"/>
       <c r="G284" s="2"/>
       <c r="H284" s="2"/>
       <c r="I284" s="3" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
       <c r="J284" s="2"/>
     </row>
-    <row r="285" spans="1:10">
+    <row r="285" spans="1:11">
       <c r="A285" s="2" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>823</v>
+        <v>814</v>
       </c>
       <c r="D285" s="2">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="E285" s="2">
-        <v>4.83</v>
+        <v>5.53</v>
       </c>
       <c r="F285" s="2"/>
       <c r="G285" s="2"/>
       <c r="H285" s="2"/>
       <c r="I285" s="3" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
       <c r="J285" s="2"/>
     </row>
-    <row r="286" spans="1:10">
+    <row r="286" spans="1:11">
       <c r="A286" s="2" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
       <c r="D286" s="2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="E286" s="2">
-        <v>5.53</v>
+        <v>5.25</v>
       </c>
       <c r="F286" s="2"/>
       <c r="G286" s="2"/>
       <c r="H286" s="2"/>
       <c r="I286" s="3" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
       <c r="J286" s="2"/>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:11">
       <c r="A287" s="2" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
       <c r="D287" s="2">
-        <v>6.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E287" s="2">
-        <v>4.83</v>
+        <v>3.43</v>
       </c>
       <c r="F287" s="2"/>
       <c r="G287" s="2"/>
       <c r="H287" s="2"/>
       <c r="I287" s="3" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="J287" s="2"/>
     </row>
-    <row r="288" spans="1:10">
+    <row r="288" spans="1:11">
       <c r="A288" s="2" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>832</v>
+        <v>823</v>
       </c>
       <c r="D288" s="2">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="E288" s="2">
-        <v>5.25</v>
+        <v>4.83</v>
       </c>
       <c r="F288" s="2"/>
       <c r="G288" s="2"/>
       <c r="H288" s="2"/>
       <c r="I288" s="3" t="s">
-        <v>833</v>
+        <v>824</v>
       </c>
       <c r="J288" s="2"/>
     </row>
     <row r="289" spans="1:10">
       <c r="A289" s="2" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
       <c r="D289" s="2">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="E289" s="2">
-        <v>4.13</v>
+        <v>5.53</v>
       </c>
       <c r="F289" s="2"/>
       <c r="G289" s="2"/>
       <c r="H289" s="2"/>
       <c r="I289" s="3" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="J289" s="2"/>
     </row>
     <row r="290" spans="1:10">
       <c r="A290" s="2" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>838</v>
+        <v>829</v>
       </c>
       <c r="D290" s="2">
-        <v>4.9000000000000004</v>
+        <v>6.9</v>
       </c>
       <c r="E290" s="2">
-        <v>3.43</v>
+        <v>4.83</v>
       </c>
       <c r="F290" s="2"/>
       <c r="G290" s="2"/>
       <c r="H290" s="2"/>
       <c r="I290" s="3" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
       <c r="J290" s="2"/>
     </row>
     <row r="291" spans="1:10">
       <c r="A291" s="2" t="s">
-        <v>840</v>
+        <v>831</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
       <c r="D291" s="2">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="E291" s="2">
-        <v>5.95</v>
+        <v>5.25</v>
       </c>
       <c r="F291" s="2"/>
       <c r="G291" s="2"/>
       <c r="H291" s="2"/>
       <c r="I291" s="3" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="J291" s="2"/>
     </row>
     <row r="292" spans="1:10">
       <c r="A292" s="2" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
       <c r="D292" s="2">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="E292" s="2">
-        <v>4.83</v>
+        <v>4.13</v>
       </c>
       <c r="F292" s="2"/>
       <c r="G292" s="2"/>
       <c r="H292" s="2"/>
       <c r="I292" s="3" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
       <c r="J292" s="2"/>
     </row>
     <row r="293" spans="1:10">
       <c r="A293" s="2" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>847</v>
+        <v>838</v>
       </c>
       <c r="D293" s="2">
-        <v>6.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E293" s="2">
-        <v>4.55</v>
+        <v>3.43</v>
       </c>
       <c r="F293" s="2"/>
       <c r="G293" s="2"/>
       <c r="H293" s="2"/>
       <c r="I293" s="3" t="s">
-        <v>848</v>
+        <v>839</v>
       </c>
       <c r="J293" s="2"/>
     </row>
     <row r="294" spans="1:10">
       <c r="A294" s="2" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
       <c r="D294" s="2">
-        <v>10.9</v>
+        <v>8.5</v>
       </c>
       <c r="E294" s="2">
-        <v>7.63</v>
+        <v>5.95</v>
       </c>
       <c r="F294" s="2"/>
       <c r="G294" s="2"/>
       <c r="H294" s="2"/>
       <c r="I294" s="3" t="s">
-        <v>851</v>
+        <v>842</v>
       </c>
       <c r="J294" s="2"/>
     </row>
     <row r="295" spans="1:10">
       <c r="A295" s="2" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="D295" s="2">
         <v>6.9</v>
@@ -10927,115 +10957,115 @@
       <c r="G295" s="2"/>
       <c r="H295" s="2"/>
       <c r="I295" s="3" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="J295" s="2"/>
     </row>
     <row r="296" spans="1:10">
       <c r="A296" s="2" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
       <c r="D296" s="2">
-        <v>11.9</v>
+        <v>6.5</v>
       </c>
       <c r="E296" s="2">
-        <v>8.33</v>
+        <v>4.55</v>
       </c>
       <c r="F296" s="2"/>
       <c r="G296" s="2"/>
       <c r="H296" s="2"/>
       <c r="I296" s="3" t="s">
-        <v>857</v>
+        <v>848</v>
       </c>
       <c r="J296" s="2"/>
     </row>
     <row r="297" spans="1:10">
       <c r="A297" s="2" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="D297" s="2">
-        <v>6.9</v>
+        <v>10.9</v>
       </c>
       <c r="E297" s="2">
-        <v>4.83</v>
+        <v>7.63</v>
       </c>
       <c r="F297" s="2"/>
       <c r="G297" s="2"/>
       <c r="H297" s="2"/>
       <c r="I297" s="3" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="J297" s="2"/>
     </row>
     <row r="298" spans="1:10">
       <c r="A298" s="2" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="D298" s="2">
-        <v>11.9</v>
+        <v>6.9</v>
       </c>
       <c r="E298" s="2">
-        <v>8.33</v>
+        <v>4.83</v>
       </c>
       <c r="F298" s="2"/>
       <c r="G298" s="2"/>
       <c r="H298" s="2"/>
       <c r="I298" s="3" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
       <c r="J298" s="2"/>
     </row>
     <row r="299" spans="1:10">
       <c r="A299" s="2" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="D299" s="2">
-        <v>6.9</v>
+        <v>11.9</v>
       </c>
       <c r="E299" s="2">
-        <v>4.83</v>
+        <v>8.33</v>
       </c>
       <c r="F299" s="2"/>
       <c r="G299" s="2"/>
       <c r="H299" s="2"/>
       <c r="I299" s="3" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
       <c r="J299" s="2"/>
     </row>
     <row r="300" spans="1:10">
       <c r="A300" s="2" t="s">
-        <v>867</v>
+        <v>858</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="D300" s="2">
         <v>6.9</v>
@@ -11047,19 +11077,19 @@
       <c r="G300" s="2"/>
       <c r="H300" s="2"/>
       <c r="I300" s="3" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="J300" s="2"/>
     </row>
     <row r="301" spans="1:10">
       <c r="A301" s="2" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="D301" s="2">
         <v>11.9</v>
@@ -11071,67 +11101,67 @@
       <c r="G301" s="2"/>
       <c r="H301" s="2"/>
       <c r="I301" s="3" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="J301" s="2"/>
     </row>
     <row r="302" spans="1:10">
       <c r="A302" s="2" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="D302" s="2">
-        <v>11.9</v>
+        <v>6.9</v>
       </c>
       <c r="E302" s="2">
-        <v>8.33</v>
+        <v>4.83</v>
       </c>
       <c r="F302" s="2"/>
       <c r="G302" s="2"/>
       <c r="H302" s="2"/>
       <c r="I302" s="3" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="J302" s="2"/>
     </row>
     <row r="303" spans="1:10">
       <c r="A303" s="2" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="D303" s="2">
-        <v>11.9</v>
+        <v>6.9</v>
       </c>
       <c r="E303" s="2">
-        <v>8.33</v>
+        <v>4.83</v>
       </c>
       <c r="F303" s="2"/>
       <c r="G303" s="2"/>
       <c r="H303" s="2"/>
       <c r="I303" s="3" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
       <c r="J303" s="2"/>
     </row>
     <row r="304" spans="1:10">
       <c r="A304" s="2" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="D304" s="2">
         <v>11.9</v>
@@ -11143,473 +11173,473 @@
       <c r="G304" s="2"/>
       <c r="H304" s="2"/>
       <c r="I304" s="3" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="J304" s="2"/>
     </row>
     <row r="305" spans="1:10">
       <c r="A305" s="2" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="D305" s="2">
-        <v>9.9</v>
+        <v>11.9</v>
       </c>
       <c r="E305" s="2">
-        <v>6.93</v>
+        <v>8.33</v>
       </c>
       <c r="F305" s="2"/>
       <c r="G305" s="2"/>
       <c r="H305" s="2"/>
       <c r="I305" s="3" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="J305" s="2"/>
     </row>
     <row r="306" spans="1:10">
       <c r="A306" s="2" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="D306" s="2">
-        <v>10.9</v>
+        <v>11.9</v>
       </c>
       <c r="E306" s="2">
-        <v>7.63</v>
+        <v>8.33</v>
       </c>
       <c r="F306" s="2"/>
       <c r="G306" s="2"/>
       <c r="H306" s="2"/>
       <c r="I306" s="3" t="s">
-        <v>887</v>
+        <v>878</v>
       </c>
       <c r="J306" s="2"/>
     </row>
     <row r="307" spans="1:10">
       <c r="A307" s="2" t="s">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>889</v>
+        <v>880</v>
       </c>
       <c r="D307" s="2">
-        <v>6.9</v>
-      </c>
-      <c r="E307" s="2"/>
+        <v>11.9</v>
+      </c>
+      <c r="E307" s="2">
+        <v>8.33</v>
+      </c>
       <c r="F307" s="2"/>
       <c r="G307" s="2"/>
       <c r="H307" s="2"/>
       <c r="I307" s="3" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
       <c r="J307" s="2"/>
     </row>
     <row r="308" spans="1:10">
       <c r="A308" s="2" t="s">
-        <v>891</v>
+        <v>882</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>892</v>
+        <v>883</v>
       </c>
       <c r="D308" s="2">
-        <v>6.9</v>
+        <v>9.9</v>
       </c>
       <c r="E308" s="2">
-        <v>4.83</v>
+        <v>6.93</v>
       </c>
       <c r="F308" s="2"/>
       <c r="G308" s="2"/>
       <c r="H308" s="2"/>
       <c r="I308" s="3" t="s">
-        <v>893</v>
+        <v>884</v>
       </c>
       <c r="J308" s="2"/>
     </row>
     <row r="309" spans="1:10">
       <c r="A309" s="2" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="D309" s="2">
-        <v>5.5</v>
+        <v>10.9</v>
       </c>
       <c r="E309" s="2">
-        <v>3.85</v>
+        <v>7.63</v>
       </c>
       <c r="F309" s="2"/>
       <c r="G309" s="2"/>
       <c r="H309" s="2"/>
       <c r="I309" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="J309" s="2"/>
     </row>
     <row r="310" spans="1:10">
       <c r="A310" s="2" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="D310" s="2">
-        <v>5.9</v>
-      </c>
-      <c r="E310" s="2">
-        <v>4.13</v>
-      </c>
+        <v>6.9</v>
+      </c>
+      <c r="E310" s="2"/>
       <c r="F310" s="2"/>
       <c r="G310" s="2"/>
       <c r="H310" s="2"/>
       <c r="I310" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="J310" s="2"/>
     </row>
     <row r="311" spans="1:10">
       <c r="A311" s="2" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>901</v>
+        <v>892</v>
       </c>
       <c r="D311" s="2">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="E311" s="2">
-        <v>4.55</v>
+        <v>4.83</v>
       </c>
       <c r="F311" s="2"/>
       <c r="G311" s="2"/>
       <c r="H311" s="2"/>
       <c r="I311" s="3" t="s">
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="J311" s="2"/>
     </row>
     <row r="312" spans="1:10">
       <c r="A312" s="2" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="D312" s="2">
-        <v>7.9</v>
+        <v>5.5</v>
       </c>
       <c r="E312" s="2">
-        <v>5.53</v>
+        <v>3.85</v>
       </c>
       <c r="F312" s="2"/>
       <c r="G312" s="2"/>
       <c r="H312" s="2"/>
       <c r="I312" s="3" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="J312" s="2"/>
     </row>
     <row r="313" spans="1:10">
       <c r="A313" s="2" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
       <c r="D313" s="2">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="E313" s="2">
-        <v>1.75</v>
+        <v>4.13</v>
       </c>
       <c r="F313" s="2"/>
       <c r="G313" s="2"/>
       <c r="H313" s="2"/>
       <c r="I313" s="3" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="J313" s="2"/>
     </row>
     <row r="314" spans="1:10">
       <c r="A314" s="2" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="D314" s="2">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="E314" s="2">
-        <v>1.75</v>
+        <v>4.55</v>
       </c>
       <c r="F314" s="2"/>
       <c r="G314" s="2"/>
       <c r="H314" s="2"/>
       <c r="I314" s="3" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
       <c r="J314" s="2"/>
     </row>
     <row r="315" spans="1:10">
       <c r="A315" s="2" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="D315" s="2">
-        <v>1.5</v>
+        <v>7.9</v>
       </c>
       <c r="E315" s="2">
-        <v>1.05</v>
+        <v>5.53</v>
       </c>
       <c r="F315" s="2"/>
       <c r="G315" s="2"/>
       <c r="H315" s="2"/>
       <c r="I315" s="3" t="s">
-        <v>628</v>
+        <v>905</v>
       </c>
       <c r="J315" s="2"/>
     </row>
     <row r="316" spans="1:10">
-      <c r="A316" s="2">
-        <v>80146</v>
-      </c>
-      <c r="B316" s="12" t="s">
+      <c r="A316" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="B316" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="C316" s="12" t="s">
-        <v>1115</v>
+      <c r="C316" s="2" t="s">
+        <v>907</v>
       </c>
       <c r="D316" s="2">
-        <v>7.9</v>
+        <v>2.5</v>
       </c>
       <c r="E316" s="2">
-        <v>5.53</v>
+        <v>1.75</v>
       </c>
       <c r="F316" s="2"/>
       <c r="G316" s="2"/>
       <c r="H316" s="2"/>
       <c r="I316" s="3" t="s">
-        <v>1116</v>
+        <v>908</v>
       </c>
       <c r="J316" s="2"/>
     </row>
     <row r="317" spans="1:10">
       <c r="A317" s="2" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>781</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="D317" s="2">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E317" s="2">
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="F317" s="2"/>
       <c r="G317" s="2"/>
       <c r="H317" s="2"/>
       <c r="I317" s="3" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="J317" s="2"/>
     </row>
     <row r="318" spans="1:10">
-      <c r="A318" s="13">
-        <v>40505</v>
+      <c r="A318" s="2" t="s">
+        <v>912</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>754</v>
+        <v>781</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>1102</v>
+        <v>913</v>
       </c>
       <c r="D318" s="2">
-        <v>20.399999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="E318" s="2">
-        <v>14.28</v>
+        <v>1.05</v>
       </c>
       <c r="F318" s="2"/>
       <c r="G318" s="2"/>
       <c r="H318" s="2"/>
       <c r="I318" s="3" t="s">
-        <v>1103</v>
+        <v>628</v>
       </c>
       <c r="J318" s="2"/>
     </row>
     <row r="319" spans="1:10">
-      <c r="A319" s="2" t="s">
-        <v>917</v>
-      </c>
-      <c r="B319" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="C319" s="2" t="s">
-        <v>918</v>
+      <c r="A319" s="2">
+        <v>80146</v>
+      </c>
+      <c r="B319" s="12" t="s">
+        <v>781</v>
+      </c>
+      <c r="C319" s="12" t="s">
+        <v>1115</v>
       </c>
       <c r="D319" s="2">
-        <v>18.899999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="E319" s="2">
-        <v>13.23</v>
+        <v>5.53</v>
       </c>
       <c r="F319" s="2"/>
       <c r="G319" s="2"/>
       <c r="H319" s="2"/>
       <c r="I319" s="3" t="s">
-        <v>919</v>
+        <v>1116</v>
       </c>
       <c r="J319" s="2"/>
     </row>
     <row r="320" spans="1:10">
       <c r="A320" s="2" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>754</v>
+        <v>781</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="D320" s="2">
-        <v>20.9</v>
+        <v>1.5</v>
       </c>
       <c r="E320" s="2">
-        <v>14.63</v>
+        <v>1.05</v>
       </c>
       <c r="F320" s="2"/>
       <c r="G320" s="2"/>
       <c r="H320" s="2"/>
       <c r="I320" s="3" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="J320" s="2"/>
     </row>
     <row r="321" spans="1:10">
-      <c r="A321" s="2" t="s">
-        <v>923</v>
+      <c r="A321" s="13">
+        <v>40505</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>924</v>
+        <v>1102</v>
       </c>
       <c r="D321" s="2">
-        <v>22.5</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="E321" s="2">
-        <v>15.75</v>
+        <v>14.28</v>
       </c>
       <c r="F321" s="2"/>
       <c r="G321" s="2"/>
       <c r="H321" s="2"/>
       <c r="I321" s="3" t="s">
-        <v>925</v>
+        <v>1103</v>
       </c>
       <c r="J321" s="2"/>
     </row>
     <row r="322" spans="1:10">
       <c r="A322" s="2" t="s">
-        <v>926</v>
+        <v>917</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>927</v>
+        <v>918</v>
       </c>
       <c r="D322" s="2">
-        <v>22.5</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="E322" s="2">
-        <v>15.75</v>
+        <v>13.23</v>
       </c>
       <c r="F322" s="2"/>
       <c r="G322" s="2"/>
       <c r="H322" s="2"/>
       <c r="I322" s="3" t="s">
-        <v>928</v>
+        <v>919</v>
       </c>
       <c r="J322" s="2"/>
     </row>
     <row r="323" spans="1:10">
       <c r="A323" s="2" t="s">
-        <v>929</v>
+        <v>920</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>930</v>
+        <v>921</v>
       </c>
       <c r="D323" s="2">
-        <v>22.5</v>
+        <v>20.9</v>
       </c>
       <c r="E323" s="2">
-        <v>15.75</v>
+        <v>14.63</v>
       </c>
       <c r="F323" s="2"/>
       <c r="G323" s="2"/>
       <c r="H323" s="2"/>
       <c r="I323" s="3" t="s">
-        <v>931</v>
+        <v>922</v>
       </c>
       <c r="J323" s="2"/>
     </row>
     <row r="324" spans="1:10">
       <c r="A324" s="2" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>933</v>
+        <v>924</v>
       </c>
       <c r="D324" s="2">
         <v>22.5</v>
@@ -11621,91 +11651,91 @@
       <c r="G324" s="2"/>
       <c r="H324" s="2"/>
       <c r="I324" s="3" t="s">
-        <v>934</v>
+        <v>925</v>
       </c>
       <c r="J324" s="2"/>
     </row>
     <row r="325" spans="1:10">
       <c r="A325" s="2" t="s">
-        <v>935</v>
+        <v>926</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>936</v>
+        <v>927</v>
       </c>
       <c r="D325" s="2">
-        <v>18.5</v>
+        <v>22.5</v>
       </c>
       <c r="E325" s="2">
-        <v>12.95</v>
+        <v>15.75</v>
       </c>
       <c r="F325" s="2"/>
       <c r="G325" s="2"/>
       <c r="H325" s="2"/>
       <c r="I325" s="3" t="s">
-        <v>937</v>
+        <v>928</v>
       </c>
       <c r="J325" s="2"/>
     </row>
     <row r="326" spans="1:10">
       <c r="A326" s="2" t="s">
-        <v>938</v>
+        <v>929</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>939</v>
+        <v>930</v>
       </c>
       <c r="D326" s="2">
-        <v>16.3</v>
+        <v>22.5</v>
       </c>
       <c r="E326" s="2">
-        <v>11.41</v>
+        <v>15.75</v>
       </c>
       <c r="F326" s="2"/>
       <c r="G326" s="2"/>
       <c r="H326" s="2"/>
       <c r="I326" s="3" t="s">
-        <v>940</v>
+        <v>931</v>
       </c>
       <c r="J326" s="2"/>
     </row>
     <row r="327" spans="1:10">
       <c r="A327" s="2" t="s">
-        <v>941</v>
+        <v>932</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="D327" s="2">
-        <v>18.5</v>
+        <v>22.5</v>
       </c>
       <c r="E327" s="2">
-        <v>12.95</v>
+        <v>15.75</v>
       </c>
       <c r="F327" s="2"/>
       <c r="G327" s="2"/>
       <c r="H327" s="2"/>
       <c r="I327" s="3" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
       <c r="J327" s="2"/>
     </row>
     <row r="328" spans="1:10">
       <c r="A328" s="2" t="s">
-        <v>944</v>
+        <v>935</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="D328" s="2">
         <v>18.5</v>
@@ -11717,43 +11747,43 @@
       <c r="G328" s="2"/>
       <c r="H328" s="2"/>
       <c r="I328" s="3" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="J328" s="2"/>
     </row>
     <row r="329" spans="1:10">
       <c r="A329" s="2" t="s">
-        <v>947</v>
+        <v>938</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="D329" s="2">
-        <v>18.5</v>
+        <v>16.3</v>
       </c>
       <c r="E329" s="2">
-        <v>12.95</v>
+        <v>11.41</v>
       </c>
       <c r="F329" s="2"/>
       <c r="G329" s="2"/>
       <c r="H329" s="2"/>
       <c r="I329" s="3" t="s">
-        <v>949</v>
+        <v>940</v>
       </c>
       <c r="J329" s="2"/>
     </row>
     <row r="330" spans="1:10">
       <c r="A330" s="2" t="s">
-        <v>950</v>
+        <v>941</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>951</v>
+        <v>942</v>
       </c>
       <c r="D330" s="2">
         <v>18.5</v>
@@ -11765,19 +11795,19 @@
       <c r="G330" s="2"/>
       <c r="H330" s="2"/>
       <c r="I330" s="3" t="s">
-        <v>952</v>
+        <v>943</v>
       </c>
       <c r="J330" s="2"/>
     </row>
     <row r="331" spans="1:10">
       <c r="A331" s="2" t="s">
-        <v>953</v>
+        <v>944</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
       <c r="D331" s="2">
         <v>18.5</v>
@@ -11789,19 +11819,19 @@
       <c r="G331" s="2"/>
       <c r="H331" s="2"/>
       <c r="I331" s="3" t="s">
-        <v>955</v>
+        <v>946</v>
       </c>
       <c r="J331" s="2"/>
     </row>
     <row r="332" spans="1:10">
       <c r="A332" s="2" t="s">
-        <v>956</v>
+        <v>947</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
       <c r="D332" s="2">
         <v>18.5</v>
@@ -11813,951 +11843,951 @@
       <c r="G332" s="2"/>
       <c r="H332" s="2"/>
       <c r="I332" s="3" t="s">
-        <v>958</v>
+        <v>949</v>
       </c>
       <c r="J332" s="2"/>
     </row>
     <row r="333" spans="1:10">
       <c r="A333" s="2" t="s">
-        <v>959</v>
+        <v>950</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>960</v>
+        <v>951</v>
       </c>
       <c r="D333" s="2">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="E333" s="2">
-        <v>13.65</v>
+        <v>12.95</v>
       </c>
       <c r="F333" s="2"/>
       <c r="G333" s="2"/>
       <c r="H333" s="2"/>
       <c r="I333" s="3" t="s">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="J333" s="2"/>
     </row>
     <row r="334" spans="1:10">
       <c r="A334" s="2" t="s">
-        <v>962</v>
+        <v>953</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>963</v>
+        <v>954</v>
       </c>
       <c r="D334" s="2">
-        <v>22.5</v>
+        <v>18.5</v>
       </c>
       <c r="E334" s="2">
-        <v>15.75</v>
+        <v>12.95</v>
       </c>
       <c r="F334" s="2"/>
       <c r="G334" s="2"/>
       <c r="H334" s="2"/>
       <c r="I334" s="3" t="s">
-        <v>964</v>
+        <v>955</v>
       </c>
       <c r="J334" s="2"/>
     </row>
     <row r="335" spans="1:10">
       <c r="A335" s="2" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>966</v>
+        <v>957</v>
       </c>
       <c r="D335" s="2">
-        <v>16.899999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="E335" s="2">
-        <v>11.83</v>
+        <v>12.95</v>
       </c>
       <c r="F335" s="2"/>
       <c r="G335" s="2"/>
       <c r="H335" s="2"/>
       <c r="I335" s="3" t="s">
-        <v>967</v>
+        <v>958</v>
       </c>
       <c r="J335" s="2"/>
     </row>
     <row r="336" spans="1:10">
       <c r="A336" s="2" t="s">
-        <v>968</v>
+        <v>959</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>754</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>969</v>
+        <v>960</v>
       </c>
       <c r="D336" s="2">
-        <v>23.9</v>
+        <v>19.5</v>
       </c>
       <c r="E336" s="2">
-        <v>16.73</v>
+        <v>13.65</v>
       </c>
       <c r="F336" s="2"/>
       <c r="G336" s="2"/>
       <c r="H336" s="2"/>
       <c r="I336" s="3" t="s">
-        <v>970</v>
+        <v>961</v>
       </c>
       <c r="J336" s="2"/>
     </row>
     <row r="337" spans="1:11">
-      <c r="A337" s="5">
-        <v>100236</v>
-      </c>
-      <c r="B337" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="C337" s="6" t="s">
-        <v>971</v>
-      </c>
-      <c r="D337" s="6">
-        <v>14.9</v>
-      </c>
-      <c r="E337" s="6">
-        <v>10.43</v>
-      </c>
-      <c r="F337" s="6"/>
-      <c r="G337" s="6"/>
-      <c r="H337" s="6"/>
-      <c r="I337" s="7" t="s">
-        <v>972</v>
-      </c>
-      <c r="J337" s="8"/>
-      <c r="K337" s="9"/>
+      <c r="A337" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="C337" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="D337" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="E337" s="2">
+        <v>15.75</v>
+      </c>
+      <c r="F337" s="2"/>
+      <c r="G337" s="2"/>
+      <c r="H337" s="2"/>
+      <c r="I337" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="J337" s="2"/>
     </row>
     <row r="338" spans="1:11">
       <c r="A338" s="2" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>225</v>
+        <v>754</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="D338" s="2">
-        <v>11.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E338" s="2">
-        <v>8.0500000000000007</v>
+        <v>11.83</v>
       </c>
       <c r="F338" s="2"/>
       <c r="G338" s="2"/>
       <c r="H338" s="2"/>
       <c r="I338" s="3" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="J338" s="2"/>
     </row>
     <row r="339" spans="1:11">
       <c r="A339" s="2" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>225</v>
+        <v>754</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="D339" s="2">
-        <v>10.9</v>
+        <v>23.9</v>
       </c>
       <c r="E339" s="2">
-        <v>7.63</v>
+        <v>16.73</v>
       </c>
       <c r="F339" s="2"/>
       <c r="G339" s="2"/>
       <c r="H339" s="2"/>
       <c r="I339" s="3" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="J339" s="2"/>
     </row>
     <row r="340" spans="1:11">
-      <c r="A340" s="2" t="s">
-        <v>979</v>
-      </c>
-      <c r="B340" s="2" t="s">
+      <c r="A340" s="5">
+        <v>100236</v>
+      </c>
+      <c r="B340" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="C340" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="D340" s="2">
+      <c r="C340" s="6" t="s">
+        <v>971</v>
+      </c>
+      <c r="D340" s="6">
         <v>14.9</v>
       </c>
-      <c r="E340" s="2">
-        <v>10.15</v>
-      </c>
-      <c r="F340" s="2"/>
-      <c r="G340" s="2"/>
-      <c r="H340" s="2"/>
-      <c r="I340" s="3" t="s">
-        <v>981</v>
-      </c>
-      <c r="J340" s="2"/>
+      <c r="E340" s="6">
+        <v>10.43</v>
+      </c>
+      <c r="F340" s="6"/>
+      <c r="G340" s="6"/>
+      <c r="H340" s="6"/>
+      <c r="I340" s="7" t="s">
+        <v>972</v>
+      </c>
+      <c r="J340" s="8"/>
+      <c r="K340" s="9"/>
     </row>
     <row r="341" spans="1:11">
       <c r="A341" s="2" t="s">
-        <v>982</v>
+        <v>973</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>983</v>
+        <v>974</v>
       </c>
       <c r="D341" s="2">
-        <v>9.9</v>
+        <v>11.5</v>
       </c>
       <c r="E341" s="2">
-        <v>6.93</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="F341" s="2"/>
       <c r="G341" s="2"/>
       <c r="H341" s="2"/>
       <c r="I341" s="3" t="s">
-        <v>984</v>
+        <v>975</v>
       </c>
       <c r="J341" s="2"/>
     </row>
     <row r="342" spans="1:11">
       <c r="A342" s="2" t="s">
-        <v>985</v>
+        <v>976</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="D342" s="2">
-        <v>16.899999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="E342" s="2">
-        <v>11.83</v>
+        <v>7.63</v>
       </c>
       <c r="F342" s="2"/>
       <c r="G342" s="2"/>
       <c r="H342" s="2"/>
       <c r="I342" s="3" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
       <c r="J342" s="2"/>
     </row>
     <row r="343" spans="1:11">
       <c r="A343" s="2" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>989</v>
+        <v>980</v>
       </c>
       <c r="D343" s="2">
-        <v>14</v>
+        <v>14.9</v>
       </c>
       <c r="E343" s="2">
-        <v>9.8000000000000007</v>
+        <v>10.15</v>
       </c>
       <c r="F343" s="2"/>
       <c r="G343" s="2"/>
       <c r="H343" s="2"/>
       <c r="I343" s="3" t="s">
-        <v>990</v>
+        <v>981</v>
       </c>
       <c r="J343" s="2"/>
     </row>
     <row r="344" spans="1:11">
       <c r="A344" s="2" t="s">
-        <v>991</v>
+        <v>982</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>1104</v>
+        <v>983</v>
       </c>
       <c r="D344" s="2">
-        <v>15.9</v>
+        <v>9.9</v>
       </c>
       <c r="E344" s="2">
-        <v>11.13</v>
+        <v>6.93</v>
       </c>
       <c r="F344" s="2"/>
       <c r="G344" s="2"/>
       <c r="H344" s="2"/>
       <c r="I344" s="3" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="J344" s="2"/>
     </row>
     <row r="345" spans="1:11">
       <c r="A345" s="2" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="D345" s="2">
-        <v>15.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E345" s="2">
-        <v>11.13</v>
+        <v>11.83</v>
       </c>
       <c r="F345" s="2"/>
       <c r="G345" s="2"/>
       <c r="H345" s="2"/>
       <c r="I345" s="3" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="J345" s="2"/>
     </row>
     <row r="346" spans="1:11">
       <c r="A346" s="2" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="D346" s="2">
-        <v>11.9</v>
+        <v>14</v>
       </c>
       <c r="E346" s="2">
-        <v>8.33</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="F346" s="2"/>
       <c r="G346" s="2"/>
       <c r="H346" s="2"/>
       <c r="I346" s="3" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="J346" s="2"/>
     </row>
     <row r="347" spans="1:11">
       <c r="A347" s="2" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>1000</v>
+        <v>1104</v>
       </c>
       <c r="D347" s="2">
-        <v>6.9</v>
+        <v>15.9</v>
       </c>
       <c r="E347" s="2">
-        <v>4.83</v>
+        <v>11.13</v>
       </c>
       <c r="F347" s="2"/>
       <c r="G347" s="2"/>
       <c r="H347" s="2"/>
       <c r="I347" s="3" t="s">
-        <v>1001</v>
+        <v>992</v>
       </c>
       <c r="J347" s="2"/>
     </row>
     <row r="348" spans="1:11">
       <c r="A348" s="2" t="s">
-        <v>1002</v>
+        <v>993</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>1003</v>
+        <v>994</v>
       </c>
       <c r="D348" s="2">
-        <v>11.5</v>
+        <v>15.9</v>
       </c>
       <c r="E348" s="2">
-        <v>8.0500000000000007</v>
+        <v>11.13</v>
       </c>
       <c r="F348" s="2"/>
       <c r="G348" s="2"/>
       <c r="H348" s="2"/>
       <c r="I348" s="3" t="s">
-        <v>1004</v>
+        <v>995</v>
       </c>
       <c r="J348" s="2"/>
     </row>
     <row r="349" spans="1:11">
-      <c r="A349" s="5">
-        <v>100224</v>
-      </c>
-      <c r="B349" s="6" t="s">
+      <c r="A349" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="B349" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C349" s="6" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D349" s="6">
-        <v>12.5</v>
-      </c>
-      <c r="E349" s="6">
-        <v>8.75</v>
-      </c>
-      <c r="F349" s="6"/>
-      <c r="G349" s="6"/>
-      <c r="H349" s="6"/>
-      <c r="I349" s="7" t="s">
-        <v>1006</v>
-      </c>
-      <c r="J349" s="8"/>
-      <c r="K349" s="9"/>
+      <c r="C349" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="D349" s="2">
+        <v>11.9</v>
+      </c>
+      <c r="E349" s="2">
+        <v>8.33</v>
+      </c>
+      <c r="F349" s="2"/>
+      <c r="G349" s="2"/>
+      <c r="H349" s="2"/>
+      <c r="I349" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="J349" s="2"/>
     </row>
     <row r="350" spans="1:11">
       <c r="A350" s="2" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="D350" s="2">
-        <v>11.3</v>
+        <v>6.9</v>
       </c>
       <c r="E350" s="2">
-        <v>7.91</v>
+        <v>4.83</v>
       </c>
       <c r="F350" s="2"/>
       <c r="G350" s="2"/>
       <c r="H350" s="2"/>
       <c r="I350" s="3" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="J350" s="2"/>
     </row>
     <row r="351" spans="1:11">
       <c r="A351" s="2" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
       <c r="D351" s="2">
-        <v>26.9</v>
+        <v>11.5</v>
       </c>
       <c r="E351" s="2">
-        <v>18.829999999999998</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="F351" s="2"/>
       <c r="G351" s="2"/>
       <c r="H351" s="2"/>
       <c r="I351" s="3" t="s">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="J351" s="2"/>
     </row>
     <row r="352" spans="1:11">
-      <c r="A352" s="2" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B352" s="2" t="s">
+      <c r="A352" s="5">
+        <v>100224</v>
+      </c>
+      <c r="B352" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C352" s="2" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D352" s="2">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="E352" s="2">
-        <v>13.93</v>
-      </c>
-      <c r="F352" s="2"/>
-      <c r="G352" s="2"/>
-      <c r="H352" s="2"/>
-      <c r="I352" s="3" t="s">
-        <v>1015</v>
-      </c>
-      <c r="J352" s="2"/>
+      <c r="C352" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D352" s="6">
+        <v>12.5</v>
+      </c>
+      <c r="E352" s="6">
+        <v>8.75</v>
+      </c>
+      <c r="F352" s="6"/>
+      <c r="G352" s="6"/>
+      <c r="H352" s="6"/>
+      <c r="I352" s="7" t="s">
+        <v>1006</v>
+      </c>
+      <c r="J352" s="8"/>
+      <c r="K352" s="9"/>
     </row>
     <row r="353" spans="1:10">
       <c r="A353" s="2" t="s">
-        <v>1016</v>
+        <v>1007</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>9</v>
+        <v>253</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>1017</v>
+        <v>1008</v>
       </c>
       <c r="D353" s="2">
-        <v>36</v>
+        <v>11.3</v>
       </c>
       <c r="E353" s="2">
-        <v>25.2</v>
+        <v>7.91</v>
       </c>
       <c r="F353" s="2"/>
       <c r="G353" s="2"/>
       <c r="H353" s="2"/>
       <c r="I353" s="3" t="s">
-        <v>223</v>
+        <v>1009</v>
       </c>
       <c r="J353" s="2"/>
     </row>
     <row r="354" spans="1:10">
       <c r="A354" s="2" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>1019</v>
+        <v>1011</v>
       </c>
       <c r="D354" s="2">
-        <v>16.899999999999999</v>
+        <v>26.9</v>
       </c>
       <c r="E354" s="2">
-        <v>11.83</v>
+        <v>18.829999999999998</v>
       </c>
       <c r="F354" s="2"/>
       <c r="G354" s="2"/>
       <c r="H354" s="2"/>
       <c r="I354" s="3" t="s">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="J354" s="2"/>
     </row>
     <row r="355" spans="1:10">
       <c r="A355" s="2" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>1022</v>
+        <v>1014</v>
       </c>
       <c r="D355" s="2">
-        <v>18.5</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="E355" s="2">
-        <v>12.95</v>
+        <v>13.93</v>
       </c>
       <c r="F355" s="2"/>
       <c r="G355" s="2"/>
       <c r="H355" s="2"/>
       <c r="I355" s="3" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="J355" s="2"/>
     </row>
     <row r="356" spans="1:10">
       <c r="A356" s="2" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>225</v>
+        <v>9</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>1025</v>
+        <v>1017</v>
       </c>
       <c r="D356" s="2">
-        <v>15.5</v>
+        <v>36</v>
       </c>
       <c r="E356" s="2">
-        <v>10.85</v>
+        <v>25.2</v>
       </c>
       <c r="F356" s="2"/>
       <c r="G356" s="2"/>
       <c r="H356" s="2"/>
       <c r="I356" s="3" t="s">
-        <v>1026</v>
+        <v>223</v>
       </c>
       <c r="J356" s="2"/>
     </row>
     <row r="357" spans="1:10">
-      <c r="A357" s="13">
-        <v>100218</v>
-      </c>
-      <c r="B357" s="12" t="s">
-        <v>1105</v>
+      <c r="A357" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>232</v>
+        <v>1019</v>
       </c>
       <c r="D357" s="2">
-        <v>12.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E357" s="2">
-        <v>9.0299999999999994</v>
+        <v>11.83</v>
       </c>
       <c r="F357" s="2"/>
       <c r="G357" s="2"/>
       <c r="H357" s="2"/>
-      <c r="I357" s="3"/>
+      <c r="I357" s="3" t="s">
+        <v>1020</v>
+      </c>
       <c r="J357" s="2"/>
     </row>
     <row r="358" spans="1:10">
       <c r="A358" s="2" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="D358" s="2">
-        <v>19.899999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="E358" s="2">
-        <v>13.93</v>
+        <v>12.95</v>
       </c>
       <c r="F358" s="2"/>
       <c r="G358" s="2"/>
       <c r="H358" s="2"/>
       <c r="I358" s="3" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="J358" s="2"/>
     </row>
     <row r="359" spans="1:10">
       <c r="A359" s="2" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>9</v>
+        <v>225</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="D359" s="2">
-        <v>50.5</v>
+        <v>15.5</v>
       </c>
       <c r="E359" s="2">
-        <v>35.35</v>
+        <v>10.85</v>
       </c>
       <c r="F359" s="2"/>
       <c r="G359" s="2"/>
       <c r="H359" s="2"/>
       <c r="I359" s="3" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="J359" s="2"/>
     </row>
     <row r="360" spans="1:10">
-      <c r="A360" s="2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="B360" s="2" t="s">
-        <v>9</v>
+      <c r="A360" s="13">
+        <v>100218</v>
+      </c>
+      <c r="B360" s="12" t="s">
+        <v>1105</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>1034</v>
+        <v>232</v>
       </c>
       <c r="D360" s="2">
-        <v>32.5</v>
+        <v>12.9</v>
       </c>
       <c r="E360" s="2">
-        <v>22.75</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="F360" s="2"/>
       <c r="G360" s="2"/>
       <c r="H360" s="2"/>
-      <c r="I360" s="3" t="s">
-        <v>1035</v>
-      </c>
+      <c r="I360" s="3"/>
       <c r="J360" s="2"/>
     </row>
     <row r="361" spans="1:10">
       <c r="A361" s="2" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>9</v>
+        <v>225</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="D361" s="2">
-        <v>43.5</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="E361" s="2">
-        <v>30.45</v>
+        <v>13.93</v>
       </c>
       <c r="F361" s="2"/>
       <c r="G361" s="2"/>
       <c r="H361" s="2"/>
       <c r="I361" s="3" t="s">
-        <v>1038</v>
+        <v>1029</v>
       </c>
       <c r="J361" s="2"/>
     </row>
     <row r="362" spans="1:10">
       <c r="A362" s="2" t="s">
-        <v>1039</v>
+        <v>1030</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>225</v>
+        <v>9</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>1040</v>
+        <v>1031</v>
       </c>
       <c r="D362" s="2">
-        <v>8.9</v>
+        <v>50.5</v>
       </c>
       <c r="E362" s="2">
-        <v>6.23</v>
+        <v>35.35</v>
       </c>
       <c r="F362" s="2"/>
       <c r="G362" s="2"/>
       <c r="H362" s="2"/>
       <c r="I362" s="3" t="s">
-        <v>1041</v>
+        <v>1032</v>
       </c>
       <c r="J362" s="2"/>
     </row>
     <row r="363" spans="1:10">
       <c r="A363" s="2" t="s">
-        <v>1042</v>
+        <v>1033</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>225</v>
+        <v>9</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>1043</v>
+        <v>1034</v>
       </c>
       <c r="D363" s="2">
-        <v>14.5</v>
+        <v>32.5</v>
       </c>
       <c r="E363" s="2">
-        <v>10.15</v>
+        <v>22.75</v>
       </c>
       <c r="F363" s="2"/>
       <c r="G363" s="2"/>
       <c r="H363" s="2"/>
       <c r="I363" s="3" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="J363" s="2"/>
     </row>
     <row r="364" spans="1:10">
-      <c r="A364" s="13">
-        <v>100206</v>
-      </c>
-      <c r="B364" s="12" t="s">
-        <v>1105</v>
-      </c>
-      <c r="C364" s="12" t="s">
-        <v>244</v>
+      <c r="A364" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>1037</v>
       </c>
       <c r="D364" s="2">
-        <v>18.899999999999999</v>
+        <v>43.5</v>
       </c>
       <c r="E364" s="2">
-        <v>13.23</v>
+        <v>30.45</v>
       </c>
       <c r="F364" s="2"/>
       <c r="G364" s="2"/>
       <c r="H364" s="2"/>
-      <c r="I364" s="3"/>
+      <c r="I364" s="3" t="s">
+        <v>1038</v>
+      </c>
       <c r="J364" s="2"/>
     </row>
     <row r="365" spans="1:10">
-      <c r="A365" s="13">
-        <v>100220</v>
-      </c>
-      <c r="B365" s="12" t="s">
-        <v>1105</v>
-      </c>
-      <c r="C365" s="12" t="s">
-        <v>1106</v>
+      <c r="A365" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>1040</v>
       </c>
       <c r="D365" s="2">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="E365" s="2">
-        <v>6.93</v>
+        <v>6.23</v>
       </c>
       <c r="F365" s="2"/>
       <c r="G365" s="2"/>
       <c r="H365" s="2"/>
-      <c r="I365" s="3"/>
+      <c r="I365" s="3" t="s">
+        <v>1041</v>
+      </c>
       <c r="J365" s="2"/>
     </row>
     <row r="366" spans="1:10">
       <c r="A366" s="2" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="D366" s="2">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="E366" s="2">
-        <v>3.64</v>
+        <v>10.15</v>
       </c>
       <c r="F366" s="2"/>
       <c r="G366" s="2"/>
       <c r="H366" s="2"/>
       <c r="I366" s="3" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="J366" s="2"/>
     </row>
     <row r="367" spans="1:10">
-      <c r="A367" s="2" t="s">
-        <v>1048</v>
-      </c>
-      <c r="B367" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C367" s="2" t="s">
-        <v>1049</v>
+      <c r="A367" s="13">
+        <v>100206</v>
+      </c>
+      <c r="B367" s="12" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C367" s="12" t="s">
+        <v>244</v>
       </c>
       <c r="D367" s="2">
-        <v>6</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="E367" s="2">
-        <v>4.2</v>
+        <v>13.23</v>
       </c>
       <c r="F367" s="2"/>
       <c r="G367" s="2"/>
       <c r="H367" s="2"/>
-      <c r="I367" s="3" t="s">
-        <v>1050</v>
-      </c>
+      <c r="I367" s="3"/>
       <c r="J367" s="2"/>
     </row>
     <row r="368" spans="1:10">
-      <c r="A368" s="2" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B368" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C368" s="2" t="s">
-        <v>1052</v>
+      <c r="A368" s="13">
+        <v>100220</v>
+      </c>
+      <c r="B368" s="12" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C368" s="12" t="s">
+        <v>1106</v>
       </c>
       <c r="D368" s="2">
-        <v>6.9</v>
+        <v>9.9</v>
       </c>
       <c r="E368" s="2">
-        <v>4.83</v>
+        <v>6.93</v>
       </c>
       <c r="F368" s="2"/>
       <c r="G368" s="2"/>
       <c r="H368" s="2"/>
-      <c r="I368" s="3" t="s">
-        <v>1053</v>
-      </c>
+      <c r="I368" s="3"/>
       <c r="J368" s="2"/>
     </row>
     <row r="369" spans="1:10">
       <c r="A369" s="2" t="s">
-        <v>1054</v>
+        <v>1045</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>1055</v>
+        <v>1046</v>
       </c>
       <c r="D369" s="2">
-        <v>7.9</v>
+        <v>5.2</v>
       </c>
       <c r="E369" s="2">
-        <v>5.53</v>
+        <v>3.64</v>
       </c>
       <c r="F369" s="2"/>
       <c r="G369" s="2"/>
       <c r="H369" s="2"/>
       <c r="I369" s="3" t="s">
-        <v>1056</v>
+        <v>1047</v>
       </c>
       <c r="J369" s="2"/>
     </row>
     <row r="370" spans="1:10">
       <c r="A370" s="2" t="s">
-        <v>1057</v>
+        <v>1048</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>1058</v>
+        <v>1049</v>
       </c>
       <c r="D370" s="2">
-        <v>8.9</v>
+        <v>6</v>
       </c>
       <c r="E370" s="2">
-        <v>6.23</v>
+        <v>4.2</v>
       </c>
       <c r="F370" s="2"/>
       <c r="G370" s="2"/>
       <c r="H370" s="2"/>
       <c r="I370" s="3" t="s">
-        <v>1059</v>
+        <v>1050</v>
       </c>
       <c r="J370" s="2"/>
     </row>
     <row r="371" spans="1:10">
       <c r="A371" s="2" t="s">
-        <v>1060</v>
+        <v>1051</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>1061</v>
+        <v>1052</v>
       </c>
       <c r="D371" s="2">
-        <v>12.9</v>
+        <v>6.9</v>
       </c>
       <c r="E371" s="2">
-        <v>9.0299999999999994</v>
+        <v>4.83</v>
       </c>
       <c r="F371" s="2"/>
       <c r="G371" s="2"/>
       <c r="H371" s="2"/>
       <c r="I371" s="3" t="s">
-        <v>1062</v>
+        <v>1053</v>
       </c>
       <c r="J371" s="2"/>
     </row>
     <row r="372" spans="1:10">
       <c r="A372" s="2" t="s">
-        <v>1063</v>
+        <v>1054</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>1064</v>
+        <v>1055</v>
       </c>
       <c r="D372" s="2">
         <v>7.9</v>
@@ -12769,168 +12799,240 @@
       <c r="G372" s="2"/>
       <c r="H372" s="2"/>
       <c r="I372" s="3" t="s">
-        <v>1065</v>
+        <v>1056</v>
       </c>
       <c r="J372" s="2"/>
     </row>
     <row r="373" spans="1:10">
       <c r="A373" s="2" t="s">
-        <v>1066</v>
+        <v>1057</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>9</v>
+        <v>225</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>1067</v>
+        <v>1058</v>
       </c>
       <c r="D373" s="2">
-        <v>2.5</v>
+        <v>8.9</v>
       </c>
       <c r="E373" s="2">
-        <v>2.5</v>
+        <v>6.23</v>
       </c>
       <c r="F373" s="2"/>
       <c r="G373" s="2"/>
       <c r="H373" s="2"/>
       <c r="I373" s="3" t="s">
-        <v>1068</v>
+        <v>1059</v>
       </c>
       <c r="J373" s="2"/>
     </row>
     <row r="374" spans="1:10">
       <c r="A374" s="2" t="s">
-        <v>1069</v>
+        <v>1060</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>781</v>
+        <v>225</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>1070</v>
+        <v>1061</v>
       </c>
       <c r="D374" s="2">
-        <v>0.3</v>
+        <v>12.9</v>
       </c>
       <c r="E374" s="2">
-        <v>0.3</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="F374" s="2"/>
       <c r="G374" s="2"/>
       <c r="H374" s="2"/>
       <c r="I374" s="3" t="s">
-        <v>1071</v>
+        <v>1062</v>
       </c>
       <c r="J374" s="2"/>
     </row>
     <row r="375" spans="1:10">
       <c r="A375" s="2" t="s">
-        <v>1072</v>
+        <v>1063</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>781</v>
+        <v>225</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>1073</v>
+        <v>1064</v>
       </c>
       <c r="D375" s="2">
-        <v>0.3</v>
+        <v>7.9</v>
       </c>
       <c r="E375" s="2">
-        <v>0.3</v>
+        <v>5.53</v>
       </c>
       <c r="F375" s="2"/>
       <c r="G375" s="2"/>
       <c r="H375" s="2"/>
       <c r="I375" s="3" t="s">
-        <v>1074</v>
+        <v>1065</v>
       </c>
       <c r="J375" s="2"/>
     </row>
     <row r="376" spans="1:10">
       <c r="A376" s="2" t="s">
-        <v>1075</v>
+        <v>1066</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>781</v>
+        <v>9</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>1076</v>
+        <v>1067</v>
       </c>
       <c r="D376" s="2">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="E376" s="2">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="F376" s="2"/>
       <c r="G376" s="2"/>
       <c r="H376" s="2"/>
       <c r="I376" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="J376" s="2"/>
+    </row>
+    <row r="377" spans="1:10">
+      <c r="A377" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D377" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E377" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F377" s="2"/>
+      <c r="G377" s="2"/>
+      <c r="H377" s="2"/>
+      <c r="I377" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="J377" s="2"/>
+    </row>
+    <row r="378" spans="1:10">
+      <c r="A378" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C378" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D378" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E378" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F378" s="2"/>
+      <c r="G378" s="2"/>
+      <c r="H378" s="2"/>
+      <c r="I378" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="J378" s="2"/>
+    </row>
+    <row r="379" spans="1:10">
+      <c r="A379" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C379" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D379" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E379" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F379" s="2"/>
+      <c r="G379" s="2"/>
+      <c r="H379" s="2"/>
+      <c r="I379" s="3" t="s">
         <v>1077</v>
       </c>
-      <c r="J376" s="2"/>
-    </row>
-    <row r="377" spans="1:10">
-      <c r="A377" s="14">
+      <c r="J379" s="2"/>
+    </row>
+    <row r="380" spans="1:10">
+      <c r="A380" s="14">
         <v>120101</v>
       </c>
-      <c r="B377" s="12" t="s">
+      <c r="B380" s="12" t="s">
         <v>1108</v>
       </c>
-      <c r="C377" t="s">
+      <c r="C380" t="s">
         <v>1109</v>
       </c>
-      <c r="D377" s="12">
+      <c r="D380" s="12">
         <v>4.5</v>
       </c>
-      <c r="E377">
+      <c r="E380">
         <v>3.15</v>
       </c>
-      <c r="I377" s="11" t="s">
+      <c r="I380" s="11" t="s">
         <v>1110</v>
       </c>
     </row>
-    <row r="378" spans="1:10">
-      <c r="A378" s="14">
+    <row r="381" spans="1:10">
+      <c r="A381" s="14">
         <v>120102</v>
       </c>
-      <c r="B378" s="12" t="s">
+      <c r="B381" s="12" t="s">
         <v>1108</v>
       </c>
-      <c r="C378" s="15" t="s">
+      <c r="C381" s="15" t="s">
         <v>1111</v>
       </c>
-      <c r="D378" s="12">
+      <c r="D381" s="12">
         <v>3.5</v>
       </c>
-      <c r="E378">
+      <c r="E381">
         <v>2.4500000000000002</v>
       </c>
-      <c r="I378" s="11" t="s">
+      <c r="I381" s="11" t="s">
         <v>1112</v>
       </c>
     </row>
-    <row r="379" spans="1:10">
-      <c r="A379" s="14">
+    <row r="382" spans="1:10">
+      <c r="A382" s="14">
         <v>120103</v>
       </c>
-      <c r="B379" s="12" t="s">
+      <c r="B382" s="12" t="s">
         <v>1108</v>
       </c>
-      <c r="C379" t="s">
+      <c r="C382" t="s">
         <v>1113</v>
       </c>
-      <c r="D379" s="12">
+      <c r="D382" s="12">
         <v>3.5</v>
       </c>
-      <c r="E379">
+      <c r="E382">
         <v>2.4500000000000002</v>
       </c>
-      <c r="I379" t="s">
+      <c r="I382" t="s">
         <v>1114</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J376" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J379" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -13018,286 +13120,286 @@
     <hyperlink ref="I86" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
     <hyperlink ref="I88" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
     <hyperlink ref="I89" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="I90" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="I91" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="I92" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="I93" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="I94" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="I95" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="I96" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="I97" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="I98" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="I99" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="I100" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="I101" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="I102" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="I103" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="I104" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="I105" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="I106" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="I107" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="I108" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="I109" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="I110" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="I111" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="I112" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="I113" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="I114" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="I115" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="I116" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="I117" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="I119" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="I120" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="I121" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="I122" r:id="rId118" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="I123" r:id="rId119" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="I124" r:id="rId120" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="I125" r:id="rId121" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="I126" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="I127" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="I128" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="I129" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="I130" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="I131" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="I132" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="I133" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="I134" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="I135" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="I136" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="I137" r:id="rId133" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="I138" r:id="rId134" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="I139" r:id="rId135" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="I140" r:id="rId136" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="I141" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="I142" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="I143" r:id="rId139" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="I144" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="I145" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="I146" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="I147" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="I148" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="I149" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="I150" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="I151" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="I152" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="I153" r:id="rId149" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="I154" r:id="rId150" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="I155" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="I156" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="I157" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="I158" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="I159" r:id="rId155" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="I160" r:id="rId156" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="I162" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="I163" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="I164" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="I165" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="I166" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="I167" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="I168" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="I169" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="I170" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="I171" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="I172" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="I173" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="I174" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="I175" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="I176" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="I177" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="I178" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="I179" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="I180" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="I181" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="I182" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="I183" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="I184" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="I185" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="I186" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="I187" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="I188" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="I189" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="I190" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="I191" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="I192" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="I193" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="I194" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="I195" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="I196" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="I197" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="I198" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="I199" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="I200" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="I201" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="I202" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="I203" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="I204" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="I205" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="I206" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="I207" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="I208" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="I209" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="I210" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="I211" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="I212" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="I213" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="I214" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="I215" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="I219" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="I220" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="I221" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="I222" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="I223" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="I224" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="I225" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="I226" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="I227" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="I228" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="I229" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="I230" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="I231" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="I232" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="I233" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="I234" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="I235" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="I236" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="I237" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="I238" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="I239" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="I240" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="I241" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="I242" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="I243" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="I244" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="I245" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="I246" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="I247" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="I248" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="I249" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="I250" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="I251" r:id="rId243" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="I252" r:id="rId244" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="I253" r:id="rId245" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="I254" r:id="rId246" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="I255" r:id="rId247" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="I256" r:id="rId248" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="I257" r:id="rId249" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="I258" r:id="rId250" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="I259" r:id="rId251" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="I260" r:id="rId252" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="I261" r:id="rId253" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="I262" r:id="rId254" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="I263" r:id="rId255" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="I264" r:id="rId256" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="I265" r:id="rId257" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="I266" r:id="rId258" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="I267" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="I268" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="I269" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="I270" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="I271" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="I272" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="I273" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="I274" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="I275" r:id="rId267" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="I276" r:id="rId268" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="I277" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="I278" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="I279" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="I280" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="I281" r:id="rId273" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="I282" r:id="rId274" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="I283" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="I284" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="I285" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="I286" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="I287" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="I288" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="I289" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="I290" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="I291" r:id="rId283" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="I292" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="I293" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="I294" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="I295" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="I296" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="I297" r:id="rId289" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="I298" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="I299" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="I300" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="I301" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="I302" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="I303" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="I304" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="I305" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="I306" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="I307" r:id="rId299" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="I308" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="I309" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="I310" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="I311" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="I312" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="I313" r:id="rId305" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="I314" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="I315" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="I317" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="I319" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="I320" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="I321" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="I322" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="I323" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="I324" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="I325" r:id="rId315" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="I326" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="I327" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="I328" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="I329" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="I330" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="I331" r:id="rId321" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="I332" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="I333" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="I334" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="I335" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="I336" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="I337" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="I338" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="I339" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="I340" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="I341" r:id="rId331" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="I342" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="I343" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="I344" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="I345" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="I346" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="I347" r:id="rId337" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="I348" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="I349" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="I350" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="I351" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="I352" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="I353" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="I354" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="I355" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="I356" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="I358" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="I359" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="I360" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="I361" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="I362" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="I363" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="I366" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="I367" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="I368" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="I369" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="I370" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="I371" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="I372" r:id="rId359" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="I373" r:id="rId360" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="I374" r:id="rId361" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="I375" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="I376" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="I377" r:id="rId364" xr:uid="{F9160EA0-F07B-4BB5-B702-F5073AA95056}"/>
-    <hyperlink ref="I378" r:id="rId365" xr:uid="{1AC55159-5C0D-4F25-94CA-0E2E9DEE3542}"/>
-    <hyperlink ref="I216" r:id="rId366" xr:uid="{39463792-79B1-460E-B346-5F21542FF683}"/>
+    <hyperlink ref="I93" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="I94" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="I95" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="I96" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="I97" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="I98" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="I99" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="I100" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="I101" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="I102" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="I103" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="I104" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="I105" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="I106" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="I107" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="I108" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="I109" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="I110" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="I111" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="I112" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="I113" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="I114" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="I115" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="I116" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="I117" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="I118" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="I119" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="I120" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="I122" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="I123" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="I124" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="I125" r:id="rId118" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="I126" r:id="rId119" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="I127" r:id="rId120" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="I128" r:id="rId121" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="I129" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="I130" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="I131" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="I132" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="I133" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="I134" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="I135" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="I136" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="I137" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="I138" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="I139" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="I140" r:id="rId133" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="I141" r:id="rId134" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="I142" r:id="rId135" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="I143" r:id="rId136" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="I144" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="I145" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="I146" r:id="rId139" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="I147" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="I148" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="I149" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="I150" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="I151" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="I152" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="I153" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="I154" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="I155" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="I156" r:id="rId149" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="I157" r:id="rId150" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="I158" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="I159" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="I160" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="I161" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="I162" r:id="rId155" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="I163" r:id="rId156" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="I165" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="I166" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="I167" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="I168" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="I169" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="I170" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="I171" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="I172" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="I173" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="I174" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="I175" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="I176" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="I177" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="I178" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="I179" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="I180" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="I181" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="I182" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="I183" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="I184" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="I185" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="I186" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="I187" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="I188" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="I189" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="I190" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="I191" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="I192" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="I193" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="I194" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="I195" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="I196" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="I197" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="I198" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="I199" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="I200" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="I201" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="I202" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="I203" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="I204" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="I205" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="I206" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="I207" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="I208" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="I209" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="I210" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="I211" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="I212" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="I213" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="I214" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="I215" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="I216" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="I217" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="I218" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="I222" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="I223" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="I224" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="I225" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="I226" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="I227" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="I228" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="I229" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="I230" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="I231" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="I232" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="I233" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="I234" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="I235" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="I236" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="I237" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="I238" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="I239" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="I240" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="I241" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="I242" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="I243" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="I244" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="I245" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="I246" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="I247" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="I248" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="I249" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="I250" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="I251" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="I252" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="I253" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="I254" r:id="rId243" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="I255" r:id="rId244" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="I256" r:id="rId245" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="I257" r:id="rId246" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="I258" r:id="rId247" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="I259" r:id="rId248" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="I260" r:id="rId249" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="I261" r:id="rId250" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="I262" r:id="rId251" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="I263" r:id="rId252" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="I264" r:id="rId253" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="I265" r:id="rId254" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="I266" r:id="rId255" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="I267" r:id="rId256" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="I268" r:id="rId257" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="I269" r:id="rId258" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="I270" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="I271" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="I272" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="I273" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="I274" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="I275" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="I276" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="I277" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="I278" r:id="rId267" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="I279" r:id="rId268" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="I280" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="I281" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="I282" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="I283" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="I284" r:id="rId273" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="I285" r:id="rId274" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="I286" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="I287" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="I288" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="I289" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="I290" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="I291" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="I292" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="I293" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="I294" r:id="rId283" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="I295" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="I296" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="I297" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="I298" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="I299" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="I300" r:id="rId289" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="I301" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="I302" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="I303" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="I304" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="I305" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="I306" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="I307" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="I308" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="I309" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="I310" r:id="rId299" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="I311" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="I312" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="I313" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="I314" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="I315" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="I316" r:id="rId305" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="I317" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="I318" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="I320" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="I322" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="I323" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="I324" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="I325" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="I326" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="I327" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="I328" r:id="rId315" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="I329" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="I330" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="I331" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="I332" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="I333" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="I334" r:id="rId321" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="I335" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="I336" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="I337" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="I338" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="I339" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="I340" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="I341" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="I342" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="I343" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="I344" r:id="rId331" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="I345" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="I346" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="I347" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="I348" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="I349" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="I350" r:id="rId337" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="I351" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="I352" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="I353" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="I354" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="I355" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="I356" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="I357" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="I358" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="I359" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="I361" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="I362" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="I363" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="I364" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="I365" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="I366" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="I369" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="I370" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="I371" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="I372" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="I373" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="I374" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="I375" r:id="rId359" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="I376" r:id="rId360" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="I377" r:id="rId361" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="I378" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="I379" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="I380" r:id="rId364" xr:uid="{F9160EA0-F07B-4BB5-B702-F5073AA95056}"/>
+    <hyperlink ref="I381" r:id="rId365" xr:uid="{1AC55159-5C0D-4F25-94CA-0E2E9DEE3542}"/>
+    <hyperlink ref="I219" r:id="rId366" xr:uid="{39463792-79B1-460E-B346-5F21542FF683}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
